--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF46847D-BA21-4BFC-986C-B8D0C26F43DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E101D433-A70B-445A-A23F-311F00B78FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>Broadcom</t>
   </si>
@@ -209,6 +209,18 @@
   <si>
     <t>Interest and other Income</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -218,13 +230,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -304,31 +322,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -689,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>317.44</v>
+        <v>330.87</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -715,7 +736,7 @@
       </c>
       <c r="G5" s="4">
         <f>G3*G4</f>
-        <v>1505069.9547545598</v>
+        <v>1568745.26187513</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -750,7 +771,7 @@
       </c>
       <c r="G8" s="4">
         <f>G5-G6+G7</f>
-        <v>1554027.9547545598</v>
+        <v>1617703.26187513</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{096D1573-7190-410A-B6D0-6D0ABA0DB551}">
-  <dimension ref="A1:BY443"/>
+  <dimension ref="A1:CC443"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
@@ -771,21 +792,21 @@
     <col min="3" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77">
+    <row r="1" spans="1:81">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:77">
+    <row r="2" spans="1:81">
       <c r="C2" s="10" t="s">
         <v>12</v>
       </c>
@@ -810,32 +831,44 @@
       <c r="J2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="Q2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="U2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="W2" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:77">
+    <row r="3" spans="1:81">
       <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
@@ -859,7 +892,7 @@
         <v>9257</v>
       </c>
       <c r="J3" s="11">
-        <f>+S3-SUM(G3:I3)</f>
+        <f>+W3-SUM(G3:I3)</f>
         <v>18913</v>
       </c>
       <c r="K3" s="11"/>
@@ -867,22 +900,22 @@
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="11">
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11">
         <v>26277</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="U3" s="11">
         <v>27891</v>
       </c>
-      <c r="R3" s="11">
+      <c r="V3" s="11">
         <v>30359</v>
       </c>
-      <c r="S3" s="11">
+      <c r="W3" s="11">
         <v>44847</v>
       </c>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
       <c r="Z3" s="11"/>
@@ -937,8 +970,12 @@
       <c r="BW3" s="11"/>
       <c r="BX3" s="11"/>
       <c r="BY3" s="11"/>
-    </row>
-    <row r="4" spans="1:77">
+      <c r="BZ3" s="11"/>
+      <c r="CA3" s="11"/>
+      <c r="CB3" s="11"/>
+      <c r="CC3" s="11"/>
+    </row>
+    <row r="4" spans="1:81">
       <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
@@ -962,7 +999,7 @@
         <v>6695</v>
       </c>
       <c r="J4" s="11">
-        <f>+S4-SUM(G4:I4)</f>
+        <f>+W4-SUM(G4:I4)</f>
         <v>-898</v>
       </c>
       <c r="K4" s="11"/>
@@ -970,22 +1007,22 @@
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
-      <c r="P4" s="11">
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11">
         <v>6926</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="U4" s="11">
         <v>7928</v>
       </c>
-      <c r="R4" s="11">
+      <c r="V4" s="11">
         <v>21215</v>
       </c>
-      <c r="S4" s="11">
+      <c r="W4" s="11">
         <v>19040</v>
       </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
       <c r="Z4" s="11"/>
@@ -1040,8 +1077,12 @@
       <c r="BW4" s="11"/>
       <c r="BX4" s="11"/>
       <c r="BY4" s="11"/>
-    </row>
-    <row r="5" spans="1:77">
+      <c r="BZ4" s="11"/>
+      <c r="CA4" s="11"/>
+      <c r="CB4" s="11"/>
+      <c r="CC4" s="11"/>
+    </row>
+    <row r="5" spans="1:81">
       <c r="B5" s="12" t="s">
         <v>18</v>
       </c>
@@ -1071,37 +1112,39 @@
         <f>+J3+J4</f>
         <v>18015</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="13">
-        <f t="shared" ref="N5:Q5" si="0">SUM(N3:N4)</f>
+      <c r="K5" s="13">
+        <v>19311</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="13">
+        <f t="shared" ref="R5:U5" si="0">SUM(R3:R4)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="13">
+      <c r="S5" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P5" s="13">
+      <c r="T5" s="13">
         <f t="shared" si="0"/>
         <v>33203</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="U5" s="13">
         <f t="shared" si="0"/>
         <v>35819</v>
       </c>
-      <c r="R5" s="13">
-        <f>SUM(R3:R4)</f>
+      <c r="V5" s="13">
+        <f>SUM(V3:V4)</f>
         <v>51574</v>
       </c>
-      <c r="S5" s="13">
-        <f t="shared" ref="S5" si="1">SUM(S3:S4)</f>
+      <c r="W5" s="13">
+        <f t="shared" ref="W5" si="1">SUM(W3:W4)</f>
         <v>63887</v>
       </c>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
@@ -1156,8 +1199,12 @@
       <c r="BW5" s="11"/>
       <c r="BX5" s="11"/>
       <c r="BY5" s="11"/>
-    </row>
-    <row r="6" spans="1:77">
+      <c r="BZ5" s="11"/>
+      <c r="CA5" s="11"/>
+      <c r="CB5" s="11"/>
+      <c r="CC5" s="11"/>
+    </row>
+    <row r="6" spans="1:81">
       <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
@@ -1181,7 +1228,7 @@
         <v>3096</v>
       </c>
       <c r="J6" s="11">
-        <f>+S6-SUM(G6:I6)</f>
+        <f>+W6-SUM(G6:I6)</f>
         <v>3606</v>
       </c>
       <c r="K6" s="11"/>
@@ -1189,22 +1236,22 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
-      <c r="P6" s="11">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11">
         <v>7629</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="U6" s="11">
         <v>8636</v>
       </c>
-      <c r="R6" s="11">
+      <c r="V6" s="11">
         <v>9797</v>
       </c>
-      <c r="S6" s="11">
+      <c r="W6" s="11">
         <v>12115</v>
       </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
@@ -1259,8 +1306,12 @@
       <c r="BW6" s="11"/>
       <c r="BX6" s="11"/>
       <c r="BY6" s="11"/>
-    </row>
-    <row r="7" spans="1:77">
+      <c r="BZ6" s="11"/>
+      <c r="CA6" s="11"/>
+      <c r="CB6" s="11"/>
+      <c r="CC6" s="11"/>
+    </row>
+    <row r="7" spans="1:81">
       <c r="B7" s="8" t="s">
         <v>31</v>
       </c>
@@ -1284,7 +1335,7 @@
         <v>608</v>
       </c>
       <c r="J7" s="11">
-        <f>+S7-SUM(G7:I7)</f>
+        <f>+W7-SUM(G7:I7)</f>
         <v>607</v>
       </c>
       <c r="K7" s="11"/>
@@ -1292,22 +1343,22 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
-      <c r="P7" s="11">
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11">
         <v>627</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="U7" s="11">
         <v>636</v>
       </c>
-      <c r="R7" s="11">
+      <c r="V7" s="11">
         <v>2991</v>
       </c>
-      <c r="S7" s="11">
+      <c r="W7" s="11">
         <v>2371</v>
       </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
@@ -1362,8 +1413,12 @@
       <c r="BW7" s="11"/>
       <c r="BX7" s="11"/>
       <c r="BY7" s="11"/>
-    </row>
-    <row r="8" spans="1:77">
+      <c r="BZ7" s="11"/>
+      <c r="CA7" s="11"/>
+      <c r="CB7" s="11"/>
+      <c r="CC7" s="11"/>
+    </row>
+    <row r="8" spans="1:81">
       <c r="B8" s="8" t="s">
         <v>32</v>
       </c>
@@ -1393,7 +1448,7 @@
         <v>1545</v>
       </c>
       <c r="J8" s="11">
-        <f>+S8-SUM(G8:I8)</f>
+        <f>+W8-SUM(G8:I8)</f>
         <v>1553</v>
       </c>
       <c r="K8" s="11"/>
@@ -1401,26 +1456,26 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
-      <c r="P8" s="11">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11">
         <f>2847+5</f>
         <v>2852</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="U8" s="11">
         <f>1853+4</f>
         <v>1857</v>
       </c>
-      <c r="R8" s="11">
+      <c r="V8" s="11">
         <f>6023+254</f>
         <v>6277</v>
       </c>
-      <c r="S8" s="11">
+      <c r="W8" s="11">
         <f>6031+76</f>
         <v>6107</v>
       </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
@@ -1475,8 +1530,12 @@
       <c r="BW8" s="11"/>
       <c r="BX8" s="11"/>
       <c r="BY8" s="11"/>
-    </row>
-    <row r="9" spans="1:77">
+      <c r="BZ8" s="11"/>
+      <c r="CA8" s="11"/>
+      <c r="CB8" s="11"/>
+      <c r="CC8" s="11"/>
+    </row>
+    <row r="9" spans="1:81">
       <c r="B9" s="8" t="s">
         <v>33</v>
       </c>
@@ -1513,42 +1572,42 @@
         <v>12249</v>
       </c>
       <c r="K9" s="11"/>
-      <c r="L9" s="11">
-        <f t="shared" ref="L9:Q9" si="3">+L5-SUM(L6:L8)</f>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11">
+        <f t="shared" ref="P9:U9" si="3">+P5-SUM(P6:P8)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="11">
+      <c r="Q9" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="R9" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O9" s="11">
+      <c r="S9" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P9" s="11">
+      <c r="T9" s="11">
         <f t="shared" si="3"/>
         <v>22095</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="U9" s="11">
         <f t="shared" si="3"/>
         <v>24690</v>
       </c>
-      <c r="R9" s="11">
-        <f>+R5-SUM(R6:R8)</f>
+      <c r="V9" s="11">
+        <f>+V5-SUM(V6:V8)</f>
         <v>32509</v>
       </c>
-      <c r="S9" s="11">
-        <f>+S5-SUM(S6:S8)</f>
+      <c r="W9" s="11">
+        <f>+W5-SUM(W6:W8)</f>
         <v>43294</v>
       </c>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
@@ -1603,8 +1662,12 @@
       <c r="BW9" s="11"/>
       <c r="BX9" s="11"/>
       <c r="BY9" s="11"/>
-    </row>
-    <row r="10" spans="1:77">
+      <c r="BZ9" s="11"/>
+      <c r="CA9" s="11"/>
+      <c r="CB9" s="11"/>
+      <c r="CC9" s="11"/>
+    </row>
+    <row r="10" spans="1:81">
       <c r="B10" s="8" t="s">
         <v>35</v>
       </c>
@@ -1628,7 +1691,7 @@
         <v>3050</v>
       </c>
       <c r="J10" s="11">
-        <f>+S10-SUM(G10:I10)</f>
+        <f>+W10-SUM(G10:I10)</f>
         <v>2981</v>
       </c>
       <c r="K10" s="11"/>
@@ -1636,22 +1699,22 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
-      <c r="P10" s="11">
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11">
         <v>4919</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="U10" s="11">
         <v>5253</v>
       </c>
-      <c r="R10" s="11">
+      <c r="V10" s="11">
         <v>9310</v>
       </c>
-      <c r="S10" s="11">
+      <c r="W10" s="11">
         <v>10977</v>
       </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
       <c r="Z10" s="11"/>
@@ -1706,8 +1769,12 @@
       <c r="BW10" s="11"/>
       <c r="BX10" s="11"/>
       <c r="BY10" s="11"/>
-    </row>
-    <row r="11" spans="1:77">
+      <c r="BZ10" s="11"/>
+      <c r="CA10" s="11"/>
+      <c r="CB10" s="11"/>
+      <c r="CC10" s="11"/>
+    </row>
+    <row r="11" spans="1:81">
       <c r="B11" s="8" t="s">
         <v>36</v>
       </c>
@@ -1731,7 +1798,7 @@
         <v>1072</v>
       </c>
       <c r="J11" s="11">
-        <f>+S11-SUM(G11:I11)</f>
+        <f>+W11-SUM(G11:I11)</f>
         <v>1107</v>
       </c>
       <c r="K11" s="11"/>
@@ -1739,22 +1806,22 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
-      <c r="P11" s="11">
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11">
         <v>1382</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="U11" s="11">
         <v>1592</v>
       </c>
-      <c r="R11" s="11">
+      <c r="V11" s="11">
         <v>4959</v>
       </c>
-      <c r="S11" s="11">
+      <c r="W11" s="11">
         <v>4211</v>
       </c>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
       <c r="Z11" s="11"/>
@@ -1809,8 +1876,12 @@
       <c r="BW11" s="11"/>
       <c r="BX11" s="11"/>
       <c r="BY11" s="11"/>
-    </row>
-    <row r="12" spans="1:77">
+      <c r="BZ11" s="11"/>
+      <c r="CA11" s="11"/>
+      <c r="CB11" s="11"/>
+      <c r="CC11" s="11"/>
+    </row>
+    <row r="12" spans="1:81">
       <c r="B12" s="8" t="s">
         <v>37</v>
       </c>
@@ -1834,7 +1905,7 @@
         <v>507</v>
       </c>
       <c r="J12" s="11">
-        <f>+S12-SUM(G12:I12)</f>
+        <f>+W12-SUM(G12:I12)</f>
         <v>507</v>
       </c>
       <c r="K12" s="11"/>
@@ -1842,22 +1913,22 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11">
         <v>1512</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="U12" s="11">
         <v>1394</v>
       </c>
-      <c r="R12" s="11">
+      <c r="V12" s="11">
         <v>3244</v>
       </c>
-      <c r="S12" s="11">
+      <c r="W12" s="11">
         <v>2031</v>
       </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
       <c r="Z12" s="11"/>
@@ -1912,8 +1983,12 @@
       <c r="BW12" s="11"/>
       <c r="BX12" s="11"/>
       <c r="BY12" s="11"/>
-    </row>
-    <row r="13" spans="1:77">
+      <c r="BZ12" s="11"/>
+      <c r="CA12" s="11"/>
+      <c r="CB12" s="11"/>
+      <c r="CC12" s="11"/>
+    </row>
+    <row r="13" spans="1:81">
       <c r="B13" s="8" t="s">
         <v>38</v>
       </c>
@@ -1937,7 +2012,7 @@
         <v>187</v>
       </c>
       <c r="J13" s="11">
-        <f>+S13-SUM(G13:I13)</f>
+        <f>+W13-SUM(G13:I13)</f>
         <v>146</v>
       </c>
       <c r="K13" s="11"/>
@@ -1945,22 +2020,22 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="11">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11">
         <v>57</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="U13" s="11">
         <v>244</v>
       </c>
-      <c r="R13" s="11">
+      <c r="V13" s="11">
         <v>1533</v>
       </c>
-      <c r="S13" s="11">
+      <c r="W13" s="11">
         <v>591</v>
       </c>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
       <c r="Z13" s="11"/>
@@ -2015,8 +2090,12 @@
       <c r="BW13" s="11"/>
       <c r="BX13" s="11"/>
       <c r="BY13" s="11"/>
-    </row>
-    <row r="14" spans="1:77">
+      <c r="BZ13" s="11"/>
+      <c r="CA13" s="11"/>
+      <c r="CB13" s="11"/>
+      <c r="CC13" s="11"/>
+    </row>
+    <row r="14" spans="1:81">
       <c r="B14" s="8" t="s">
         <v>34</v>
       </c>
@@ -2053,42 +2132,42 @@
         <v>7508</v>
       </c>
       <c r="K14" s="11"/>
-      <c r="L14" s="11">
-        <f t="shared" ref="L14:Q14" si="5">+L9-SUM(L10:L13)</f>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11">
+        <f t="shared" ref="P14:U14" si="5">+P9-SUM(P10:P13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="11">
+      <c r="Q14" s="11">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="11">
+      <c r="R14" s="11">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="11">
+      <c r="S14" s="11">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P14" s="11">
+      <c r="T14" s="11">
         <f t="shared" si="5"/>
         <v>14225</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="U14" s="11">
         <f t="shared" si="5"/>
         <v>16207</v>
       </c>
-      <c r="R14" s="11">
-        <f>+R9-SUM(R10:R13)</f>
+      <c r="V14" s="11">
+        <f>+V9-SUM(V10:V13)</f>
         <v>13463</v>
       </c>
-      <c r="S14" s="11">
-        <f t="shared" ref="S14" si="6">+S9-SUM(S10:S13)</f>
+      <c r="W14" s="11">
+        <f t="shared" ref="W14" si="6">+W9-SUM(W10:W13)</f>
         <v>25484</v>
       </c>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
       <c r="Z14" s="11"/>
@@ -2143,8 +2222,12 @@
       <c r="BW14" s="11"/>
       <c r="BX14" s="11"/>
       <c r="BY14" s="11"/>
-    </row>
-    <row r="15" spans="1:77">
+      <c r="BZ14" s="11"/>
+      <c r="CA14" s="11"/>
+      <c r="CB14" s="11"/>
+      <c r="CC14" s="11"/>
+    </row>
+    <row r="15" spans="1:81">
       <c r="B15" s="8" t="s">
         <v>56</v>
       </c>
@@ -2170,7 +2253,7 @@
         <v>-807</v>
       </c>
       <c r="J15" s="11">
-        <f>+S15-SUM(G15:I15)</f>
+        <f>+W15-SUM(G15:I15)</f>
         <v>-864</v>
       </c>
       <c r="K15" s="11"/>
@@ -2178,22 +2261,22 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="11">
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11">
         <v>-1737</v>
       </c>
-      <c r="Q15" s="11">
+      <c r="U15" s="11">
         <v>-1622</v>
       </c>
-      <c r="R15" s="11">
+      <c r="V15" s="11">
         <v>-3953</v>
       </c>
-      <c r="S15" s="11">
+      <c r="W15" s="11">
         <v>-3210</v>
       </c>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
       <c r="Z15" s="11"/>
@@ -2248,8 +2331,12 @@
       <c r="BW15" s="11"/>
       <c r="BX15" s="11"/>
       <c r="BY15" s="11"/>
-    </row>
-    <row r="16" spans="1:77">
+      <c r="BZ15" s="11"/>
+      <c r="CA15" s="11"/>
+      <c r="CB15" s="11"/>
+      <c r="CC15" s="11"/>
+    </row>
+    <row r="16" spans="1:81">
       <c r="B16" s="8" t="s">
         <v>40</v>
       </c>
@@ -2273,7 +2360,7 @@
         <v>205</v>
       </c>
       <c r="J16" s="11">
-        <f>+S16-SUM(G16:I16)</f>
+        <f>+W16-SUM(G16:I16)</f>
         <v>225</v>
       </c>
       <c r="K16" s="11"/>
@@ -2281,22 +2368,22 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="11">
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11">
         <v>-54</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="U16" s="11">
         <v>512</v>
       </c>
-      <c r="R16" s="11">
+      <c r="V16" s="11">
         <v>406</v>
       </c>
-      <c r="S16" s="11">
+      <c r="W16" s="11">
         <v>455</v>
       </c>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
       <c r="Z16" s="11"/>
@@ -2351,8 +2438,12 @@
       <c r="BW16" s="11"/>
       <c r="BX16" s="11"/>
       <c r="BY16" s="11"/>
-    </row>
-    <row r="17" spans="2:77">
+      <c r="BZ16" s="11"/>
+      <c r="CA16" s="11"/>
+      <c r="CB16" s="11"/>
+      <c r="CC16" s="11"/>
+    </row>
+    <row r="17" spans="2:81">
       <c r="B17" s="8" t="s">
         <v>41</v>
       </c>
@@ -2389,42 +2480,42 @@
         <v>6869</v>
       </c>
       <c r="K17" s="11"/>
-      <c r="L17" s="11">
-        <f t="shared" ref="L17:Q17" si="8">+L14+SUM(L15:L16)</f>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11">
+        <f t="shared" ref="P17:U17" si="8">+P14+SUM(P15:P16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="11">
+      <c r="Q17" s="11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N17" s="11">
+      <c r="R17" s="11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O17" s="11">
+      <c r="S17" s="11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P17" s="11">
+      <c r="T17" s="11">
         <f t="shared" si="8"/>
         <v>12434</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="U17" s="11">
         <f t="shared" si="8"/>
         <v>15097</v>
       </c>
-      <c r="R17" s="11">
-        <f>+R14+SUM(R15:R16)</f>
+      <c r="V17" s="11">
+        <f>+V14+SUM(V15:V16)</f>
         <v>9916</v>
       </c>
-      <c r="S17" s="11">
-        <f t="shared" ref="S17" si="9">+S14+SUM(S15:S16)</f>
+      <c r="W17" s="11">
+        <f t="shared" ref="W17" si="9">+W14+SUM(W15:W16)</f>
         <v>22729</v>
       </c>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
@@ -2479,8 +2570,12 @@
       <c r="BW17" s="11"/>
       <c r="BX17" s="11"/>
       <c r="BY17" s="11"/>
-    </row>
-    <row r="18" spans="2:77">
+      <c r="BZ17" s="11"/>
+      <c r="CA17" s="11"/>
+      <c r="CB17" s="11"/>
+      <c r="CC17" s="11"/>
+    </row>
+    <row r="18" spans="2:81">
       <c r="B18" s="8" t="s">
         <v>42</v>
       </c>
@@ -2504,7 +2599,7 @@
         <v>1145</v>
       </c>
       <c r="J18" s="11">
-        <f>+S18-SUM(G18:I18)</f>
+        <f>+W18-SUM(G18:I18)</f>
         <v>-1649</v>
       </c>
       <c r="K18" s="11"/>
@@ -2512,22 +2607,22 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
-      <c r="P18" s="11">
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11">
         <v>939</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="U18" s="11">
         <v>1015</v>
       </c>
-      <c r="R18" s="11">
+      <c r="V18" s="11">
         <v>3748</v>
       </c>
-      <c r="S18" s="11">
+      <c r="W18" s="11">
         <v>-397</v>
       </c>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
@@ -2582,8 +2677,12 @@
       <c r="BW18" s="11"/>
       <c r="BX18" s="11"/>
       <c r="BY18" s="11"/>
-    </row>
-    <row r="19" spans="2:77">
+      <c r="BZ18" s="11"/>
+      <c r="CA18" s="11"/>
+      <c r="CB18" s="11"/>
+      <c r="CC18" s="11"/>
+    </row>
+    <row r="19" spans="2:81">
       <c r="B19" s="8" t="s">
         <v>43</v>
       </c>
@@ -2620,42 +2719,42 @@
         <v>8518</v>
       </c>
       <c r="K19" s="11"/>
-      <c r="L19" s="11">
-        <f t="shared" ref="L19:Q19" si="11">+L17-L18</f>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11">
+        <f t="shared" ref="P19:U19" si="11">+P17-P18</f>
         <v>0</v>
       </c>
-      <c r="M19" s="11">
+      <c r="Q19" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N19" s="11">
+      <c r="R19" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O19" s="11">
+      <c r="S19" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P19" s="11">
+      <c r="T19" s="11">
         <f t="shared" si="11"/>
         <v>11495</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="U19" s="11">
         <f t="shared" si="11"/>
         <v>14082</v>
       </c>
-      <c r="R19" s="11">
-        <f>+R17-R18</f>
+      <c r="V19" s="11">
+        <f>+V17-V18</f>
         <v>6168</v>
       </c>
-      <c r="S19" s="11">
-        <f t="shared" ref="S19" si="12">+S17-S18</f>
+      <c r="W19" s="11">
+        <f t="shared" ref="W19" si="12">+W17-W18</f>
         <v>23126</v>
       </c>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
       <c r="Z19" s="11"/>
@@ -2710,8 +2809,12 @@
       <c r="BW19" s="11"/>
       <c r="BX19" s="11"/>
       <c r="BY19" s="11"/>
-    </row>
-    <row r="20" spans="2:77">
+      <c r="BZ19" s="11"/>
+      <c r="CA19" s="11"/>
+      <c r="CB19" s="11"/>
+      <c r="CC19" s="11"/>
+    </row>
+    <row r="20" spans="2:81">
       <c r="B20" s="8" t="s">
         <v>44</v>
       </c>
@@ -2735,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="11">
-        <f>+S20-SUM(G20:I20)</f>
+        <f>+W20-SUM(G20:I20)</f>
         <v>0</v>
       </c>
       <c r="K20" s="11"/>
@@ -2743,22 +2846,22 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
-      <c r="P20" s="11">
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11">
         <v>272</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="U20" s="11">
         <v>0</v>
       </c>
-      <c r="R20" s="11">
+      <c r="V20" s="11">
         <v>273</v>
       </c>
-      <c r="S20" s="11">
+      <c r="W20" s="11">
         <v>0</v>
       </c>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
       <c r="Z20" s="11"/>
@@ -2813,8 +2916,12 @@
       <c r="BW20" s="11"/>
       <c r="BX20" s="11"/>
       <c r="BY20" s="11"/>
-    </row>
-    <row r="21" spans="2:77">
+      <c r="BZ20" s="11"/>
+      <c r="CA20" s="11"/>
+      <c r="CB20" s="11"/>
+      <c r="CC20" s="11"/>
+    </row>
+    <row r="21" spans="2:81">
       <c r="B21" s="8" t="s">
         <v>39</v>
       </c>
@@ -2851,42 +2958,42 @@
         <v>8518</v>
       </c>
       <c r="K21" s="11"/>
-      <c r="L21" s="11">
-        <f t="shared" ref="L21:Q21" si="15">+L19-L20</f>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11">
+        <f t="shared" ref="P21:U21" si="15">+P19-P20</f>
         <v>0</v>
       </c>
-      <c r="M21" s="11">
+      <c r="Q21" s="11">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N21" s="11">
+      <c r="R21" s="11">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O21" s="11">
+      <c r="S21" s="11">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P21" s="11">
+      <c r="T21" s="11">
         <f t="shared" si="15"/>
         <v>11223</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="U21" s="11">
         <f t="shared" si="15"/>
         <v>14082</v>
       </c>
-      <c r="R21" s="11">
-        <f>+R19-R20</f>
+      <c r="V21" s="11">
+        <f>+V19-V20</f>
         <v>5895</v>
       </c>
-      <c r="S21" s="11">
-        <f t="shared" ref="S21" si="16">+S19-S20</f>
+      <c r="W21" s="11">
+        <f t="shared" ref="W21" si="16">+W19-W20</f>
         <v>23126</v>
       </c>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
       <c r="Z21" s="11"/>
@@ -2941,8 +3048,12 @@
       <c r="BW21" s="11"/>
       <c r="BX21" s="11"/>
       <c r="BY21" s="11"/>
-    </row>
-    <row r="22" spans="2:77">
+      <c r="BZ21" s="11"/>
+      <c r="CA21" s="11"/>
+      <c r="CB21" s="11"/>
+      <c r="CC21" s="11"/>
+    </row>
+    <row r="22" spans="2:81">
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -3018,8 +3129,12 @@
       <c r="BW22" s="11"/>
       <c r="BX22" s="11"/>
       <c r="BY22" s="11"/>
-    </row>
-    <row r="23" spans="2:77">
+      <c r="BZ22" s="11"/>
+      <c r="CA22" s="11"/>
+      <c r="CB22" s="11"/>
+      <c r="CC22" s="11"/>
+    </row>
+    <row r="23" spans="2:81">
       <c r="B23" s="8" t="s">
         <v>45</v>
       </c>
@@ -3055,43 +3170,43 @@
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="14" t="e">
-        <f t="shared" ref="L23:Q23" si="19">+L21/L24</f>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="14" t="e">
+        <f t="shared" ref="P23:U23" si="19">+P21/P24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M23" s="14" t="e">
+      <c r="Q23" s="14" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N23" s="14" t="e">
+      <c r="R23" s="14" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O23" s="14" t="e">
+      <c r="S23" s="14" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P23" s="14">
+      <c r="T23" s="14">
         <f t="shared" si="19"/>
         <v>2.7446808510638299</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="U23" s="14">
         <f t="shared" si="19"/>
         <v>3.3940708604483008</v>
       </c>
-      <c r="R23" s="14">
-        <f>+R21/R24</f>
+      <c r="V23" s="14">
+        <f>+V21/V24</f>
         <v>1.2748702422145328</v>
       </c>
-      <c r="S23" s="14">
-        <f>+S21/S24</f>
+      <c r="W23" s="14">
+        <f>+W21/W24</f>
         <v>4.9078947368421053</v>
       </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
       <c r="Z23" s="11"/>
@@ -3146,8 +3261,12 @@
       <c r="BW23" s="11"/>
       <c r="BX23" s="11"/>
       <c r="BY23" s="11"/>
-    </row>
-    <row r="24" spans="2:77">
+      <c r="BZ23" s="11"/>
+      <c r="CA23" s="11"/>
+      <c r="CB23" s="11"/>
+      <c r="CC23" s="11"/>
+    </row>
+    <row r="24" spans="2:81">
       <c r="B24" s="8" t="s">
         <v>5</v>
       </c>
@@ -3176,22 +3295,22 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
-      <c r="P24" s="11">
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11">
         <v>4089</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="U24" s="11">
         <v>4149</v>
       </c>
-      <c r="R24" s="11">
+      <c r="V24" s="11">
         <v>4624</v>
       </c>
-      <c r="S24" s="11">
+      <c r="W24" s="11">
         <v>4712</v>
       </c>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
       <c r="Z24" s="11"/>
@@ -3246,8 +3365,12 @@
       <c r="BW24" s="11"/>
       <c r="BX24" s="11"/>
       <c r="BY24" s="11"/>
-    </row>
-    <row r="25" spans="2:77">
+      <c r="BZ24" s="11"/>
+      <c r="CA24" s="11"/>
+      <c r="CB24" s="11"/>
+      <c r="CC24" s="11"/>
+    </row>
+    <row r="25" spans="2:81">
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -3323,8 +3446,12 @@
       <c r="BW25" s="11"/>
       <c r="BX25" s="11"/>
       <c r="BY25" s="11"/>
-    </row>
-    <row r="26" spans="2:77">
+      <c r="BZ25" s="11"/>
+      <c r="CA25" s="11"/>
+      <c r="CB25" s="11"/>
+      <c r="CC25" s="11"/>
+    </row>
+    <row r="26" spans="2:81">
       <c r="B26" s="8" t="s">
         <v>50</v>
       </c>
@@ -3348,40 +3475,40 @@
         <f t="shared" ref="J26:J28" si="23">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="15" t="e">
-        <f t="shared" ref="M26:Q28" si="24">+M3/L3-1</f>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="15" t="e">
+        <f t="shared" ref="Q26:U28" si="24">+Q3/P3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N26" s="15" t="e">
+      <c r="R26" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="15" t="e">
+      <c r="S26" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P26" s="15" t="e">
+      <c r="T26" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q26" s="15">
+      <c r="U26" s="15">
         <f t="shared" si="24"/>
         <v>6.1422536819271567E-2</v>
       </c>
-      <c r="R26" s="15">
-        <f>+R3/Q3-1</f>
+      <c r="V26" s="15">
+        <f>+V3/U3-1</f>
         <v>8.8487325660607352E-2</v>
       </c>
-      <c r="S26" s="15">
-        <f>+S3/R3-1</f>
+      <c r="W26" s="15">
+        <f>+W3/V3-1</f>
         <v>0.47722256991337009</v>
       </c>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
       <c r="Z26" s="11"/>
@@ -3436,8 +3563,12 @@
       <c r="BW26" s="11"/>
       <c r="BX26" s="11"/>
       <c r="BY26" s="11"/>
-    </row>
-    <row r="27" spans="2:77">
+      <c r="BZ26" s="11"/>
+      <c r="CA26" s="11"/>
+      <c r="CB26" s="11"/>
+      <c r="CC26" s="11"/>
+    </row>
+    <row r="27" spans="2:81">
       <c r="B27" s="8" t="s">
         <v>51</v>
       </c>
@@ -3461,40 +3592,40 @@
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="15" t="e">
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N27" s="15" t="e">
+      <c r="R27" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="15" t="e">
+      <c r="S27" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P27" s="15" t="e">
+      <c r="T27" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="U27" s="15">
         <f t="shared" si="24"/>
         <v>0.14467224949465773</v>
       </c>
-      <c r="R27" s="15">
-        <f t="shared" ref="R27:S28" si="25">+R4/Q4-1</f>
+      <c r="V27" s="15">
+        <f t="shared" ref="V27:W28" si="25">+V4/U4-1</f>
         <v>1.6759586276488396</v>
       </c>
-      <c r="S27" s="15">
+      <c r="W27" s="15">
         <f t="shared" si="25"/>
         <v>-0.10252180061277394</v>
       </c>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
       <c r="Z27" s="11"/>
@@ -3549,8 +3680,12 @@
       <c r="BW27" s="11"/>
       <c r="BX27" s="11"/>
       <c r="BY27" s="11"/>
-    </row>
-    <row r="28" spans="2:77">
+      <c r="BZ27" s="11"/>
+      <c r="CA27" s="11"/>
+      <c r="CB27" s="11"/>
+      <c r="CC27" s="11"/>
+    </row>
+    <row r="28" spans="2:81">
       <c r="B28" s="12" t="s">
         <v>46</v>
       </c>
@@ -3574,45 +3709,45 @@
         <f t="shared" si="23"/>
         <v>0.2818414686210331</v>
       </c>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="16" t="e">
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="16" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N28" s="16" t="e">
+      <c r="R28" s="16" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="16" t="e">
+      <c r="S28" s="16" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="16" t="e">
+      <c r="T28" s="16" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="U28" s="16">
         <f t="shared" si="24"/>
         <v>7.8788061319760239E-2</v>
       </c>
-      <c r="R28" s="16">
+      <c r="V28" s="16">
         <f t="shared" si="25"/>
         <v>0.43985035874815037</v>
       </c>
-      <c r="S28" s="16">
+      <c r="W28" s="16">
         <f t="shared" si="25"/>
         <v>0.23874432853763516</v>
       </c>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
       <c r="AC28" s="11"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
@@ -3662,8 +3797,12 @@
       <c r="BW28" s="11"/>
       <c r="BX28" s="11"/>
       <c r="BY28" s="11"/>
-    </row>
-    <row r="29" spans="2:77">
+      <c r="BZ28" s="11"/>
+      <c r="CA28" s="11"/>
+      <c r="CB28" s="11"/>
+      <c r="CC28" s="11"/>
+    </row>
+    <row r="29" spans="2:81">
       <c r="B29" s="8" t="s">
         <v>47</v>
       </c>
@@ -3699,43 +3838,43 @@
         <f t="shared" si="27"/>
         <v>0.6799333888426311</v>
       </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="15" t="e">
-        <f t="shared" ref="L29:Q29" si="28">+L9/L5</f>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="15" t="e">
+        <f t="shared" ref="P29:U29" si="28">+P9/P5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M29" s="15" t="e">
+      <c r="Q29" s="15" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" s="15" t="e">
+      <c r="R29" s="15" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="15" t="e">
+      <c r="S29" s="15" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P29" s="15">
+      <c r="T29" s="15">
         <f t="shared" si="28"/>
         <v>0.66545191699545225</v>
       </c>
-      <c r="Q29" s="15">
+      <c r="U29" s="15">
         <f t="shared" si="28"/>
         <v>0.68929897540411511</v>
       </c>
-      <c r="R29" s="15">
-        <f>+R9/R5</f>
+      <c r="V29" s="15">
+        <f>+V9/V5</f>
         <v>0.63033699150734868</v>
       </c>
-      <c r="S29" s="15">
-        <f>+S9/S5</f>
+      <c r="W29" s="15">
+        <f>+W9/W5</f>
         <v>0.67766525271181932</v>
       </c>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
@@ -3790,8 +3929,12 @@
       <c r="BW29" s="11"/>
       <c r="BX29" s="11"/>
       <c r="BY29" s="11"/>
-    </row>
-    <row r="30" spans="2:77">
+      <c r="BZ29" s="11"/>
+      <c r="CA29" s="11"/>
+      <c r="CB29" s="11"/>
+      <c r="CC29" s="11"/>
+    </row>
+    <row r="30" spans="2:81">
       <c r="B30" s="8" t="s">
         <v>48</v>
       </c>
@@ -3827,43 +3970,43 @@
         <f t="shared" si="30"/>
         <v>0.41676380793782958</v>
       </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="15" t="e">
-        <f t="shared" ref="L30:Q30" si="31">+L14/L5</f>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="15" t="e">
+        <f t="shared" ref="P30:U30" si="31">+P14/P5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="15" t="e">
+      <c r="Q30" s="15" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N30" s="15" t="e">
+      <c r="R30" s="15" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="15" t="e">
+      <c r="S30" s="15" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P30" s="15">
+      <c r="T30" s="15">
         <f t="shared" si="31"/>
         <v>0.42842514230641809</v>
       </c>
-      <c r="Q30" s="15">
+      <c r="U30" s="15">
         <f t="shared" si="31"/>
         <v>0.45246935983695802</v>
       </c>
-      <c r="R30" s="15">
-        <f>+R14/R5</f>
+      <c r="V30" s="15">
+        <f>+V14/V5</f>
         <v>0.26104238569822003</v>
       </c>
-      <c r="S30" s="15">
-        <f>+S14/S5</f>
+      <c r="W30" s="15">
+        <f>+W14/W5</f>
         <v>0.39889179332258518</v>
       </c>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
       <c r="X30" s="11"/>
       <c r="Y30" s="11"/>
       <c r="Z30" s="11"/>
@@ -3918,8 +4061,12 @@
       <c r="BW30" s="11"/>
       <c r="BX30" s="11"/>
       <c r="BY30" s="11"/>
-    </row>
-    <row r="31" spans="2:77">
+      <c r="BZ30" s="11"/>
+      <c r="CA30" s="11"/>
+      <c r="CB30" s="11"/>
+      <c r="CC30" s="11"/>
+    </row>
+    <row r="31" spans="2:81">
       <c r="B31" s="8" t="s">
         <v>49</v>
       </c>
@@ -3955,43 +4102,43 @@
         <f t="shared" si="33"/>
         <v>-0.24006405590333382</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="15" t="e">
-        <f t="shared" ref="L31:Q31" si="34">+L18/L17</f>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="15" t="e">
+        <f t="shared" ref="P31:U31" si="34">+P18/P17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M31" s="15" t="e">
+      <c r="Q31" s="15" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="15" t="e">
+      <c r="R31" s="15" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="15" t="e">
+      <c r="S31" s="15" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P31" s="15">
+      <c r="T31" s="15">
         <f t="shared" si="34"/>
         <v>7.5518738941611707E-2</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="U31" s="15">
         <f t="shared" si="34"/>
         <v>6.7231900377558454E-2</v>
       </c>
-      <c r="R31" s="15">
-        <f>+R18/R17</f>
+      <c r="V31" s="15">
+        <f>+V18/V17</f>
         <v>0.37797498991528844</v>
       </c>
-      <c r="S31" s="15">
-        <f>+S18/S17</f>
+      <c r="W31" s="15">
+        <f>+W18/W17</f>
         <v>-1.7466672532887501E-2</v>
       </c>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="11"/>
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
       <c r="Z31" s="11"/>
@@ -4046,8 +4193,12 @@
       <c r="BW31" s="11"/>
       <c r="BX31" s="11"/>
       <c r="BY31" s="11"/>
-    </row>
-    <row r="32" spans="2:77">
+      <c r="BZ31" s="11"/>
+      <c r="CA31" s="11"/>
+      <c r="CB31" s="11"/>
+      <c r="CC31" s="11"/>
+    </row>
+    <row r="32" spans="2:81">
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -4123,8 +4274,12 @@
       <c r="BW32" s="11"/>
       <c r="BX32" s="11"/>
       <c r="BY32" s="11"/>
-    </row>
-    <row r="33" spans="3:77">
+      <c r="BZ32" s="11"/>
+      <c r="CA32" s="11"/>
+      <c r="CB32" s="11"/>
+      <c r="CC32" s="11"/>
+    </row>
+    <row r="33" spans="3:81">
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
@@ -4200,8 +4355,12 @@
       <c r="BW33" s="11"/>
       <c r="BX33" s="11"/>
       <c r="BY33" s="11"/>
-    </row>
-    <row r="34" spans="3:77">
+      <c r="BZ33" s="11"/>
+      <c r="CA33" s="11"/>
+      <c r="CB33" s="11"/>
+      <c r="CC33" s="11"/>
+    </row>
+    <row r="34" spans="3:81">
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -4277,8 +4436,12 @@
       <c r="BW34" s="11"/>
       <c r="BX34" s="11"/>
       <c r="BY34" s="11"/>
-    </row>
-    <row r="35" spans="3:77">
+      <c r="BZ34" s="11"/>
+      <c r="CA34" s="11"/>
+      <c r="CB34" s="11"/>
+      <c r="CC34" s="11"/>
+    </row>
+    <row r="35" spans="3:81">
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
@@ -4354,8 +4517,12 @@
       <c r="BW35" s="11"/>
       <c r="BX35" s="11"/>
       <c r="BY35" s="11"/>
-    </row>
-    <row r="36" spans="3:77">
+      <c r="BZ35" s="11"/>
+      <c r="CA35" s="11"/>
+      <c r="CB35" s="11"/>
+      <c r="CC35" s="11"/>
+    </row>
+    <row r="36" spans="3:81">
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -4431,8 +4598,12 @@
       <c r="BW36" s="11"/>
       <c r="BX36" s="11"/>
       <c r="BY36" s="11"/>
-    </row>
-    <row r="37" spans="3:77">
+      <c r="BZ36" s="11"/>
+      <c r="CA36" s="11"/>
+      <c r="CB36" s="11"/>
+      <c r="CC36" s="11"/>
+    </row>
+    <row r="37" spans="3:81">
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -4508,8 +4679,12 @@
       <c r="BW37" s="11"/>
       <c r="BX37" s="11"/>
       <c r="BY37" s="11"/>
-    </row>
-    <row r="38" spans="3:77">
+      <c r="BZ37" s="11"/>
+      <c r="CA37" s="11"/>
+      <c r="CB37" s="11"/>
+      <c r="CC37" s="11"/>
+    </row>
+    <row r="38" spans="3:81">
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -4585,8 +4760,12 @@
       <c r="BW38" s="11"/>
       <c r="BX38" s="11"/>
       <c r="BY38" s="11"/>
-    </row>
-    <row r="39" spans="3:77">
+      <c r="BZ38" s="11"/>
+      <c r="CA38" s="11"/>
+      <c r="CB38" s="11"/>
+      <c r="CC38" s="11"/>
+    </row>
+    <row r="39" spans="3:81">
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
@@ -4662,8 +4841,12 @@
       <c r="BW39" s="11"/>
       <c r="BX39" s="11"/>
       <c r="BY39" s="11"/>
-    </row>
-    <row r="40" spans="3:77">
+      <c r="BZ39" s="11"/>
+      <c r="CA39" s="11"/>
+      <c r="CB39" s="11"/>
+      <c r="CC39" s="11"/>
+    </row>
+    <row r="40" spans="3:81">
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -4739,8 +4922,12 @@
       <c r="BW40" s="11"/>
       <c r="BX40" s="11"/>
       <c r="BY40" s="11"/>
-    </row>
-    <row r="41" spans="3:77">
+      <c r="BZ40" s="11"/>
+      <c r="CA40" s="11"/>
+      <c r="CB40" s="11"/>
+      <c r="CC40" s="11"/>
+    </row>
+    <row r="41" spans="3:81">
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
@@ -4816,8 +5003,12 @@
       <c r="BW41" s="11"/>
       <c r="BX41" s="11"/>
       <c r="BY41" s="11"/>
-    </row>
-    <row r="42" spans="3:77">
+      <c r="BZ41" s="11"/>
+      <c r="CA41" s="11"/>
+      <c r="CB41" s="11"/>
+      <c r="CC41" s="11"/>
+    </row>
+    <row r="42" spans="3:81">
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -4893,8 +5084,12 @@
       <c r="BW42" s="11"/>
       <c r="BX42" s="11"/>
       <c r="BY42" s="11"/>
-    </row>
-    <row r="43" spans="3:77">
+      <c r="BZ42" s="11"/>
+      <c r="CA42" s="11"/>
+      <c r="CB42" s="11"/>
+      <c r="CC42" s="11"/>
+    </row>
+    <row r="43" spans="3:81">
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -4970,8 +5165,12 @@
       <c r="BW43" s="11"/>
       <c r="BX43" s="11"/>
       <c r="BY43" s="11"/>
-    </row>
-    <row r="44" spans="3:77">
+      <c r="BZ43" s="11"/>
+      <c r="CA43" s="11"/>
+      <c r="CB43" s="11"/>
+      <c r="CC43" s="11"/>
+    </row>
+    <row r="44" spans="3:81">
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -5047,8 +5246,12 @@
       <c r="BW44" s="11"/>
       <c r="BX44" s="11"/>
       <c r="BY44" s="11"/>
-    </row>
-    <row r="45" spans="3:77">
+      <c r="BZ44" s="11"/>
+      <c r="CA44" s="11"/>
+      <c r="CB44" s="11"/>
+      <c r="CC44" s="11"/>
+    </row>
+    <row r="45" spans="3:81">
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
@@ -5124,8 +5327,12 @@
       <c r="BW45" s="11"/>
       <c r="BX45" s="11"/>
       <c r="BY45" s="11"/>
-    </row>
-    <row r="46" spans="3:77">
+      <c r="BZ45" s="11"/>
+      <c r="CA45" s="11"/>
+      <c r="CB45" s="11"/>
+      <c r="CC45" s="11"/>
+    </row>
+    <row r="46" spans="3:81">
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -5201,8 +5408,12 @@
       <c r="BW46" s="11"/>
       <c r="BX46" s="11"/>
       <c r="BY46" s="11"/>
-    </row>
-    <row r="47" spans="3:77">
+      <c r="BZ46" s="11"/>
+      <c r="CA46" s="11"/>
+      <c r="CB46" s="11"/>
+      <c r="CC46" s="11"/>
+    </row>
+    <row r="47" spans="3:81">
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
@@ -5278,8 +5489,12 @@
       <c r="BW47" s="11"/>
       <c r="BX47" s="11"/>
       <c r="BY47" s="11"/>
-    </row>
-    <row r="48" spans="3:77">
+      <c r="BZ47" s="11"/>
+      <c r="CA47" s="11"/>
+      <c r="CB47" s="11"/>
+      <c r="CC47" s="11"/>
+    </row>
+    <row r="48" spans="3:81">
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
@@ -5355,8 +5570,12 @@
       <c r="BW48" s="11"/>
       <c r="BX48" s="11"/>
       <c r="BY48" s="11"/>
-    </row>
-    <row r="49" spans="3:77">
+      <c r="BZ48" s="11"/>
+      <c r="CA48" s="11"/>
+      <c r="CB48" s="11"/>
+      <c r="CC48" s="11"/>
+    </row>
+    <row r="49" spans="3:81">
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
@@ -5432,8 +5651,12 @@
       <c r="BW49" s="11"/>
       <c r="BX49" s="11"/>
       <c r="BY49" s="11"/>
-    </row>
-    <row r="50" spans="3:77">
+      <c r="BZ49" s="11"/>
+      <c r="CA49" s="11"/>
+      <c r="CB49" s="11"/>
+      <c r="CC49" s="11"/>
+    </row>
+    <row r="50" spans="3:81">
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
@@ -5509,8 +5732,12 @@
       <c r="BW50" s="11"/>
       <c r="BX50" s="11"/>
       <c r="BY50" s="11"/>
-    </row>
-    <row r="51" spans="3:77">
+      <c r="BZ50" s="11"/>
+      <c r="CA50" s="11"/>
+      <c r="CB50" s="11"/>
+      <c r="CC50" s="11"/>
+    </row>
+    <row r="51" spans="3:81">
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
@@ -5586,8 +5813,12 @@
       <c r="BW51" s="11"/>
       <c r="BX51" s="11"/>
       <c r="BY51" s="11"/>
-    </row>
-    <row r="52" spans="3:77">
+      <c r="BZ51" s="11"/>
+      <c r="CA51" s="11"/>
+      <c r="CB51" s="11"/>
+      <c r="CC51" s="11"/>
+    </row>
+    <row r="52" spans="3:81">
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
@@ -5663,8 +5894,12 @@
       <c r="BW52" s="11"/>
       <c r="BX52" s="11"/>
       <c r="BY52" s="11"/>
-    </row>
-    <row r="53" spans="3:77">
+      <c r="BZ52" s="11"/>
+      <c r="CA52" s="11"/>
+      <c r="CB52" s="11"/>
+      <c r="CC52" s="11"/>
+    </row>
+    <row r="53" spans="3:81">
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
@@ -5740,8 +5975,12 @@
       <c r="BW53" s="11"/>
       <c r="BX53" s="11"/>
       <c r="BY53" s="11"/>
-    </row>
-    <row r="54" spans="3:77">
+      <c r="BZ53" s="11"/>
+      <c r="CA53" s="11"/>
+      <c r="CB53" s="11"/>
+      <c r="CC53" s="11"/>
+    </row>
+    <row r="54" spans="3:81">
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
@@ -5817,8 +6056,12 @@
       <c r="BW54" s="11"/>
       <c r="BX54" s="11"/>
       <c r="BY54" s="11"/>
-    </row>
-    <row r="55" spans="3:77">
+      <c r="BZ54" s="11"/>
+      <c r="CA54" s="11"/>
+      <c r="CB54" s="11"/>
+      <c r="CC54" s="11"/>
+    </row>
+    <row r="55" spans="3:81">
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
@@ -5894,8 +6137,12 @@
       <c r="BW55" s="11"/>
       <c r="BX55" s="11"/>
       <c r="BY55" s="11"/>
-    </row>
-    <row r="56" spans="3:77">
+      <c r="BZ55" s="11"/>
+      <c r="CA55" s="11"/>
+      <c r="CB55" s="11"/>
+      <c r="CC55" s="11"/>
+    </row>
+    <row r="56" spans="3:81">
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5971,8 +6218,12 @@
       <c r="BW56" s="11"/>
       <c r="BX56" s="11"/>
       <c r="BY56" s="11"/>
-    </row>
-    <row r="57" spans="3:77">
+      <c r="BZ56" s="11"/>
+      <c r="CA56" s="11"/>
+      <c r="CB56" s="11"/>
+      <c r="CC56" s="11"/>
+    </row>
+    <row r="57" spans="3:81">
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
@@ -6048,8 +6299,12 @@
       <c r="BW57" s="11"/>
       <c r="BX57" s="11"/>
       <c r="BY57" s="11"/>
-    </row>
-    <row r="58" spans="3:77">
+      <c r="BZ57" s="11"/>
+      <c r="CA57" s="11"/>
+      <c r="CB57" s="11"/>
+      <c r="CC57" s="11"/>
+    </row>
+    <row r="58" spans="3:81">
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
@@ -6125,8 +6380,12 @@
       <c r="BW58" s="11"/>
       <c r="BX58" s="11"/>
       <c r="BY58" s="11"/>
-    </row>
-    <row r="59" spans="3:77">
+      <c r="BZ58" s="11"/>
+      <c r="CA58" s="11"/>
+      <c r="CB58" s="11"/>
+      <c r="CC58" s="11"/>
+    </row>
+    <row r="59" spans="3:81">
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
@@ -6202,8 +6461,12 @@
       <c r="BW59" s="11"/>
       <c r="BX59" s="11"/>
       <c r="BY59" s="11"/>
-    </row>
-    <row r="60" spans="3:77">
+      <c r="BZ59" s="11"/>
+      <c r="CA59" s="11"/>
+      <c r="CB59" s="11"/>
+      <c r="CC59" s="11"/>
+    </row>
+    <row r="60" spans="3:81">
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
@@ -6279,8 +6542,12 @@
       <c r="BW60" s="11"/>
       <c r="BX60" s="11"/>
       <c r="BY60" s="11"/>
-    </row>
-    <row r="61" spans="3:77">
+      <c r="BZ60" s="11"/>
+      <c r="CA60" s="11"/>
+      <c r="CB60" s="11"/>
+      <c r="CC60" s="11"/>
+    </row>
+    <row r="61" spans="3:81">
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
       <c r="E61" s="11"/>
@@ -6356,8 +6623,12 @@
       <c r="BW61" s="11"/>
       <c r="BX61" s="11"/>
       <c r="BY61" s="11"/>
-    </row>
-    <row r="62" spans="3:77">
+      <c r="BZ61" s="11"/>
+      <c r="CA61" s="11"/>
+      <c r="CB61" s="11"/>
+      <c r="CC61" s="11"/>
+    </row>
+    <row r="62" spans="3:81">
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
@@ -6433,8 +6704,12 @@
       <c r="BW62" s="11"/>
       <c r="BX62" s="11"/>
       <c r="BY62" s="11"/>
-    </row>
-    <row r="63" spans="3:77">
+      <c r="BZ62" s="11"/>
+      <c r="CA62" s="11"/>
+      <c r="CB62" s="11"/>
+      <c r="CC62" s="11"/>
+    </row>
+    <row r="63" spans="3:81">
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
@@ -6510,8 +6785,12 @@
       <c r="BW63" s="11"/>
       <c r="BX63" s="11"/>
       <c r="BY63" s="11"/>
-    </row>
-    <row r="64" spans="3:77">
+      <c r="BZ63" s="11"/>
+      <c r="CA63" s="11"/>
+      <c r="CB63" s="11"/>
+      <c r="CC63" s="11"/>
+    </row>
+    <row r="64" spans="3:81">
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
@@ -6587,8 +6866,12 @@
       <c r="BW64" s="11"/>
       <c r="BX64" s="11"/>
       <c r="BY64" s="11"/>
-    </row>
-    <row r="65" spans="3:77">
+      <c r="BZ64" s="11"/>
+      <c r="CA64" s="11"/>
+      <c r="CB64" s="11"/>
+      <c r="CC64" s="11"/>
+    </row>
+    <row r="65" spans="3:81">
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
       <c r="E65" s="11"/>
@@ -6664,8 +6947,12 @@
       <c r="BW65" s="11"/>
       <c r="BX65" s="11"/>
       <c r="BY65" s="11"/>
-    </row>
-    <row r="66" spans="3:77">
+      <c r="BZ65" s="11"/>
+      <c r="CA65" s="11"/>
+      <c r="CB65" s="11"/>
+      <c r="CC65" s="11"/>
+    </row>
+    <row r="66" spans="3:81">
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
@@ -6741,8 +7028,12 @@
       <c r="BW66" s="11"/>
       <c r="BX66" s="11"/>
       <c r="BY66" s="11"/>
-    </row>
-    <row r="67" spans="3:77">
+      <c r="BZ66" s="11"/>
+      <c r="CA66" s="11"/>
+      <c r="CB66" s="11"/>
+      <c r="CC66" s="11"/>
+    </row>
+    <row r="67" spans="3:81">
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6818,8 +7109,12 @@
       <c r="BW67" s="11"/>
       <c r="BX67" s="11"/>
       <c r="BY67" s="11"/>
-    </row>
-    <row r="68" spans="3:77">
+      <c r="BZ67" s="11"/>
+      <c r="CA67" s="11"/>
+      <c r="CB67" s="11"/>
+      <c r="CC67" s="11"/>
+    </row>
+    <row r="68" spans="3:81">
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
@@ -6895,8 +7190,12 @@
       <c r="BW68" s="11"/>
       <c r="BX68" s="11"/>
       <c r="BY68" s="11"/>
-    </row>
-    <row r="69" spans="3:77">
+      <c r="BZ68" s="11"/>
+      <c r="CA68" s="11"/>
+      <c r="CB68" s="11"/>
+      <c r="CC68" s="11"/>
+    </row>
+    <row r="69" spans="3:81">
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
@@ -6972,8 +7271,12 @@
       <c r="BW69" s="11"/>
       <c r="BX69" s="11"/>
       <c r="BY69" s="11"/>
-    </row>
-    <row r="70" spans="3:77">
+      <c r="BZ69" s="11"/>
+      <c r="CA69" s="11"/>
+      <c r="CB69" s="11"/>
+      <c r="CC69" s="11"/>
+    </row>
+    <row r="70" spans="3:81">
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -7049,8 +7352,12 @@
       <c r="BW70" s="11"/>
       <c r="BX70" s="11"/>
       <c r="BY70" s="11"/>
-    </row>
-    <row r="71" spans="3:77">
+      <c r="BZ70" s="11"/>
+      <c r="CA70" s="11"/>
+      <c r="CB70" s="11"/>
+      <c r="CC70" s="11"/>
+    </row>
+    <row r="71" spans="3:81">
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
@@ -7126,8 +7433,12 @@
       <c r="BW71" s="11"/>
       <c r="BX71" s="11"/>
       <c r="BY71" s="11"/>
-    </row>
-    <row r="72" spans="3:77">
+      <c r="BZ71" s="11"/>
+      <c r="CA71" s="11"/>
+      <c r="CB71" s="11"/>
+      <c r="CC71" s="11"/>
+    </row>
+    <row r="72" spans="3:81">
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
@@ -7203,8 +7514,12 @@
       <c r="BW72" s="11"/>
       <c r="BX72" s="11"/>
       <c r="BY72" s="11"/>
-    </row>
-    <row r="73" spans="3:77">
+      <c r="BZ72" s="11"/>
+      <c r="CA72" s="11"/>
+      <c r="CB72" s="11"/>
+      <c r="CC72" s="11"/>
+    </row>
+    <row r="73" spans="3:81">
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
@@ -7280,8 +7595,12 @@
       <c r="BW73" s="11"/>
       <c r="BX73" s="11"/>
       <c r="BY73" s="11"/>
-    </row>
-    <row r="74" spans="3:77">
+      <c r="BZ73" s="11"/>
+      <c r="CA73" s="11"/>
+      <c r="CB73" s="11"/>
+      <c r="CC73" s="11"/>
+    </row>
+    <row r="74" spans="3:81">
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
@@ -7357,8 +7676,12 @@
       <c r="BW74" s="11"/>
       <c r="BX74" s="11"/>
       <c r="BY74" s="11"/>
-    </row>
-    <row r="75" spans="3:77">
+      <c r="BZ74" s="11"/>
+      <c r="CA74" s="11"/>
+      <c r="CB74" s="11"/>
+      <c r="CC74" s="11"/>
+    </row>
+    <row r="75" spans="3:81">
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
@@ -7434,8 +7757,12 @@
       <c r="BW75" s="11"/>
       <c r="BX75" s="11"/>
       <c r="BY75" s="11"/>
-    </row>
-    <row r="76" spans="3:77">
+      <c r="BZ75" s="11"/>
+      <c r="CA75" s="11"/>
+      <c r="CB75" s="11"/>
+      <c r="CC75" s="11"/>
+    </row>
+    <row r="76" spans="3:81">
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
@@ -7511,8 +7838,12 @@
       <c r="BW76" s="11"/>
       <c r="BX76" s="11"/>
       <c r="BY76" s="11"/>
-    </row>
-    <row r="77" spans="3:77">
+      <c r="BZ76" s="11"/>
+      <c r="CA76" s="11"/>
+      <c r="CB76" s="11"/>
+      <c r="CC76" s="11"/>
+    </row>
+    <row r="77" spans="3:81">
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
@@ -7588,8 +7919,12 @@
       <c r="BW77" s="11"/>
       <c r="BX77" s="11"/>
       <c r="BY77" s="11"/>
-    </row>
-    <row r="78" spans="3:77">
+      <c r="BZ77" s="11"/>
+      <c r="CA77" s="11"/>
+      <c r="CB77" s="11"/>
+      <c r="CC77" s="11"/>
+    </row>
+    <row r="78" spans="3:81">
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
@@ -7665,8 +8000,12 @@
       <c r="BW78" s="11"/>
       <c r="BX78" s="11"/>
       <c r="BY78" s="11"/>
-    </row>
-    <row r="79" spans="3:77">
+      <c r="BZ78" s="11"/>
+      <c r="CA78" s="11"/>
+      <c r="CB78" s="11"/>
+      <c r="CC78" s="11"/>
+    </row>
+    <row r="79" spans="3:81">
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
@@ -7742,8 +8081,12 @@
       <c r="BW79" s="11"/>
       <c r="BX79" s="11"/>
       <c r="BY79" s="11"/>
-    </row>
-    <row r="80" spans="3:77">
+      <c r="BZ79" s="11"/>
+      <c r="CA79" s="11"/>
+      <c r="CB79" s="11"/>
+      <c r="CC79" s="11"/>
+    </row>
+    <row r="80" spans="3:81">
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
@@ -7819,8 +8162,12 @@
       <c r="BW80" s="11"/>
       <c r="BX80" s="11"/>
       <c r="BY80" s="11"/>
-    </row>
-    <row r="81" spans="3:77">
+      <c r="BZ80" s="11"/>
+      <c r="CA80" s="11"/>
+      <c r="CB80" s="11"/>
+      <c r="CC80" s="11"/>
+    </row>
+    <row r="81" spans="3:81">
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -7896,8 +8243,12 @@
       <c r="BW81" s="11"/>
       <c r="BX81" s="11"/>
       <c r="BY81" s="11"/>
-    </row>
-    <row r="82" spans="3:77">
+      <c r="BZ81" s="11"/>
+      <c r="CA81" s="11"/>
+      <c r="CB81" s="11"/>
+      <c r="CC81" s="11"/>
+    </row>
+    <row r="82" spans="3:81">
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
@@ -7973,8 +8324,12 @@
       <c r="BW82" s="11"/>
       <c r="BX82" s="11"/>
       <c r="BY82" s="11"/>
-    </row>
-    <row r="83" spans="3:77">
+      <c r="BZ82" s="11"/>
+      <c r="CA82" s="11"/>
+      <c r="CB82" s="11"/>
+      <c r="CC82" s="11"/>
+    </row>
+    <row r="83" spans="3:81">
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
       <c r="E83" s="11"/>
@@ -8050,8 +8405,12 @@
       <c r="BW83" s="11"/>
       <c r="BX83" s="11"/>
       <c r="BY83" s="11"/>
-    </row>
-    <row r="84" spans="3:77">
+      <c r="BZ83" s="11"/>
+      <c r="CA83" s="11"/>
+      <c r="CB83" s="11"/>
+      <c r="CC83" s="11"/>
+    </row>
+    <row r="84" spans="3:81">
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
@@ -8127,8 +8486,12 @@
       <c r="BW84" s="11"/>
       <c r="BX84" s="11"/>
       <c r="BY84" s="11"/>
-    </row>
-    <row r="85" spans="3:77">
+      <c r="BZ84" s="11"/>
+      <c r="CA84" s="11"/>
+      <c r="CB84" s="11"/>
+      <c r="CC84" s="11"/>
+    </row>
+    <row r="85" spans="3:81">
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
@@ -8204,8 +8567,12 @@
       <c r="BW85" s="11"/>
       <c r="BX85" s="11"/>
       <c r="BY85" s="11"/>
-    </row>
-    <row r="86" spans="3:77">
+      <c r="BZ85" s="11"/>
+      <c r="CA85" s="11"/>
+      <c r="CB85" s="11"/>
+      <c r="CC85" s="11"/>
+    </row>
+    <row r="86" spans="3:81">
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
@@ -8281,8 +8648,12 @@
       <c r="BW86" s="11"/>
       <c r="BX86" s="11"/>
       <c r="BY86" s="11"/>
-    </row>
-    <row r="87" spans="3:77">
+      <c r="BZ86" s="11"/>
+      <c r="CA86" s="11"/>
+      <c r="CB86" s="11"/>
+      <c r="CC86" s="11"/>
+    </row>
+    <row r="87" spans="3:81">
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
       <c r="E87" s="11"/>
@@ -8358,8 +8729,12 @@
       <c r="BW87" s="11"/>
       <c r="BX87" s="11"/>
       <c r="BY87" s="11"/>
-    </row>
-    <row r="88" spans="3:77">
+      <c r="BZ87" s="11"/>
+      <c r="CA87" s="11"/>
+      <c r="CB87" s="11"/>
+      <c r="CC87" s="11"/>
+    </row>
+    <row r="88" spans="3:81">
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
@@ -8435,8 +8810,12 @@
       <c r="BW88" s="11"/>
       <c r="BX88" s="11"/>
       <c r="BY88" s="11"/>
-    </row>
-    <row r="89" spans="3:77">
+      <c r="BZ88" s="11"/>
+      <c r="CA88" s="11"/>
+      <c r="CB88" s="11"/>
+      <c r="CC88" s="11"/>
+    </row>
+    <row r="89" spans="3:81">
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
@@ -8512,8 +8891,12 @@
       <c r="BW89" s="11"/>
       <c r="BX89" s="11"/>
       <c r="BY89" s="11"/>
-    </row>
-    <row r="90" spans="3:77">
+      <c r="BZ89" s="11"/>
+      <c r="CA89" s="11"/>
+      <c r="CB89" s="11"/>
+      <c r="CC89" s="11"/>
+    </row>
+    <row r="90" spans="3:81">
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
       <c r="E90" s="11"/>
@@ -8589,8 +8972,12 @@
       <c r="BW90" s="11"/>
       <c r="BX90" s="11"/>
       <c r="BY90" s="11"/>
-    </row>
-    <row r="91" spans="3:77">
+      <c r="BZ90" s="11"/>
+      <c r="CA90" s="11"/>
+      <c r="CB90" s="11"/>
+      <c r="CC90" s="11"/>
+    </row>
+    <row r="91" spans="3:81">
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
@@ -8666,8 +9053,12 @@
       <c r="BW91" s="11"/>
       <c r="BX91" s="11"/>
       <c r="BY91" s="11"/>
-    </row>
-    <row r="92" spans="3:77">
+      <c r="BZ91" s="11"/>
+      <c r="CA91" s="11"/>
+      <c r="CB91" s="11"/>
+      <c r="CC91" s="11"/>
+    </row>
+    <row r="92" spans="3:81">
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -8743,8 +9134,12 @@
       <c r="BW92" s="11"/>
       <c r="BX92" s="11"/>
       <c r="BY92" s="11"/>
-    </row>
-    <row r="93" spans="3:77">
+      <c r="BZ92" s="11"/>
+      <c r="CA92" s="11"/>
+      <c r="CB92" s="11"/>
+      <c r="CC92" s="11"/>
+    </row>
+    <row r="93" spans="3:81">
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
       <c r="E93" s="11"/>
@@ -8820,8 +9215,12 @@
       <c r="BW93" s="11"/>
       <c r="BX93" s="11"/>
       <c r="BY93" s="11"/>
-    </row>
-    <row r="94" spans="3:77">
+      <c r="BZ93" s="11"/>
+      <c r="CA93" s="11"/>
+      <c r="CB93" s="11"/>
+      <c r="CC93" s="11"/>
+    </row>
+    <row r="94" spans="3:81">
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -8897,8 +9296,12 @@
       <c r="BW94" s="11"/>
       <c r="BX94" s="11"/>
       <c r="BY94" s="11"/>
-    </row>
-    <row r="95" spans="3:77">
+      <c r="BZ94" s="11"/>
+      <c r="CA94" s="11"/>
+      <c r="CB94" s="11"/>
+      <c r="CC94" s="11"/>
+    </row>
+    <row r="95" spans="3:81">
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
       <c r="E95" s="11"/>
@@ -8974,8 +9377,12 @@
       <c r="BW95" s="11"/>
       <c r="BX95" s="11"/>
       <c r="BY95" s="11"/>
-    </row>
-    <row r="96" spans="3:77">
+      <c r="BZ95" s="11"/>
+      <c r="CA95" s="11"/>
+      <c r="CB95" s="11"/>
+      <c r="CC95" s="11"/>
+    </row>
+    <row r="96" spans="3:81">
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
       <c r="E96" s="11"/>
@@ -9051,8 +9458,12 @@
       <c r="BW96" s="11"/>
       <c r="BX96" s="11"/>
       <c r="BY96" s="11"/>
-    </row>
-    <row r="97" spans="3:77">
+      <c r="BZ96" s="11"/>
+      <c r="CA96" s="11"/>
+      <c r="CB96" s="11"/>
+      <c r="CC96" s="11"/>
+    </row>
+    <row r="97" spans="3:81">
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
       <c r="E97" s="11"/>
@@ -9128,8 +9539,12 @@
       <c r="BW97" s="11"/>
       <c r="BX97" s="11"/>
       <c r="BY97" s="11"/>
-    </row>
-    <row r="98" spans="3:77">
+      <c r="BZ97" s="11"/>
+      <c r="CA97" s="11"/>
+      <c r="CB97" s="11"/>
+      <c r="CC97" s="11"/>
+    </row>
+    <row r="98" spans="3:81">
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
@@ -9205,8 +9620,12 @@
       <c r="BW98" s="11"/>
       <c r="BX98" s="11"/>
       <c r="BY98" s="11"/>
-    </row>
-    <row r="99" spans="3:77">
+      <c r="BZ98" s="11"/>
+      <c r="CA98" s="11"/>
+      <c r="CB98" s="11"/>
+      <c r="CC98" s="11"/>
+    </row>
+    <row r="99" spans="3:81">
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
@@ -9282,8 +9701,12 @@
       <c r="BW99" s="11"/>
       <c r="BX99" s="11"/>
       <c r="BY99" s="11"/>
-    </row>
-    <row r="100" spans="3:77">
+      <c r="BZ99" s="11"/>
+      <c r="CA99" s="11"/>
+      <c r="CB99" s="11"/>
+      <c r="CC99" s="11"/>
+    </row>
+    <row r="100" spans="3:81">
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
@@ -9359,8 +9782,12 @@
       <c r="BW100" s="11"/>
       <c r="BX100" s="11"/>
       <c r="BY100" s="11"/>
-    </row>
-    <row r="101" spans="3:77">
+      <c r="BZ100" s="11"/>
+      <c r="CA100" s="11"/>
+      <c r="CB100" s="11"/>
+      <c r="CC100" s="11"/>
+    </row>
+    <row r="101" spans="3:81">
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
@@ -9436,8 +9863,12 @@
       <c r="BW101" s="11"/>
       <c r="BX101" s="11"/>
       <c r="BY101" s="11"/>
-    </row>
-    <row r="102" spans="3:77">
+      <c r="BZ101" s="11"/>
+      <c r="CA101" s="11"/>
+      <c r="CB101" s="11"/>
+      <c r="CC101" s="11"/>
+    </row>
+    <row r="102" spans="3:81">
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
@@ -9513,8 +9944,12 @@
       <c r="BW102" s="11"/>
       <c r="BX102" s="11"/>
       <c r="BY102" s="11"/>
-    </row>
-    <row r="103" spans="3:77">
+      <c r="BZ102" s="11"/>
+      <c r="CA102" s="11"/>
+      <c r="CB102" s="11"/>
+      <c r="CC102" s="11"/>
+    </row>
+    <row r="103" spans="3:81">
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
@@ -9590,8 +10025,12 @@
       <c r="BW103" s="11"/>
       <c r="BX103" s="11"/>
       <c r="BY103" s="11"/>
-    </row>
-    <row r="104" spans="3:77">
+      <c r="BZ103" s="11"/>
+      <c r="CA103" s="11"/>
+      <c r="CB103" s="11"/>
+      <c r="CC103" s="11"/>
+    </row>
+    <row r="104" spans="3:81">
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
@@ -9667,8 +10106,12 @@
       <c r="BW104" s="11"/>
       <c r="BX104" s="11"/>
       <c r="BY104" s="11"/>
-    </row>
-    <row r="105" spans="3:77">
+      <c r="BZ104" s="11"/>
+      <c r="CA104" s="11"/>
+      <c r="CB104" s="11"/>
+      <c r="CC104" s="11"/>
+    </row>
+    <row r="105" spans="3:81">
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
@@ -9744,8 +10187,12 @@
       <c r="BW105" s="11"/>
       <c r="BX105" s="11"/>
       <c r="BY105" s="11"/>
-    </row>
-    <row r="106" spans="3:77">
+      <c r="BZ105" s="11"/>
+      <c r="CA105" s="11"/>
+      <c r="CB105" s="11"/>
+      <c r="CC105" s="11"/>
+    </row>
+    <row r="106" spans="3:81">
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -9821,8 +10268,12 @@
       <c r="BW106" s="11"/>
       <c r="BX106" s="11"/>
       <c r="BY106" s="11"/>
-    </row>
-    <row r="107" spans="3:77">
+      <c r="BZ106" s="11"/>
+      <c r="CA106" s="11"/>
+      <c r="CB106" s="11"/>
+      <c r="CC106" s="11"/>
+    </row>
+    <row r="107" spans="3:81">
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
@@ -9898,8 +10349,12 @@
       <c r="BW107" s="11"/>
       <c r="BX107" s="11"/>
       <c r="BY107" s="11"/>
-    </row>
-    <row r="108" spans="3:77">
+      <c r="BZ107" s="11"/>
+      <c r="CA107" s="11"/>
+      <c r="CB107" s="11"/>
+      <c r="CC107" s="11"/>
+    </row>
+    <row r="108" spans="3:81">
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
       <c r="E108" s="11"/>
@@ -9975,8 +10430,12 @@
       <c r="BW108" s="11"/>
       <c r="BX108" s="11"/>
       <c r="BY108" s="11"/>
-    </row>
-    <row r="109" spans="3:77">
+      <c r="BZ108" s="11"/>
+      <c r="CA108" s="11"/>
+      <c r="CB108" s="11"/>
+      <c r="CC108" s="11"/>
+    </row>
+    <row r="109" spans="3:81">
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
       <c r="E109" s="11"/>
@@ -10052,8 +10511,12 @@
       <c r="BW109" s="11"/>
       <c r="BX109" s="11"/>
       <c r="BY109" s="11"/>
-    </row>
-    <row r="110" spans="3:77">
+      <c r="BZ109" s="11"/>
+      <c r="CA109" s="11"/>
+      <c r="CB109" s="11"/>
+      <c r="CC109" s="11"/>
+    </row>
+    <row r="110" spans="3:81">
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
       <c r="E110" s="11"/>
@@ -10129,8 +10592,12 @@
       <c r="BW110" s="11"/>
       <c r="BX110" s="11"/>
       <c r="BY110" s="11"/>
-    </row>
-    <row r="111" spans="3:77">
+      <c r="BZ110" s="11"/>
+      <c r="CA110" s="11"/>
+      <c r="CB110" s="11"/>
+      <c r="CC110" s="11"/>
+    </row>
+    <row r="111" spans="3:81">
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
       <c r="E111" s="11"/>
@@ -10206,8 +10673,12 @@
       <c r="BW111" s="11"/>
       <c r="BX111" s="11"/>
       <c r="BY111" s="11"/>
-    </row>
-    <row r="112" spans="3:77">
+      <c r="BZ111" s="11"/>
+      <c r="CA111" s="11"/>
+      <c r="CB111" s="11"/>
+      <c r="CC111" s="11"/>
+    </row>
+    <row r="112" spans="3:81">
       <c r="C112" s="11"/>
       <c r="D112" s="11"/>
       <c r="E112" s="11"/>
@@ -10283,8 +10754,12 @@
       <c r="BW112" s="11"/>
       <c r="BX112" s="11"/>
       <c r="BY112" s="11"/>
-    </row>
-    <row r="113" spans="3:77">
+      <c r="BZ112" s="11"/>
+      <c r="CA112" s="11"/>
+      <c r="CB112" s="11"/>
+      <c r="CC112" s="11"/>
+    </row>
+    <row r="113" spans="3:81">
       <c r="C113" s="11"/>
       <c r="D113" s="11"/>
       <c r="E113" s="11"/>
@@ -10360,8 +10835,12 @@
       <c r="BW113" s="11"/>
       <c r="BX113" s="11"/>
       <c r="BY113" s="11"/>
-    </row>
-    <row r="114" spans="3:77">
+      <c r="BZ113" s="11"/>
+      <c r="CA113" s="11"/>
+      <c r="CB113" s="11"/>
+      <c r="CC113" s="11"/>
+    </row>
+    <row r="114" spans="3:81">
       <c r="C114" s="11"/>
       <c r="D114" s="11"/>
       <c r="E114" s="11"/>
@@ -10437,8 +10916,12 @@
       <c r="BW114" s="11"/>
       <c r="BX114" s="11"/>
       <c r="BY114" s="11"/>
-    </row>
-    <row r="115" spans="3:77">
+      <c r="BZ114" s="11"/>
+      <c r="CA114" s="11"/>
+      <c r="CB114" s="11"/>
+      <c r="CC114" s="11"/>
+    </row>
+    <row r="115" spans="3:81">
       <c r="C115" s="11"/>
       <c r="D115" s="11"/>
       <c r="E115" s="11"/>
@@ -10514,8 +10997,12 @@
       <c r="BW115" s="11"/>
       <c r="BX115" s="11"/>
       <c r="BY115" s="11"/>
-    </row>
-    <row r="116" spans="3:77">
+      <c r="BZ115" s="11"/>
+      <c r="CA115" s="11"/>
+      <c r="CB115" s="11"/>
+      <c r="CC115" s="11"/>
+    </row>
+    <row r="116" spans="3:81">
       <c r="C116" s="11"/>
       <c r="D116" s="11"/>
       <c r="E116" s="11"/>
@@ -10591,8 +11078,12 @@
       <c r="BW116" s="11"/>
       <c r="BX116" s="11"/>
       <c r="BY116" s="11"/>
-    </row>
-    <row r="117" spans="3:77">
+      <c r="BZ116" s="11"/>
+      <c r="CA116" s="11"/>
+      <c r="CB116" s="11"/>
+      <c r="CC116" s="11"/>
+    </row>
+    <row r="117" spans="3:81">
       <c r="C117" s="11"/>
       <c r="D117" s="11"/>
       <c r="E117" s="11"/>
@@ -10668,8 +11159,12 @@
       <c r="BW117" s="11"/>
       <c r="BX117" s="11"/>
       <c r="BY117" s="11"/>
-    </row>
-    <row r="118" spans="3:77">
+      <c r="BZ117" s="11"/>
+      <c r="CA117" s="11"/>
+      <c r="CB117" s="11"/>
+      <c r="CC117" s="11"/>
+    </row>
+    <row r="118" spans="3:81">
       <c r="C118" s="11"/>
       <c r="D118" s="11"/>
       <c r="E118" s="11"/>
@@ -10745,8 +11240,12 @@
       <c r="BW118" s="11"/>
       <c r="BX118" s="11"/>
       <c r="BY118" s="11"/>
-    </row>
-    <row r="119" spans="3:77">
+      <c r="BZ118" s="11"/>
+      <c r="CA118" s="11"/>
+      <c r="CB118" s="11"/>
+      <c r="CC118" s="11"/>
+    </row>
+    <row r="119" spans="3:81">
       <c r="C119" s="11"/>
       <c r="D119" s="11"/>
       <c r="E119" s="11"/>
@@ -10822,8 +11321,12 @@
       <c r="BW119" s="11"/>
       <c r="BX119" s="11"/>
       <c r="BY119" s="11"/>
-    </row>
-    <row r="120" spans="3:77">
+      <c r="BZ119" s="11"/>
+      <c r="CA119" s="11"/>
+      <c r="CB119" s="11"/>
+      <c r="CC119" s="11"/>
+    </row>
+    <row r="120" spans="3:81">
       <c r="C120" s="11"/>
       <c r="D120" s="11"/>
       <c r="E120" s="11"/>
@@ -10899,8 +11402,12 @@
       <c r="BW120" s="11"/>
       <c r="BX120" s="11"/>
       <c r="BY120" s="11"/>
-    </row>
-    <row r="121" spans="3:77">
+      <c r="BZ120" s="11"/>
+      <c r="CA120" s="11"/>
+      <c r="CB120" s="11"/>
+      <c r="CC120" s="11"/>
+    </row>
+    <row r="121" spans="3:81">
       <c r="C121" s="11"/>
       <c r="D121" s="11"/>
       <c r="E121" s="11"/>
@@ -10976,8 +11483,12 @@
       <c r="BW121" s="11"/>
       <c r="BX121" s="11"/>
       <c r="BY121" s="11"/>
-    </row>
-    <row r="122" spans="3:77">
+      <c r="BZ121" s="11"/>
+      <c r="CA121" s="11"/>
+      <c r="CB121" s="11"/>
+      <c r="CC121" s="11"/>
+    </row>
+    <row r="122" spans="3:81">
       <c r="C122" s="11"/>
       <c r="D122" s="11"/>
       <c r="E122" s="11"/>
@@ -11053,8 +11564,12 @@
       <c r="BW122" s="11"/>
       <c r="BX122" s="11"/>
       <c r="BY122" s="11"/>
-    </row>
-    <row r="123" spans="3:77">
+      <c r="BZ122" s="11"/>
+      <c r="CA122" s="11"/>
+      <c r="CB122" s="11"/>
+      <c r="CC122" s="11"/>
+    </row>
+    <row r="123" spans="3:81">
       <c r="C123" s="11"/>
       <c r="D123" s="11"/>
       <c r="E123" s="11"/>
@@ -11130,8 +11645,12 @@
       <c r="BW123" s="11"/>
       <c r="BX123" s="11"/>
       <c r="BY123" s="11"/>
-    </row>
-    <row r="124" spans="3:77">
+      <c r="BZ123" s="11"/>
+      <c r="CA123" s="11"/>
+      <c r="CB123" s="11"/>
+      <c r="CC123" s="11"/>
+    </row>
+    <row r="124" spans="3:81">
       <c r="C124" s="11"/>
       <c r="D124" s="11"/>
       <c r="E124" s="11"/>
@@ -11207,8 +11726,12 @@
       <c r="BW124" s="11"/>
       <c r="BX124" s="11"/>
       <c r="BY124" s="11"/>
-    </row>
-    <row r="125" spans="3:77">
+      <c r="BZ124" s="11"/>
+      <c r="CA124" s="11"/>
+      <c r="CB124" s="11"/>
+      <c r="CC124" s="11"/>
+    </row>
+    <row r="125" spans="3:81">
       <c r="C125" s="11"/>
       <c r="D125" s="11"/>
       <c r="E125" s="11"/>
@@ -11284,8 +11807,12 @@
       <c r="BW125" s="11"/>
       <c r="BX125" s="11"/>
       <c r="BY125" s="11"/>
-    </row>
-    <row r="126" spans="3:77">
+      <c r="BZ125" s="11"/>
+      <c r="CA125" s="11"/>
+      <c r="CB125" s="11"/>
+      <c r="CC125" s="11"/>
+    </row>
+    <row r="126" spans="3:81">
       <c r="C126" s="11"/>
       <c r="D126" s="11"/>
       <c r="E126" s="11"/>
@@ -11361,8 +11888,12 @@
       <c r="BW126" s="11"/>
       <c r="BX126" s="11"/>
       <c r="BY126" s="11"/>
-    </row>
-    <row r="127" spans="3:77">
+      <c r="BZ126" s="11"/>
+      <c r="CA126" s="11"/>
+      <c r="CB126" s="11"/>
+      <c r="CC126" s="11"/>
+    </row>
+    <row r="127" spans="3:81">
       <c r="C127" s="11"/>
       <c r="D127" s="11"/>
       <c r="E127" s="11"/>
@@ -11438,8 +11969,12 @@
       <c r="BW127" s="11"/>
       <c r="BX127" s="11"/>
       <c r="BY127" s="11"/>
-    </row>
-    <row r="128" spans="3:77">
+      <c r="BZ127" s="11"/>
+      <c r="CA127" s="11"/>
+      <c r="CB127" s="11"/>
+      <c r="CC127" s="11"/>
+    </row>
+    <row r="128" spans="3:81">
       <c r="C128" s="11"/>
       <c r="D128" s="11"/>
       <c r="E128" s="11"/>
@@ -11515,8 +12050,12 @@
       <c r="BW128" s="11"/>
       <c r="BX128" s="11"/>
       <c r="BY128" s="11"/>
-    </row>
-    <row r="129" spans="3:77">
+      <c r="BZ128" s="11"/>
+      <c r="CA128" s="11"/>
+      <c r="CB128" s="11"/>
+      <c r="CC128" s="11"/>
+    </row>
+    <row r="129" spans="3:81">
       <c r="C129" s="11"/>
       <c r="D129" s="11"/>
       <c r="E129" s="11"/>
@@ -11592,8 +12131,12 @@
       <c r="BW129" s="11"/>
       <c r="BX129" s="11"/>
       <c r="BY129" s="11"/>
-    </row>
-    <row r="130" spans="3:77">
+      <c r="BZ129" s="11"/>
+      <c r="CA129" s="11"/>
+      <c r="CB129" s="11"/>
+      <c r="CC129" s="11"/>
+    </row>
+    <row r="130" spans="3:81">
       <c r="C130" s="11"/>
       <c r="D130" s="11"/>
       <c r="E130" s="11"/>
@@ -11669,8 +12212,12 @@
       <c r="BW130" s="11"/>
       <c r="BX130" s="11"/>
       <c r="BY130" s="11"/>
-    </row>
-    <row r="131" spans="3:77">
+      <c r="BZ130" s="11"/>
+      <c r="CA130" s="11"/>
+      <c r="CB130" s="11"/>
+      <c r="CC130" s="11"/>
+    </row>
+    <row r="131" spans="3:81">
       <c r="C131" s="11"/>
       <c r="D131" s="11"/>
       <c r="E131" s="11"/>
@@ -11746,8 +12293,12 @@
       <c r="BW131" s="11"/>
       <c r="BX131" s="11"/>
       <c r="BY131" s="11"/>
-    </row>
-    <row r="132" spans="3:77">
+      <c r="BZ131" s="11"/>
+      <c r="CA131" s="11"/>
+      <c r="CB131" s="11"/>
+      <c r="CC131" s="11"/>
+    </row>
+    <row r="132" spans="3:81">
       <c r="C132" s="11"/>
       <c r="D132" s="11"/>
       <c r="E132" s="11"/>
@@ -11823,8 +12374,12 @@
       <c r="BW132" s="11"/>
       <c r="BX132" s="11"/>
       <c r="BY132" s="11"/>
-    </row>
-    <row r="133" spans="3:77">
+      <c r="BZ132" s="11"/>
+      <c r="CA132" s="11"/>
+      <c r="CB132" s="11"/>
+      <c r="CC132" s="11"/>
+    </row>
+    <row r="133" spans="3:81">
       <c r="C133" s="11"/>
       <c r="D133" s="11"/>
       <c r="E133" s="11"/>
@@ -11900,8 +12455,12 @@
       <c r="BW133" s="11"/>
       <c r="BX133" s="11"/>
       <c r="BY133" s="11"/>
-    </row>
-    <row r="134" spans="3:77">
+      <c r="BZ133" s="11"/>
+      <c r="CA133" s="11"/>
+      <c r="CB133" s="11"/>
+      <c r="CC133" s="11"/>
+    </row>
+    <row r="134" spans="3:81">
       <c r="C134" s="11"/>
       <c r="D134" s="11"/>
       <c r="E134" s="11"/>
@@ -11977,8 +12536,12 @@
       <c r="BW134" s="11"/>
       <c r="BX134" s="11"/>
       <c r="BY134" s="11"/>
-    </row>
-    <row r="135" spans="3:77">
+      <c r="BZ134" s="11"/>
+      <c r="CA134" s="11"/>
+      <c r="CB134" s="11"/>
+      <c r="CC134" s="11"/>
+    </row>
+    <row r="135" spans="3:81">
       <c r="C135" s="11"/>
       <c r="D135" s="11"/>
       <c r="E135" s="11"/>
@@ -12054,8 +12617,12 @@
       <c r="BW135" s="11"/>
       <c r="BX135" s="11"/>
       <c r="BY135" s="11"/>
-    </row>
-    <row r="136" spans="3:77">
+      <c r="BZ135" s="11"/>
+      <c r="CA135" s="11"/>
+      <c r="CB135" s="11"/>
+      <c r="CC135" s="11"/>
+    </row>
+    <row r="136" spans="3:81">
       <c r="C136" s="11"/>
       <c r="D136" s="11"/>
       <c r="E136" s="11"/>
@@ -12131,8 +12698,12 @@
       <c r="BW136" s="11"/>
       <c r="BX136" s="11"/>
       <c r="BY136" s="11"/>
-    </row>
-    <row r="137" spans="3:77">
+      <c r="BZ136" s="11"/>
+      <c r="CA136" s="11"/>
+      <c r="CB136" s="11"/>
+      <c r="CC136" s="11"/>
+    </row>
+    <row r="137" spans="3:81">
       <c r="C137" s="11"/>
       <c r="D137" s="11"/>
       <c r="E137" s="11"/>
@@ -12208,8 +12779,12 @@
       <c r="BW137" s="11"/>
       <c r="BX137" s="11"/>
       <c r="BY137" s="11"/>
-    </row>
-    <row r="138" spans="3:77">
+      <c r="BZ137" s="11"/>
+      <c r="CA137" s="11"/>
+      <c r="CB137" s="11"/>
+      <c r="CC137" s="11"/>
+    </row>
+    <row r="138" spans="3:81">
       <c r="C138" s="11"/>
       <c r="D138" s="11"/>
       <c r="E138" s="11"/>
@@ -12285,8 +12860,12 @@
       <c r="BW138" s="11"/>
       <c r="BX138" s="11"/>
       <c r="BY138" s="11"/>
-    </row>
-    <row r="139" spans="3:77">
+      <c r="BZ138" s="11"/>
+      <c r="CA138" s="11"/>
+      <c r="CB138" s="11"/>
+      <c r="CC138" s="11"/>
+    </row>
+    <row r="139" spans="3:81">
       <c r="C139" s="11"/>
       <c r="D139" s="11"/>
       <c r="E139" s="11"/>
@@ -12362,8 +12941,12 @@
       <c r="BW139" s="11"/>
       <c r="BX139" s="11"/>
       <c r="BY139" s="11"/>
-    </row>
-    <row r="140" spans="3:77">
+      <c r="BZ139" s="11"/>
+      <c r="CA139" s="11"/>
+      <c r="CB139" s="11"/>
+      <c r="CC139" s="11"/>
+    </row>
+    <row r="140" spans="3:81">
       <c r="C140" s="11"/>
       <c r="D140" s="11"/>
       <c r="E140" s="11"/>
@@ -12439,8 +13022,12 @@
       <c r="BW140" s="11"/>
       <c r="BX140" s="11"/>
       <c r="BY140" s="11"/>
-    </row>
-    <row r="141" spans="3:77">
+      <c r="BZ140" s="11"/>
+      <c r="CA140" s="11"/>
+      <c r="CB140" s="11"/>
+      <c r="CC140" s="11"/>
+    </row>
+    <row r="141" spans="3:81">
       <c r="C141" s="11"/>
       <c r="D141" s="11"/>
       <c r="E141" s="11"/>
@@ -12516,8 +13103,12 @@
       <c r="BW141" s="11"/>
       <c r="BX141" s="11"/>
       <c r="BY141" s="11"/>
-    </row>
-    <row r="142" spans="3:77">
+      <c r="BZ141" s="11"/>
+      <c r="CA141" s="11"/>
+      <c r="CB141" s="11"/>
+      <c r="CC141" s="11"/>
+    </row>
+    <row r="142" spans="3:81">
       <c r="C142" s="11"/>
       <c r="D142" s="11"/>
       <c r="E142" s="11"/>
@@ -12593,8 +13184,12 @@
       <c r="BW142" s="11"/>
       <c r="BX142" s="11"/>
       <c r="BY142" s="11"/>
-    </row>
-    <row r="143" spans="3:77">
+      <c r="BZ142" s="11"/>
+      <c r="CA142" s="11"/>
+      <c r="CB142" s="11"/>
+      <c r="CC142" s="11"/>
+    </row>
+    <row r="143" spans="3:81">
       <c r="C143" s="11"/>
       <c r="D143" s="11"/>
       <c r="E143" s="11"/>
@@ -12670,8 +13265,12 @@
       <c r="BW143" s="11"/>
       <c r="BX143" s="11"/>
       <c r="BY143" s="11"/>
-    </row>
-    <row r="144" spans="3:77">
+      <c r="BZ143" s="11"/>
+      <c r="CA143" s="11"/>
+      <c r="CB143" s="11"/>
+      <c r="CC143" s="11"/>
+    </row>
+    <row r="144" spans="3:81">
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
       <c r="E144" s="11"/>
@@ -12747,8 +13346,12 @@
       <c r="BW144" s="11"/>
       <c r="BX144" s="11"/>
       <c r="BY144" s="11"/>
-    </row>
-    <row r="145" spans="3:77">
+      <c r="BZ144" s="11"/>
+      <c r="CA144" s="11"/>
+      <c r="CB144" s="11"/>
+      <c r="CC144" s="11"/>
+    </row>
+    <row r="145" spans="3:81">
       <c r="C145" s="11"/>
       <c r="D145" s="11"/>
       <c r="E145" s="11"/>
@@ -12824,8 +13427,12 @@
       <c r="BW145" s="11"/>
       <c r="BX145" s="11"/>
       <c r="BY145" s="11"/>
-    </row>
-    <row r="146" spans="3:77">
+      <c r="BZ145" s="11"/>
+      <c r="CA145" s="11"/>
+      <c r="CB145" s="11"/>
+      <c r="CC145" s="11"/>
+    </row>
+    <row r="146" spans="3:81">
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
       <c r="E146" s="11"/>
@@ -12901,8 +13508,12 @@
       <c r="BW146" s="11"/>
       <c r="BX146" s="11"/>
       <c r="BY146" s="11"/>
-    </row>
-    <row r="147" spans="3:77">
+      <c r="BZ146" s="11"/>
+      <c r="CA146" s="11"/>
+      <c r="CB146" s="11"/>
+      <c r="CC146" s="11"/>
+    </row>
+    <row r="147" spans="3:81">
       <c r="C147" s="11"/>
       <c r="D147" s="11"/>
       <c r="E147" s="11"/>
@@ -12978,8 +13589,12 @@
       <c r="BW147" s="11"/>
       <c r="BX147" s="11"/>
       <c r="BY147" s="11"/>
-    </row>
-    <row r="148" spans="3:77">
+      <c r="BZ147" s="11"/>
+      <c r="CA147" s="11"/>
+      <c r="CB147" s="11"/>
+      <c r="CC147" s="11"/>
+    </row>
+    <row r="148" spans="3:81">
       <c r="C148" s="11"/>
       <c r="D148" s="11"/>
       <c r="E148" s="11"/>
@@ -13055,8 +13670,12 @@
       <c r="BW148" s="11"/>
       <c r="BX148" s="11"/>
       <c r="BY148" s="11"/>
-    </row>
-    <row r="149" spans="3:77">
+      <c r="BZ148" s="11"/>
+      <c r="CA148" s="11"/>
+      <c r="CB148" s="11"/>
+      <c r="CC148" s="11"/>
+    </row>
+    <row r="149" spans="3:81">
       <c r="C149" s="11"/>
       <c r="D149" s="11"/>
       <c r="E149" s="11"/>
@@ -13132,8 +13751,12 @@
       <c r="BW149" s="11"/>
       <c r="BX149" s="11"/>
       <c r="BY149" s="11"/>
-    </row>
-    <row r="150" spans="3:77">
+      <c r="BZ149" s="11"/>
+      <c r="CA149" s="11"/>
+      <c r="CB149" s="11"/>
+      <c r="CC149" s="11"/>
+    </row>
+    <row r="150" spans="3:81">
       <c r="C150" s="11"/>
       <c r="D150" s="11"/>
       <c r="E150" s="11"/>
@@ -13209,8 +13832,12 @@
       <c r="BW150" s="11"/>
       <c r="BX150" s="11"/>
       <c r="BY150" s="11"/>
-    </row>
-    <row r="151" spans="3:77">
+      <c r="BZ150" s="11"/>
+      <c r="CA150" s="11"/>
+      <c r="CB150" s="11"/>
+      <c r="CC150" s="11"/>
+    </row>
+    <row r="151" spans="3:81">
       <c r="C151" s="11"/>
       <c r="D151" s="11"/>
       <c r="E151" s="11"/>
@@ -13286,8 +13913,12 @@
       <c r="BW151" s="11"/>
       <c r="BX151" s="11"/>
       <c r="BY151" s="11"/>
-    </row>
-    <row r="152" spans="3:77">
+      <c r="BZ151" s="11"/>
+      <c r="CA151" s="11"/>
+      <c r="CB151" s="11"/>
+      <c r="CC151" s="11"/>
+    </row>
+    <row r="152" spans="3:81">
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
       <c r="E152" s="11"/>
@@ -13363,8 +13994,12 @@
       <c r="BW152" s="11"/>
       <c r="BX152" s="11"/>
       <c r="BY152" s="11"/>
-    </row>
-    <row r="153" spans="3:77">
+      <c r="BZ152" s="11"/>
+      <c r="CA152" s="11"/>
+      <c r="CB152" s="11"/>
+      <c r="CC152" s="11"/>
+    </row>
+    <row r="153" spans="3:81">
       <c r="C153" s="11"/>
       <c r="D153" s="11"/>
       <c r="E153" s="11"/>
@@ -13440,8 +14075,12 @@
       <c r="BW153" s="11"/>
       <c r="BX153" s="11"/>
       <c r="BY153" s="11"/>
-    </row>
-    <row r="154" spans="3:77">
+      <c r="BZ153" s="11"/>
+      <c r="CA153" s="11"/>
+      <c r="CB153" s="11"/>
+      <c r="CC153" s="11"/>
+    </row>
+    <row r="154" spans="3:81">
       <c r="C154" s="11"/>
       <c r="D154" s="11"/>
       <c r="E154" s="11"/>
@@ -13517,8 +14156,12 @@
       <c r="BW154" s="11"/>
       <c r="BX154" s="11"/>
       <c r="BY154" s="11"/>
-    </row>
-    <row r="155" spans="3:77">
+      <c r="BZ154" s="11"/>
+      <c r="CA154" s="11"/>
+      <c r="CB154" s="11"/>
+      <c r="CC154" s="11"/>
+    </row>
+    <row r="155" spans="3:81">
       <c r="C155" s="11"/>
       <c r="D155" s="11"/>
       <c r="E155" s="11"/>
@@ -13594,8 +14237,12 @@
       <c r="BW155" s="11"/>
       <c r="BX155" s="11"/>
       <c r="BY155" s="11"/>
-    </row>
-    <row r="156" spans="3:77">
+      <c r="BZ155" s="11"/>
+      <c r="CA155" s="11"/>
+      <c r="CB155" s="11"/>
+      <c r="CC155" s="11"/>
+    </row>
+    <row r="156" spans="3:81">
       <c r="C156" s="11"/>
       <c r="D156" s="11"/>
       <c r="E156" s="11"/>
@@ -13671,8 +14318,12 @@
       <c r="BW156" s="11"/>
       <c r="BX156" s="11"/>
       <c r="BY156" s="11"/>
-    </row>
-    <row r="157" spans="3:77">
+      <c r="BZ156" s="11"/>
+      <c r="CA156" s="11"/>
+      <c r="CB156" s="11"/>
+      <c r="CC156" s="11"/>
+    </row>
+    <row r="157" spans="3:81">
       <c r="C157" s="11"/>
       <c r="D157" s="11"/>
       <c r="E157" s="11"/>
@@ -13748,8 +14399,12 @@
       <c r="BW157" s="11"/>
       <c r="BX157" s="11"/>
       <c r="BY157" s="11"/>
-    </row>
-    <row r="158" spans="3:77">
+      <c r="BZ157" s="11"/>
+      <c r="CA157" s="11"/>
+      <c r="CB157" s="11"/>
+      <c r="CC157" s="11"/>
+    </row>
+    <row r="158" spans="3:81">
       <c r="C158" s="11"/>
       <c r="D158" s="11"/>
       <c r="E158" s="11"/>
@@ -13825,8 +14480,12 @@
       <c r="BW158" s="11"/>
       <c r="BX158" s="11"/>
       <c r="BY158" s="11"/>
-    </row>
-    <row r="159" spans="3:77">
+      <c r="BZ158" s="11"/>
+      <c r="CA158" s="11"/>
+      <c r="CB158" s="11"/>
+      <c r="CC158" s="11"/>
+    </row>
+    <row r="159" spans="3:81">
       <c r="C159" s="11"/>
       <c r="D159" s="11"/>
       <c r="E159" s="11"/>
@@ -13902,8 +14561,12 @@
       <c r="BW159" s="11"/>
       <c r="BX159" s="11"/>
       <c r="BY159" s="11"/>
-    </row>
-    <row r="160" spans="3:77">
+      <c r="BZ159" s="11"/>
+      <c r="CA159" s="11"/>
+      <c r="CB159" s="11"/>
+      <c r="CC159" s="11"/>
+    </row>
+    <row r="160" spans="3:81">
       <c r="C160" s="11"/>
       <c r="D160" s="11"/>
       <c r="E160" s="11"/>
@@ -13979,8 +14642,12 @@
       <c r="BW160" s="11"/>
       <c r="BX160" s="11"/>
       <c r="BY160" s="11"/>
-    </row>
-    <row r="161" spans="3:77">
+      <c r="BZ160" s="11"/>
+      <c r="CA160" s="11"/>
+      <c r="CB160" s="11"/>
+      <c r="CC160" s="11"/>
+    </row>
+    <row r="161" spans="3:81">
       <c r="C161" s="11"/>
       <c r="D161" s="11"/>
       <c r="E161" s="11"/>
@@ -14056,8 +14723,12 @@
       <c r="BW161" s="11"/>
       <c r="BX161" s="11"/>
       <c r="BY161" s="11"/>
-    </row>
-    <row r="162" spans="3:77">
+      <c r="BZ161" s="11"/>
+      <c r="CA161" s="11"/>
+      <c r="CB161" s="11"/>
+      <c r="CC161" s="11"/>
+    </row>
+    <row r="162" spans="3:81">
       <c r="C162" s="11"/>
       <c r="D162" s="11"/>
       <c r="E162" s="11"/>
@@ -14133,8 +14804,12 @@
       <c r="BW162" s="11"/>
       <c r="BX162" s="11"/>
       <c r="BY162" s="11"/>
-    </row>
-    <row r="163" spans="3:77">
+      <c r="BZ162" s="11"/>
+      <c r="CA162" s="11"/>
+      <c r="CB162" s="11"/>
+      <c r="CC162" s="11"/>
+    </row>
+    <row r="163" spans="3:81">
       <c r="C163" s="11"/>
       <c r="D163" s="11"/>
       <c r="E163" s="11"/>
@@ -14210,8 +14885,12 @@
       <c r="BW163" s="11"/>
       <c r="BX163" s="11"/>
       <c r="BY163" s="11"/>
-    </row>
-    <row r="164" spans="3:77">
+      <c r="BZ163" s="11"/>
+      <c r="CA163" s="11"/>
+      <c r="CB163" s="11"/>
+      <c r="CC163" s="11"/>
+    </row>
+    <row r="164" spans="3:81">
       <c r="C164" s="11"/>
       <c r="D164" s="11"/>
       <c r="E164" s="11"/>
@@ -14287,8 +14966,12 @@
       <c r="BW164" s="11"/>
       <c r="BX164" s="11"/>
       <c r="BY164" s="11"/>
-    </row>
-    <row r="165" spans="3:77">
+      <c r="BZ164" s="11"/>
+      <c r="CA164" s="11"/>
+      <c r="CB164" s="11"/>
+      <c r="CC164" s="11"/>
+    </row>
+    <row r="165" spans="3:81">
       <c r="C165" s="11"/>
       <c r="D165" s="11"/>
       <c r="E165" s="11"/>
@@ -14364,8 +15047,12 @@
       <c r="BW165" s="11"/>
       <c r="BX165" s="11"/>
       <c r="BY165" s="11"/>
-    </row>
-    <row r="166" spans="3:77">
+      <c r="BZ165" s="11"/>
+      <c r="CA165" s="11"/>
+      <c r="CB165" s="11"/>
+      <c r="CC165" s="11"/>
+    </row>
+    <row r="166" spans="3:81">
       <c r="C166" s="11"/>
       <c r="D166" s="11"/>
       <c r="E166" s="11"/>
@@ -14441,8 +15128,12 @@
       <c r="BW166" s="11"/>
       <c r="BX166" s="11"/>
       <c r="BY166" s="11"/>
-    </row>
-    <row r="167" spans="3:77">
+      <c r="BZ166" s="11"/>
+      <c r="CA166" s="11"/>
+      <c r="CB166" s="11"/>
+      <c r="CC166" s="11"/>
+    </row>
+    <row r="167" spans="3:81">
       <c r="C167" s="11"/>
       <c r="D167" s="11"/>
       <c r="E167" s="11"/>
@@ -14518,8 +15209,12 @@
       <c r="BW167" s="11"/>
       <c r="BX167" s="11"/>
       <c r="BY167" s="11"/>
-    </row>
-    <row r="168" spans="3:77">
+      <c r="BZ167" s="11"/>
+      <c r="CA167" s="11"/>
+      <c r="CB167" s="11"/>
+      <c r="CC167" s="11"/>
+    </row>
+    <row r="168" spans="3:81">
       <c r="C168" s="11"/>
       <c r="D168" s="11"/>
       <c r="E168" s="11"/>
@@ -14595,8 +15290,12 @@
       <c r="BW168" s="11"/>
       <c r="BX168" s="11"/>
       <c r="BY168" s="11"/>
-    </row>
-    <row r="169" spans="3:77">
+      <c r="BZ168" s="11"/>
+      <c r="CA168" s="11"/>
+      <c r="CB168" s="11"/>
+      <c r="CC168" s="11"/>
+    </row>
+    <row r="169" spans="3:81">
       <c r="C169" s="11"/>
       <c r="D169" s="11"/>
       <c r="E169" s="11"/>
@@ -14672,8 +15371,12 @@
       <c r="BW169" s="11"/>
       <c r="BX169" s="11"/>
       <c r="BY169" s="11"/>
-    </row>
-    <row r="170" spans="3:77">
+      <c r="BZ169" s="11"/>
+      <c r="CA169" s="11"/>
+      <c r="CB169" s="11"/>
+      <c r="CC169" s="11"/>
+    </row>
+    <row r="170" spans="3:81">
       <c r="C170" s="11"/>
       <c r="D170" s="11"/>
       <c r="E170" s="11"/>
@@ -14749,8 +15452,12 @@
       <c r="BW170" s="11"/>
       <c r="BX170" s="11"/>
       <c r="BY170" s="11"/>
-    </row>
-    <row r="171" spans="3:77">
+      <c r="BZ170" s="11"/>
+      <c r="CA170" s="11"/>
+      <c r="CB170" s="11"/>
+      <c r="CC170" s="11"/>
+    </row>
+    <row r="171" spans="3:81">
       <c r="C171" s="11"/>
       <c r="D171" s="11"/>
       <c r="E171" s="11"/>
@@ -14826,8 +15533,12 @@
       <c r="BW171" s="11"/>
       <c r="BX171" s="11"/>
       <c r="BY171" s="11"/>
-    </row>
-    <row r="172" spans="3:77">
+      <c r="BZ171" s="11"/>
+      <c r="CA171" s="11"/>
+      <c r="CB171" s="11"/>
+      <c r="CC171" s="11"/>
+    </row>
+    <row r="172" spans="3:81">
       <c r="C172" s="11"/>
       <c r="D172" s="11"/>
       <c r="E172" s="11"/>
@@ -14903,8 +15614,12 @@
       <c r="BW172" s="11"/>
       <c r="BX172" s="11"/>
       <c r="BY172" s="11"/>
-    </row>
-    <row r="173" spans="3:77">
+      <c r="BZ172" s="11"/>
+      <c r="CA172" s="11"/>
+      <c r="CB172" s="11"/>
+      <c r="CC172" s="11"/>
+    </row>
+    <row r="173" spans="3:81">
       <c r="C173" s="11"/>
       <c r="D173" s="11"/>
       <c r="E173" s="11"/>
@@ -14980,8 +15695,12 @@
       <c r="BW173" s="11"/>
       <c r="BX173" s="11"/>
       <c r="BY173" s="11"/>
-    </row>
-    <row r="174" spans="3:77">
+      <c r="BZ173" s="11"/>
+      <c r="CA173" s="11"/>
+      <c r="CB173" s="11"/>
+      <c r="CC173" s="11"/>
+    </row>
+    <row r="174" spans="3:81">
       <c r="C174" s="11"/>
       <c r="D174" s="11"/>
       <c r="E174" s="11"/>
@@ -15057,8 +15776,12 @@
       <c r="BW174" s="11"/>
       <c r="BX174" s="11"/>
       <c r="BY174" s="11"/>
-    </row>
-    <row r="175" spans="3:77">
+      <c r="BZ174" s="11"/>
+      <c r="CA174" s="11"/>
+      <c r="CB174" s="11"/>
+      <c r="CC174" s="11"/>
+    </row>
+    <row r="175" spans="3:81">
       <c r="C175" s="11"/>
       <c r="D175" s="11"/>
       <c r="E175" s="11"/>
@@ -15134,8 +15857,12 @@
       <c r="BW175" s="11"/>
       <c r="BX175" s="11"/>
       <c r="BY175" s="11"/>
-    </row>
-    <row r="176" spans="3:77">
+      <c r="BZ175" s="11"/>
+      <c r="CA175" s="11"/>
+      <c r="CB175" s="11"/>
+      <c r="CC175" s="11"/>
+    </row>
+    <row r="176" spans="3:81">
       <c r="C176" s="11"/>
       <c r="D176" s="11"/>
       <c r="E176" s="11"/>
@@ -15211,8 +15938,12 @@
       <c r="BW176" s="11"/>
       <c r="BX176" s="11"/>
       <c r="BY176" s="11"/>
-    </row>
-    <row r="177" spans="3:77">
+      <c r="BZ176" s="11"/>
+      <c r="CA176" s="11"/>
+      <c r="CB176" s="11"/>
+      <c r="CC176" s="11"/>
+    </row>
+    <row r="177" spans="3:81">
       <c r="C177" s="11"/>
       <c r="D177" s="11"/>
       <c r="E177" s="11"/>
@@ -15288,8 +16019,12 @@
       <c r="BW177" s="11"/>
       <c r="BX177" s="11"/>
       <c r="BY177" s="11"/>
-    </row>
-    <row r="178" spans="3:77">
+      <c r="BZ177" s="11"/>
+      <c r="CA177" s="11"/>
+      <c r="CB177" s="11"/>
+      <c r="CC177" s="11"/>
+    </row>
+    <row r="178" spans="3:81">
       <c r="C178" s="11"/>
       <c r="D178" s="11"/>
       <c r="E178" s="11"/>
@@ -15365,8 +16100,12 @@
       <c r="BW178" s="11"/>
       <c r="BX178" s="11"/>
       <c r="BY178" s="11"/>
-    </row>
-    <row r="179" spans="3:77">
+      <c r="BZ178" s="11"/>
+      <c r="CA178" s="11"/>
+      <c r="CB178" s="11"/>
+      <c r="CC178" s="11"/>
+    </row>
+    <row r="179" spans="3:81">
       <c r="C179" s="11"/>
       <c r="D179" s="11"/>
       <c r="E179" s="11"/>
@@ -15442,8 +16181,12 @@
       <c r="BW179" s="11"/>
       <c r="BX179" s="11"/>
       <c r="BY179" s="11"/>
-    </row>
-    <row r="180" spans="3:77">
+      <c r="BZ179" s="11"/>
+      <c r="CA179" s="11"/>
+      <c r="CB179" s="11"/>
+      <c r="CC179" s="11"/>
+    </row>
+    <row r="180" spans="3:81">
       <c r="C180" s="11"/>
       <c r="D180" s="11"/>
       <c r="E180" s="11"/>
@@ -15519,8 +16262,12 @@
       <c r="BW180" s="11"/>
       <c r="BX180" s="11"/>
       <c r="BY180" s="11"/>
-    </row>
-    <row r="181" spans="3:77">
+      <c r="BZ180" s="11"/>
+      <c r="CA180" s="11"/>
+      <c r="CB180" s="11"/>
+      <c r="CC180" s="11"/>
+    </row>
+    <row r="181" spans="3:81">
       <c r="C181" s="11"/>
       <c r="D181" s="11"/>
       <c r="E181" s="11"/>
@@ -15596,8 +16343,12 @@
       <c r="BW181" s="11"/>
       <c r="BX181" s="11"/>
       <c r="BY181" s="11"/>
-    </row>
-    <row r="182" spans="3:77">
+      <c r="BZ181" s="11"/>
+      <c r="CA181" s="11"/>
+      <c r="CB181" s="11"/>
+      <c r="CC181" s="11"/>
+    </row>
+    <row r="182" spans="3:81">
       <c r="C182" s="11"/>
       <c r="D182" s="11"/>
       <c r="E182" s="11"/>
@@ -15673,8 +16424,12 @@
       <c r="BW182" s="11"/>
       <c r="BX182" s="11"/>
       <c r="BY182" s="11"/>
-    </row>
-    <row r="183" spans="3:77">
+      <c r="BZ182" s="11"/>
+      <c r="CA182" s="11"/>
+      <c r="CB182" s="11"/>
+      <c r="CC182" s="11"/>
+    </row>
+    <row r="183" spans="3:81">
       <c r="C183" s="11"/>
       <c r="D183" s="11"/>
       <c r="E183" s="11"/>
@@ -15750,8 +16505,12 @@
       <c r="BW183" s="11"/>
       <c r="BX183" s="11"/>
       <c r="BY183" s="11"/>
-    </row>
-    <row r="184" spans="3:77">
+      <c r="BZ183" s="11"/>
+      <c r="CA183" s="11"/>
+      <c r="CB183" s="11"/>
+      <c r="CC183" s="11"/>
+    </row>
+    <row r="184" spans="3:81">
       <c r="C184" s="11"/>
       <c r="D184" s="11"/>
       <c r="E184" s="11"/>
@@ -15827,8 +16586,12 @@
       <c r="BW184" s="11"/>
       <c r="BX184" s="11"/>
       <c r="BY184" s="11"/>
-    </row>
-    <row r="185" spans="3:77">
+      <c r="BZ184" s="11"/>
+      <c r="CA184" s="11"/>
+      <c r="CB184" s="11"/>
+      <c r="CC184" s="11"/>
+    </row>
+    <row r="185" spans="3:81">
       <c r="C185" s="11"/>
       <c r="D185" s="11"/>
       <c r="E185" s="11"/>
@@ -15904,8 +16667,12 @@
       <c r="BW185" s="11"/>
       <c r="BX185" s="11"/>
       <c r="BY185" s="11"/>
-    </row>
-    <row r="186" spans="3:77">
+      <c r="BZ185" s="11"/>
+      <c r="CA185" s="11"/>
+      <c r="CB185" s="11"/>
+      <c r="CC185" s="11"/>
+    </row>
+    <row r="186" spans="3:81">
       <c r="C186" s="11"/>
       <c r="D186" s="11"/>
       <c r="E186" s="11"/>
@@ -15981,8 +16748,12 @@
       <c r="BW186" s="11"/>
       <c r="BX186" s="11"/>
       <c r="BY186" s="11"/>
-    </row>
-    <row r="187" spans="3:77">
+      <c r="BZ186" s="11"/>
+      <c r="CA186" s="11"/>
+      <c r="CB186" s="11"/>
+      <c r="CC186" s="11"/>
+    </row>
+    <row r="187" spans="3:81">
       <c r="C187" s="11"/>
       <c r="D187" s="11"/>
       <c r="E187" s="11"/>
@@ -16058,8 +16829,12 @@
       <c r="BW187" s="11"/>
       <c r="BX187" s="11"/>
       <c r="BY187" s="11"/>
-    </row>
-    <row r="188" spans="3:77">
+      <c r="BZ187" s="11"/>
+      <c r="CA187" s="11"/>
+      <c r="CB187" s="11"/>
+      <c r="CC187" s="11"/>
+    </row>
+    <row r="188" spans="3:81">
       <c r="C188" s="11"/>
       <c r="D188" s="11"/>
       <c r="E188" s="11"/>
@@ -16135,8 +16910,12 @@
       <c r="BW188" s="11"/>
       <c r="BX188" s="11"/>
       <c r="BY188" s="11"/>
-    </row>
-    <row r="189" spans="3:77">
+      <c r="BZ188" s="11"/>
+      <c r="CA188" s="11"/>
+      <c r="CB188" s="11"/>
+      <c r="CC188" s="11"/>
+    </row>
+    <row r="189" spans="3:81">
       <c r="C189" s="11"/>
       <c r="D189" s="11"/>
       <c r="E189" s="11"/>
@@ -16212,8 +16991,12 @@
       <c r="BW189" s="11"/>
       <c r="BX189" s="11"/>
       <c r="BY189" s="11"/>
-    </row>
-    <row r="190" spans="3:77">
+      <c r="BZ189" s="11"/>
+      <c r="CA189" s="11"/>
+      <c r="CB189" s="11"/>
+      <c r="CC189" s="11"/>
+    </row>
+    <row r="190" spans="3:81">
       <c r="C190" s="11"/>
       <c r="D190" s="11"/>
       <c r="E190" s="11"/>
@@ -16289,8 +17072,12 @@
       <c r="BW190" s="11"/>
       <c r="BX190" s="11"/>
       <c r="BY190" s="11"/>
-    </row>
-    <row r="191" spans="3:77">
+      <c r="BZ190" s="11"/>
+      <c r="CA190" s="11"/>
+      <c r="CB190" s="11"/>
+      <c r="CC190" s="11"/>
+    </row>
+    <row r="191" spans="3:81">
       <c r="C191" s="11"/>
       <c r="D191" s="11"/>
       <c r="E191" s="11"/>
@@ -16366,8 +17153,12 @@
       <c r="BW191" s="11"/>
       <c r="BX191" s="11"/>
       <c r="BY191" s="11"/>
-    </row>
-    <row r="192" spans="3:77">
+      <c r="BZ191" s="11"/>
+      <c r="CA191" s="11"/>
+      <c r="CB191" s="11"/>
+      <c r="CC191" s="11"/>
+    </row>
+    <row r="192" spans="3:81">
       <c r="C192" s="11"/>
       <c r="D192" s="11"/>
       <c r="E192" s="11"/>
@@ -16443,8 +17234,12 @@
       <c r="BW192" s="11"/>
       <c r="BX192" s="11"/>
       <c r="BY192" s="11"/>
-    </row>
-    <row r="193" spans="3:77">
+      <c r="BZ192" s="11"/>
+      <c r="CA192" s="11"/>
+      <c r="CB192" s="11"/>
+      <c r="CC192" s="11"/>
+    </row>
+    <row r="193" spans="3:81">
       <c r="C193" s="11"/>
       <c r="D193" s="11"/>
       <c r="E193" s="11"/>
@@ -16520,8 +17315,12 @@
       <c r="BW193" s="11"/>
       <c r="BX193" s="11"/>
       <c r="BY193" s="11"/>
-    </row>
-    <row r="194" spans="3:77">
+      <c r="BZ193" s="11"/>
+      <c r="CA193" s="11"/>
+      <c r="CB193" s="11"/>
+      <c r="CC193" s="11"/>
+    </row>
+    <row r="194" spans="3:81">
       <c r="C194" s="11"/>
       <c r="D194" s="11"/>
       <c r="E194" s="11"/>
@@ -16597,8 +17396,12 @@
       <c r="BW194" s="11"/>
       <c r="BX194" s="11"/>
       <c r="BY194" s="11"/>
-    </row>
-    <row r="195" spans="3:77">
+      <c r="BZ194" s="11"/>
+      <c r="CA194" s="11"/>
+      <c r="CB194" s="11"/>
+      <c r="CC194" s="11"/>
+    </row>
+    <row r="195" spans="3:81">
       <c r="C195" s="11"/>
       <c r="D195" s="11"/>
       <c r="E195" s="11"/>
@@ -16674,8 +17477,12 @@
       <c r="BW195" s="11"/>
       <c r="BX195" s="11"/>
       <c r="BY195" s="11"/>
-    </row>
-    <row r="196" spans="3:77">
+      <c r="BZ195" s="11"/>
+      <c r="CA195" s="11"/>
+      <c r="CB195" s="11"/>
+      <c r="CC195" s="11"/>
+    </row>
+    <row r="196" spans="3:81">
       <c r="C196" s="11"/>
       <c r="D196" s="11"/>
       <c r="E196" s="11"/>
@@ -16751,8 +17558,12 @@
       <c r="BW196" s="11"/>
       <c r="BX196" s="11"/>
       <c r="BY196" s="11"/>
-    </row>
-    <row r="197" spans="3:77">
+      <c r="BZ196" s="11"/>
+      <c r="CA196" s="11"/>
+      <c r="CB196" s="11"/>
+      <c r="CC196" s="11"/>
+    </row>
+    <row r="197" spans="3:81">
       <c r="C197" s="11"/>
       <c r="D197" s="11"/>
       <c r="E197" s="11"/>
@@ -16828,8 +17639,12 @@
       <c r="BW197" s="11"/>
       <c r="BX197" s="11"/>
       <c r="BY197" s="11"/>
-    </row>
-    <row r="198" spans="3:77">
+      <c r="BZ197" s="11"/>
+      <c r="CA197" s="11"/>
+      <c r="CB197" s="11"/>
+      <c r="CC197" s="11"/>
+    </row>
+    <row r="198" spans="3:81">
       <c r="C198" s="11"/>
       <c r="D198" s="11"/>
       <c r="E198" s="11"/>
@@ -16905,8 +17720,12 @@
       <c r="BW198" s="11"/>
       <c r="BX198" s="11"/>
       <c r="BY198" s="11"/>
-    </row>
-    <row r="199" spans="3:77">
+      <c r="BZ198" s="11"/>
+      <c r="CA198" s="11"/>
+      <c r="CB198" s="11"/>
+      <c r="CC198" s="11"/>
+    </row>
+    <row r="199" spans="3:81">
       <c r="C199" s="11"/>
       <c r="D199" s="11"/>
       <c r="E199" s="11"/>
@@ -16982,8 +17801,12 @@
       <c r="BW199" s="11"/>
       <c r="BX199" s="11"/>
       <c r="BY199" s="11"/>
-    </row>
-    <row r="200" spans="3:77">
+      <c r="BZ199" s="11"/>
+      <c r="CA199" s="11"/>
+      <c r="CB199" s="11"/>
+      <c r="CC199" s="11"/>
+    </row>
+    <row r="200" spans="3:81">
       <c r="C200" s="11"/>
       <c r="D200" s="11"/>
       <c r="E200" s="11"/>
@@ -17059,8 +17882,12 @@
       <c r="BW200" s="11"/>
       <c r="BX200" s="11"/>
       <c r="BY200" s="11"/>
-    </row>
-    <row r="201" spans="3:77">
+      <c r="BZ200" s="11"/>
+      <c r="CA200" s="11"/>
+      <c r="CB200" s="11"/>
+      <c r="CC200" s="11"/>
+    </row>
+    <row r="201" spans="3:81">
       <c r="C201" s="11"/>
       <c r="D201" s="11"/>
       <c r="E201" s="11"/>
@@ -17136,8 +17963,12 @@
       <c r="BW201" s="11"/>
       <c r="BX201" s="11"/>
       <c r="BY201" s="11"/>
-    </row>
-    <row r="202" spans="3:77">
+      <c r="BZ201" s="11"/>
+      <c r="CA201" s="11"/>
+      <c r="CB201" s="11"/>
+      <c r="CC201" s="11"/>
+    </row>
+    <row r="202" spans="3:81">
       <c r="C202" s="11"/>
       <c r="D202" s="11"/>
       <c r="E202" s="11"/>
@@ -17213,8 +18044,12 @@
       <c r="BW202" s="11"/>
       <c r="BX202" s="11"/>
       <c r="BY202" s="11"/>
-    </row>
-    <row r="203" spans="3:77">
+      <c r="BZ202" s="11"/>
+      <c r="CA202" s="11"/>
+      <c r="CB202" s="11"/>
+      <c r="CC202" s="11"/>
+    </row>
+    <row r="203" spans="3:81">
       <c r="C203" s="11"/>
       <c r="D203" s="11"/>
       <c r="E203" s="11"/>
@@ -17290,8 +18125,12 @@
       <c r="BW203" s="11"/>
       <c r="BX203" s="11"/>
       <c r="BY203" s="11"/>
-    </row>
-    <row r="204" spans="3:77">
+      <c r="BZ203" s="11"/>
+      <c r="CA203" s="11"/>
+      <c r="CB203" s="11"/>
+      <c r="CC203" s="11"/>
+    </row>
+    <row r="204" spans="3:81">
       <c r="C204" s="11"/>
       <c r="D204" s="11"/>
       <c r="E204" s="11"/>
@@ -17367,8 +18206,12 @@
       <c r="BW204" s="11"/>
       <c r="BX204" s="11"/>
       <c r="BY204" s="11"/>
-    </row>
-    <row r="205" spans="3:77">
+      <c r="BZ204" s="11"/>
+      <c r="CA204" s="11"/>
+      <c r="CB204" s="11"/>
+      <c r="CC204" s="11"/>
+    </row>
+    <row r="205" spans="3:81">
       <c r="C205" s="11"/>
       <c r="D205" s="11"/>
       <c r="E205" s="11"/>
@@ -17444,8 +18287,12 @@
       <c r="BW205" s="11"/>
       <c r="BX205" s="11"/>
       <c r="BY205" s="11"/>
-    </row>
-    <row r="206" spans="3:77">
+      <c r="BZ205" s="11"/>
+      <c r="CA205" s="11"/>
+      <c r="CB205" s="11"/>
+      <c r="CC205" s="11"/>
+    </row>
+    <row r="206" spans="3:81">
       <c r="C206" s="11"/>
       <c r="D206" s="11"/>
       <c r="E206" s="11"/>
@@ -17521,8 +18368,12 @@
       <c r="BW206" s="11"/>
       <c r="BX206" s="11"/>
       <c r="BY206" s="11"/>
-    </row>
-    <row r="207" spans="3:77">
+      <c r="BZ206" s="11"/>
+      <c r="CA206" s="11"/>
+      <c r="CB206" s="11"/>
+      <c r="CC206" s="11"/>
+    </row>
+    <row r="207" spans="3:81">
       <c r="C207" s="11"/>
       <c r="D207" s="11"/>
       <c r="E207" s="11"/>
@@ -17598,8 +18449,12 @@
       <c r="BW207" s="11"/>
       <c r="BX207" s="11"/>
       <c r="BY207" s="11"/>
-    </row>
-    <row r="208" spans="3:77">
+      <c r="BZ207" s="11"/>
+      <c r="CA207" s="11"/>
+      <c r="CB207" s="11"/>
+      <c r="CC207" s="11"/>
+    </row>
+    <row r="208" spans="3:81">
       <c r="C208" s="11"/>
       <c r="D208" s="11"/>
       <c r="E208" s="11"/>
@@ -17675,8 +18530,12 @@
       <c r="BW208" s="11"/>
       <c r="BX208" s="11"/>
       <c r="BY208" s="11"/>
-    </row>
-    <row r="209" spans="3:77">
+      <c r="BZ208" s="11"/>
+      <c r="CA208" s="11"/>
+      <c r="CB208" s="11"/>
+      <c r="CC208" s="11"/>
+    </row>
+    <row r="209" spans="3:81">
       <c r="C209" s="11"/>
       <c r="D209" s="11"/>
       <c r="E209" s="11"/>
@@ -17752,8 +18611,12 @@
       <c r="BW209" s="11"/>
       <c r="BX209" s="11"/>
       <c r="BY209" s="11"/>
-    </row>
-    <row r="210" spans="3:77">
+      <c r="BZ209" s="11"/>
+      <c r="CA209" s="11"/>
+      <c r="CB209" s="11"/>
+      <c r="CC209" s="11"/>
+    </row>
+    <row r="210" spans="3:81">
       <c r="C210" s="11"/>
       <c r="D210" s="11"/>
       <c r="E210" s="11"/>
@@ -17829,8 +18692,12 @@
       <c r="BW210" s="11"/>
       <c r="BX210" s="11"/>
       <c r="BY210" s="11"/>
-    </row>
-    <row r="211" spans="3:77">
+      <c r="BZ210" s="11"/>
+      <c r="CA210" s="11"/>
+      <c r="CB210" s="11"/>
+      <c r="CC210" s="11"/>
+    </row>
+    <row r="211" spans="3:81">
       <c r="C211" s="11"/>
       <c r="D211" s="11"/>
       <c r="E211" s="11"/>
@@ -17906,8 +18773,12 @@
       <c r="BW211" s="11"/>
       <c r="BX211" s="11"/>
       <c r="BY211" s="11"/>
-    </row>
-    <row r="212" spans="3:77">
+      <c r="BZ211" s="11"/>
+      <c r="CA211" s="11"/>
+      <c r="CB211" s="11"/>
+      <c r="CC211" s="11"/>
+    </row>
+    <row r="212" spans="3:81">
       <c r="C212" s="11"/>
       <c r="D212" s="11"/>
       <c r="E212" s="11"/>
@@ -17983,8 +18854,12 @@
       <c r="BW212" s="11"/>
       <c r="BX212" s="11"/>
       <c r="BY212" s="11"/>
-    </row>
-    <row r="213" spans="3:77">
+      <c r="BZ212" s="11"/>
+      <c r="CA212" s="11"/>
+      <c r="CB212" s="11"/>
+      <c r="CC212" s="11"/>
+    </row>
+    <row r="213" spans="3:81">
       <c r="C213" s="11"/>
       <c r="D213" s="11"/>
       <c r="E213" s="11"/>
@@ -18060,8 +18935,12 @@
       <c r="BW213" s="11"/>
       <c r="BX213" s="11"/>
       <c r="BY213" s="11"/>
-    </row>
-    <row r="214" spans="3:77">
+      <c r="BZ213" s="11"/>
+      <c r="CA213" s="11"/>
+      <c r="CB213" s="11"/>
+      <c r="CC213" s="11"/>
+    </row>
+    <row r="214" spans="3:81">
       <c r="C214" s="11"/>
       <c r="D214" s="11"/>
       <c r="E214" s="11"/>
@@ -18137,8 +19016,12 @@
       <c r="BW214" s="11"/>
       <c r="BX214" s="11"/>
       <c r="BY214" s="11"/>
-    </row>
-    <row r="215" spans="3:77">
+      <c r="BZ214" s="11"/>
+      <c r="CA214" s="11"/>
+      <c r="CB214" s="11"/>
+      <c r="CC214" s="11"/>
+    </row>
+    <row r="215" spans="3:81">
       <c r="C215" s="11"/>
       <c r="D215" s="11"/>
       <c r="E215" s="11"/>
@@ -18214,8 +19097,12 @@
       <c r="BW215" s="11"/>
       <c r="BX215" s="11"/>
       <c r="BY215" s="11"/>
-    </row>
-    <row r="216" spans="3:77">
+      <c r="BZ215" s="11"/>
+      <c r="CA215" s="11"/>
+      <c r="CB215" s="11"/>
+      <c r="CC215" s="11"/>
+    </row>
+    <row r="216" spans="3:81">
       <c r="C216" s="11"/>
       <c r="D216" s="11"/>
       <c r="E216" s="11"/>
@@ -18291,8 +19178,12 @@
       <c r="BW216" s="11"/>
       <c r="BX216" s="11"/>
       <c r="BY216" s="11"/>
-    </row>
-    <row r="217" spans="3:77">
+      <c r="BZ216" s="11"/>
+      <c r="CA216" s="11"/>
+      <c r="CB216" s="11"/>
+      <c r="CC216" s="11"/>
+    </row>
+    <row r="217" spans="3:81">
       <c r="C217" s="11"/>
       <c r="D217" s="11"/>
       <c r="E217" s="11"/>
@@ -18368,8 +19259,12 @@
       <c r="BW217" s="11"/>
       <c r="BX217" s="11"/>
       <c r="BY217" s="11"/>
-    </row>
-    <row r="218" spans="3:77">
+      <c r="BZ217" s="11"/>
+      <c r="CA217" s="11"/>
+      <c r="CB217" s="11"/>
+      <c r="CC217" s="11"/>
+    </row>
+    <row r="218" spans="3:81">
       <c r="C218" s="11"/>
       <c r="D218" s="11"/>
       <c r="E218" s="11"/>
@@ -18445,8 +19340,12 @@
       <c r="BW218" s="11"/>
       <c r="BX218" s="11"/>
       <c r="BY218" s="11"/>
-    </row>
-    <row r="219" spans="3:77">
+      <c r="BZ218" s="11"/>
+      <c r="CA218" s="11"/>
+      <c r="CB218" s="11"/>
+      <c r="CC218" s="11"/>
+    </row>
+    <row r="219" spans="3:81">
       <c r="C219" s="11"/>
       <c r="D219" s="11"/>
       <c r="E219" s="11"/>
@@ -18522,8 +19421,12 @@
       <c r="BW219" s="11"/>
       <c r="BX219" s="11"/>
       <c r="BY219" s="11"/>
-    </row>
-    <row r="220" spans="3:77">
+      <c r="BZ219" s="11"/>
+      <c r="CA219" s="11"/>
+      <c r="CB219" s="11"/>
+      <c r="CC219" s="11"/>
+    </row>
+    <row r="220" spans="3:81">
       <c r="C220" s="11"/>
       <c r="D220" s="11"/>
       <c r="E220" s="11"/>
@@ -18599,8 +19502,12 @@
       <c r="BW220" s="11"/>
       <c r="BX220" s="11"/>
       <c r="BY220" s="11"/>
-    </row>
-    <row r="221" spans="3:77">
+      <c r="BZ220" s="11"/>
+      <c r="CA220" s="11"/>
+      <c r="CB220" s="11"/>
+      <c r="CC220" s="11"/>
+    </row>
+    <row r="221" spans="3:81">
       <c r="C221" s="11"/>
       <c r="D221" s="11"/>
       <c r="E221" s="11"/>
@@ -18676,8 +19583,12 @@
       <c r="BW221" s="11"/>
       <c r="BX221" s="11"/>
       <c r="BY221" s="11"/>
-    </row>
-    <row r="222" spans="3:77">
+      <c r="BZ221" s="11"/>
+      <c r="CA221" s="11"/>
+      <c r="CB221" s="11"/>
+      <c r="CC221" s="11"/>
+    </row>
+    <row r="222" spans="3:81">
       <c r="C222" s="11"/>
       <c r="D222" s="11"/>
       <c r="E222" s="11"/>
@@ -18753,8 +19664,12 @@
       <c r="BW222" s="11"/>
       <c r="BX222" s="11"/>
       <c r="BY222" s="11"/>
-    </row>
-    <row r="223" spans="3:77">
+      <c r="BZ222" s="11"/>
+      <c r="CA222" s="11"/>
+      <c r="CB222" s="11"/>
+      <c r="CC222" s="11"/>
+    </row>
+    <row r="223" spans="3:81">
       <c r="C223" s="11"/>
       <c r="D223" s="11"/>
       <c r="E223" s="11"/>
@@ -18830,8 +19745,12 @@
       <c r="BW223" s="11"/>
       <c r="BX223" s="11"/>
       <c r="BY223" s="11"/>
-    </row>
-    <row r="224" spans="3:77">
+      <c r="BZ223" s="11"/>
+      <c r="CA223" s="11"/>
+      <c r="CB223" s="11"/>
+      <c r="CC223" s="11"/>
+    </row>
+    <row r="224" spans="3:81">
       <c r="C224" s="11"/>
       <c r="D224" s="11"/>
       <c r="E224" s="11"/>
@@ -18907,8 +19826,12 @@
       <c r="BW224" s="11"/>
       <c r="BX224" s="11"/>
       <c r="BY224" s="11"/>
-    </row>
-    <row r="225" spans="3:77">
+      <c r="BZ224" s="11"/>
+      <c r="CA224" s="11"/>
+      <c r="CB224" s="11"/>
+      <c r="CC224" s="11"/>
+    </row>
+    <row r="225" spans="3:81">
       <c r="C225" s="11"/>
       <c r="D225" s="11"/>
       <c r="E225" s="11"/>
@@ -18984,8 +19907,12 @@
       <c r="BW225" s="11"/>
       <c r="BX225" s="11"/>
       <c r="BY225" s="11"/>
-    </row>
-    <row r="226" spans="3:77">
+      <c r="BZ225" s="11"/>
+      <c r="CA225" s="11"/>
+      <c r="CB225" s="11"/>
+      <c r="CC225" s="11"/>
+    </row>
+    <row r="226" spans="3:81">
       <c r="C226" s="11"/>
       <c r="D226" s="11"/>
       <c r="E226" s="11"/>
@@ -19061,8 +19988,12 @@
       <c r="BW226" s="11"/>
       <c r="BX226" s="11"/>
       <c r="BY226" s="11"/>
-    </row>
-    <row r="227" spans="3:77">
+      <c r="BZ226" s="11"/>
+      <c r="CA226" s="11"/>
+      <c r="CB226" s="11"/>
+      <c r="CC226" s="11"/>
+    </row>
+    <row r="227" spans="3:81">
       <c r="C227" s="11"/>
       <c r="D227" s="11"/>
       <c r="E227" s="11"/>
@@ -19138,8 +20069,12 @@
       <c r="BW227" s="11"/>
       <c r="BX227" s="11"/>
       <c r="BY227" s="11"/>
-    </row>
-    <row r="228" spans="3:77">
+      <c r="BZ227" s="11"/>
+      <c r="CA227" s="11"/>
+      <c r="CB227" s="11"/>
+      <c r="CC227" s="11"/>
+    </row>
+    <row r="228" spans="3:81">
       <c r="C228" s="11"/>
       <c r="D228" s="11"/>
       <c r="E228" s="11"/>
@@ -19215,8 +20150,12 @@
       <c r="BW228" s="11"/>
       <c r="BX228" s="11"/>
       <c r="BY228" s="11"/>
-    </row>
-    <row r="229" spans="3:77">
+      <c r="BZ228" s="11"/>
+      <c r="CA228" s="11"/>
+      <c r="CB228" s="11"/>
+      <c r="CC228" s="11"/>
+    </row>
+    <row r="229" spans="3:81">
       <c r="C229" s="11"/>
       <c r="D229" s="11"/>
       <c r="E229" s="11"/>
@@ -19292,8 +20231,12 @@
       <c r="BW229" s="11"/>
       <c r="BX229" s="11"/>
       <c r="BY229" s="11"/>
-    </row>
-    <row r="230" spans="3:77">
+      <c r="BZ229" s="11"/>
+      <c r="CA229" s="11"/>
+      <c r="CB229" s="11"/>
+      <c r="CC229" s="11"/>
+    </row>
+    <row r="230" spans="3:81">
       <c r="C230" s="11"/>
       <c r="D230" s="11"/>
       <c r="E230" s="11"/>
@@ -19369,8 +20312,12 @@
       <c r="BW230" s="11"/>
       <c r="BX230" s="11"/>
       <c r="BY230" s="11"/>
-    </row>
-    <row r="231" spans="3:77">
+      <c r="BZ230" s="11"/>
+      <c r="CA230" s="11"/>
+      <c r="CB230" s="11"/>
+      <c r="CC230" s="11"/>
+    </row>
+    <row r="231" spans="3:81">
       <c r="C231" s="11"/>
       <c r="D231" s="11"/>
       <c r="E231" s="11"/>
@@ -19446,8 +20393,12 @@
       <c r="BW231" s="11"/>
       <c r="BX231" s="11"/>
       <c r="BY231" s="11"/>
-    </row>
-    <row r="232" spans="3:77">
+      <c r="BZ231" s="11"/>
+      <c r="CA231" s="11"/>
+      <c r="CB231" s="11"/>
+      <c r="CC231" s="11"/>
+    </row>
+    <row r="232" spans="3:81">
       <c r="C232" s="11"/>
       <c r="D232" s="11"/>
       <c r="E232" s="11"/>
@@ -19523,8 +20474,12 @@
       <c r="BW232" s="11"/>
       <c r="BX232" s="11"/>
       <c r="BY232" s="11"/>
-    </row>
-    <row r="233" spans="3:77">
+      <c r="BZ232" s="11"/>
+      <c r="CA232" s="11"/>
+      <c r="CB232" s="11"/>
+      <c r="CC232" s="11"/>
+    </row>
+    <row r="233" spans="3:81">
       <c r="C233" s="11"/>
       <c r="D233" s="11"/>
       <c r="E233" s="11"/>
@@ -19600,8 +20555,12 @@
       <c r="BW233" s="11"/>
       <c r="BX233" s="11"/>
       <c r="BY233" s="11"/>
-    </row>
-    <row r="234" spans="3:77">
+      <c r="BZ233" s="11"/>
+      <c r="CA233" s="11"/>
+      <c r="CB233" s="11"/>
+      <c r="CC233" s="11"/>
+    </row>
+    <row r="234" spans="3:81">
       <c r="C234" s="11"/>
       <c r="D234" s="11"/>
       <c r="E234" s="11"/>
@@ -19677,8 +20636,12 @@
       <c r="BW234" s="11"/>
       <c r="BX234" s="11"/>
       <c r="BY234" s="11"/>
-    </row>
-    <row r="235" spans="3:77">
+      <c r="BZ234" s="11"/>
+      <c r="CA234" s="11"/>
+      <c r="CB234" s="11"/>
+      <c r="CC234" s="11"/>
+    </row>
+    <row r="235" spans="3:81">
       <c r="C235" s="11"/>
       <c r="D235" s="11"/>
       <c r="E235" s="11"/>
@@ -19754,8 +20717,12 @@
       <c r="BW235" s="11"/>
       <c r="BX235" s="11"/>
       <c r="BY235" s="11"/>
-    </row>
-    <row r="236" spans="3:77">
+      <c r="BZ235" s="11"/>
+      <c r="CA235" s="11"/>
+      <c r="CB235" s="11"/>
+      <c r="CC235" s="11"/>
+    </row>
+    <row r="236" spans="3:81">
       <c r="C236" s="11"/>
       <c r="D236" s="11"/>
       <c r="E236" s="11"/>
@@ -19831,8 +20798,12 @@
       <c r="BW236" s="11"/>
       <c r="BX236" s="11"/>
       <c r="BY236" s="11"/>
-    </row>
-    <row r="237" spans="3:77">
+      <c r="BZ236" s="11"/>
+      <c r="CA236" s="11"/>
+      <c r="CB236" s="11"/>
+      <c r="CC236" s="11"/>
+    </row>
+    <row r="237" spans="3:81">
       <c r="C237" s="11"/>
       <c r="D237" s="11"/>
       <c r="E237" s="11"/>
@@ -19908,8 +20879,12 @@
       <c r="BW237" s="11"/>
       <c r="BX237" s="11"/>
       <c r="BY237" s="11"/>
-    </row>
-    <row r="238" spans="3:77">
+      <c r="BZ237" s="11"/>
+      <c r="CA237" s="11"/>
+      <c r="CB237" s="11"/>
+      <c r="CC237" s="11"/>
+    </row>
+    <row r="238" spans="3:81">
       <c r="C238" s="11"/>
       <c r="D238" s="11"/>
       <c r="E238" s="11"/>
@@ -19985,8 +20960,12 @@
       <c r="BW238" s="11"/>
       <c r="BX238" s="11"/>
       <c r="BY238" s="11"/>
-    </row>
-    <row r="239" spans="3:77">
+      <c r="BZ238" s="11"/>
+      <c r="CA238" s="11"/>
+      <c r="CB238" s="11"/>
+      <c r="CC238" s="11"/>
+    </row>
+    <row r="239" spans="3:81">
       <c r="C239" s="11"/>
       <c r="D239" s="11"/>
       <c r="E239" s="11"/>
@@ -20062,8 +21041,12 @@
       <c r="BW239" s="11"/>
       <c r="BX239" s="11"/>
       <c r="BY239" s="11"/>
-    </row>
-    <row r="240" spans="3:77">
+      <c r="BZ239" s="11"/>
+      <c r="CA239" s="11"/>
+      <c r="CB239" s="11"/>
+      <c r="CC239" s="11"/>
+    </row>
+    <row r="240" spans="3:81">
       <c r="C240" s="11"/>
       <c r="D240" s="11"/>
       <c r="E240" s="11"/>
@@ -20139,8 +21122,12 @@
       <c r="BW240" s="11"/>
       <c r="BX240" s="11"/>
       <c r="BY240" s="11"/>
-    </row>
-    <row r="241" spans="3:77">
+      <c r="BZ240" s="11"/>
+      <c r="CA240" s="11"/>
+      <c r="CB240" s="11"/>
+      <c r="CC240" s="11"/>
+    </row>
+    <row r="241" spans="3:81">
       <c r="C241" s="11"/>
       <c r="D241" s="11"/>
       <c r="E241" s="11"/>
@@ -20216,8 +21203,12 @@
       <c r="BW241" s="11"/>
       <c r="BX241" s="11"/>
       <c r="BY241" s="11"/>
-    </row>
-    <row r="242" spans="3:77">
+      <c r="BZ241" s="11"/>
+      <c r="CA241" s="11"/>
+      <c r="CB241" s="11"/>
+      <c r="CC241" s="11"/>
+    </row>
+    <row r="242" spans="3:81">
       <c r="C242" s="11"/>
       <c r="D242" s="11"/>
       <c r="E242" s="11"/>
@@ -20293,8 +21284,12 @@
       <c r="BW242" s="11"/>
       <c r="BX242" s="11"/>
       <c r="BY242" s="11"/>
-    </row>
-    <row r="243" spans="3:77">
+      <c r="BZ242" s="11"/>
+      <c r="CA242" s="11"/>
+      <c r="CB242" s="11"/>
+      <c r="CC242" s="11"/>
+    </row>
+    <row r="243" spans="3:81">
       <c r="C243" s="11"/>
       <c r="D243" s="11"/>
       <c r="E243" s="11"/>
@@ -20370,8 +21365,12 @@
       <c r="BW243" s="11"/>
       <c r="BX243" s="11"/>
       <c r="BY243" s="11"/>
-    </row>
-    <row r="244" spans="3:77">
+      <c r="BZ243" s="11"/>
+      <c r="CA243" s="11"/>
+      <c r="CB243" s="11"/>
+      <c r="CC243" s="11"/>
+    </row>
+    <row r="244" spans="3:81">
       <c r="C244" s="11"/>
       <c r="D244" s="11"/>
       <c r="E244" s="11"/>
@@ -20447,8 +21446,12 @@
       <c r="BW244" s="11"/>
       <c r="BX244" s="11"/>
       <c r="BY244" s="11"/>
-    </row>
-    <row r="245" spans="3:77">
+      <c r="BZ244" s="11"/>
+      <c r="CA244" s="11"/>
+      <c r="CB244" s="11"/>
+      <c r="CC244" s="11"/>
+    </row>
+    <row r="245" spans="3:81">
       <c r="C245" s="11"/>
       <c r="D245" s="11"/>
       <c r="E245" s="11"/>
@@ -20524,8 +21527,12 @@
       <c r="BW245" s="11"/>
       <c r="BX245" s="11"/>
       <c r="BY245" s="11"/>
-    </row>
-    <row r="246" spans="3:77">
+      <c r="BZ245" s="11"/>
+      <c r="CA245" s="11"/>
+      <c r="CB245" s="11"/>
+      <c r="CC245" s="11"/>
+    </row>
+    <row r="246" spans="3:81">
       <c r="C246" s="11"/>
       <c r="D246" s="11"/>
       <c r="E246" s="11"/>
@@ -20601,8 +21608,12 @@
       <c r="BW246" s="11"/>
       <c r="BX246" s="11"/>
       <c r="BY246" s="11"/>
-    </row>
-    <row r="247" spans="3:77">
+      <c r="BZ246" s="11"/>
+      <c r="CA246" s="11"/>
+      <c r="CB246" s="11"/>
+      <c r="CC246" s="11"/>
+    </row>
+    <row r="247" spans="3:81">
       <c r="C247" s="11"/>
       <c r="D247" s="11"/>
       <c r="E247" s="11"/>
@@ -20678,8 +21689,12 @@
       <c r="BW247" s="11"/>
       <c r="BX247" s="11"/>
       <c r="BY247" s="11"/>
-    </row>
-    <row r="248" spans="3:77">
+      <c r="BZ247" s="11"/>
+      <c r="CA247" s="11"/>
+      <c r="CB247" s="11"/>
+      <c r="CC247" s="11"/>
+    </row>
+    <row r="248" spans="3:81">
       <c r="C248" s="11"/>
       <c r="D248" s="11"/>
       <c r="E248" s="11"/>
@@ -20755,8 +21770,12 @@
       <c r="BW248" s="11"/>
       <c r="BX248" s="11"/>
       <c r="BY248" s="11"/>
-    </row>
-    <row r="249" spans="3:77">
+      <c r="BZ248" s="11"/>
+      <c r="CA248" s="11"/>
+      <c r="CB248" s="11"/>
+      <c r="CC248" s="11"/>
+    </row>
+    <row r="249" spans="3:81">
       <c r="C249" s="11"/>
       <c r="D249" s="11"/>
       <c r="E249" s="11"/>
@@ -20832,8 +21851,12 @@
       <c r="BW249" s="11"/>
       <c r="BX249" s="11"/>
       <c r="BY249" s="11"/>
-    </row>
-    <row r="250" spans="3:77">
+      <c r="BZ249" s="11"/>
+      <c r="CA249" s="11"/>
+      <c r="CB249" s="11"/>
+      <c r="CC249" s="11"/>
+    </row>
+    <row r="250" spans="3:81">
       <c r="C250" s="11"/>
       <c r="D250" s="11"/>
       <c r="E250" s="11"/>
@@ -20909,8 +21932,12 @@
       <c r="BW250" s="11"/>
       <c r="BX250" s="11"/>
       <c r="BY250" s="11"/>
-    </row>
-    <row r="251" spans="3:77">
+      <c r="BZ250" s="11"/>
+      <c r="CA250" s="11"/>
+      <c r="CB250" s="11"/>
+      <c r="CC250" s="11"/>
+    </row>
+    <row r="251" spans="3:81">
       <c r="C251" s="11"/>
       <c r="D251" s="11"/>
       <c r="E251" s="11"/>
@@ -20986,8 +22013,12 @@
       <c r="BW251" s="11"/>
       <c r="BX251" s="11"/>
       <c r="BY251" s="11"/>
-    </row>
-    <row r="252" spans="3:77">
+      <c r="BZ251" s="11"/>
+      <c r="CA251" s="11"/>
+      <c r="CB251" s="11"/>
+      <c r="CC251" s="11"/>
+    </row>
+    <row r="252" spans="3:81">
       <c r="C252" s="11"/>
       <c r="D252" s="11"/>
       <c r="E252" s="11"/>
@@ -21063,8 +22094,12 @@
       <c r="BW252" s="11"/>
       <c r="BX252" s="11"/>
       <c r="BY252" s="11"/>
-    </row>
-    <row r="253" spans="3:77">
+      <c r="BZ252" s="11"/>
+      <c r="CA252" s="11"/>
+      <c r="CB252" s="11"/>
+      <c r="CC252" s="11"/>
+    </row>
+    <row r="253" spans="3:81">
       <c r="C253" s="11"/>
       <c r="D253" s="11"/>
       <c r="E253" s="11"/>
@@ -21140,8 +22175,12 @@
       <c r="BW253" s="11"/>
       <c r="BX253" s="11"/>
       <c r="BY253" s="11"/>
-    </row>
-    <row r="254" spans="3:77">
+      <c r="BZ253" s="11"/>
+      <c r="CA253" s="11"/>
+      <c r="CB253" s="11"/>
+      <c r="CC253" s="11"/>
+    </row>
+    <row r="254" spans="3:81">
       <c r="C254" s="11"/>
       <c r="D254" s="11"/>
       <c r="E254" s="11"/>
@@ -21217,8 +22256,12 @@
       <c r="BW254" s="11"/>
       <c r="BX254" s="11"/>
       <c r="BY254" s="11"/>
-    </row>
-    <row r="255" spans="3:77">
+      <c r="BZ254" s="11"/>
+      <c r="CA254" s="11"/>
+      <c r="CB254" s="11"/>
+      <c r="CC254" s="11"/>
+    </row>
+    <row r="255" spans="3:81">
       <c r="C255" s="11"/>
       <c r="D255" s="11"/>
       <c r="E255" s="11"/>
@@ -21294,8 +22337,12 @@
       <c r="BW255" s="11"/>
       <c r="BX255" s="11"/>
       <c r="BY255" s="11"/>
-    </row>
-    <row r="256" spans="3:77">
+      <c r="BZ255" s="11"/>
+      <c r="CA255" s="11"/>
+      <c r="CB255" s="11"/>
+      <c r="CC255" s="11"/>
+    </row>
+    <row r="256" spans="3:81">
       <c r="C256" s="11"/>
       <c r="D256" s="11"/>
       <c r="E256" s="11"/>
@@ -21371,8 +22418,12 @@
       <c r="BW256" s="11"/>
       <c r="BX256" s="11"/>
       <c r="BY256" s="11"/>
-    </row>
-    <row r="257" spans="3:77">
+      <c r="BZ256" s="11"/>
+      <c r="CA256" s="11"/>
+      <c r="CB256" s="11"/>
+      <c r="CC256" s="11"/>
+    </row>
+    <row r="257" spans="3:81">
       <c r="C257" s="11"/>
       <c r="D257" s="11"/>
       <c r="E257" s="11"/>
@@ -21448,8 +22499,12 @@
       <c r="BW257" s="11"/>
       <c r="BX257" s="11"/>
       <c r="BY257" s="11"/>
-    </row>
-    <row r="258" spans="3:77">
+      <c r="BZ257" s="11"/>
+      <c r="CA257" s="11"/>
+      <c r="CB257" s="11"/>
+      <c r="CC257" s="11"/>
+    </row>
+    <row r="258" spans="3:81">
       <c r="C258" s="11"/>
       <c r="D258" s="11"/>
       <c r="E258" s="11"/>
@@ -21525,8 +22580,12 @@
       <c r="BW258" s="11"/>
       <c r="BX258" s="11"/>
       <c r="BY258" s="11"/>
-    </row>
-    <row r="259" spans="3:77">
+      <c r="BZ258" s="11"/>
+      <c r="CA258" s="11"/>
+      <c r="CB258" s="11"/>
+      <c r="CC258" s="11"/>
+    </row>
+    <row r="259" spans="3:81">
       <c r="C259" s="11"/>
       <c r="D259" s="11"/>
       <c r="E259" s="11"/>
@@ -21602,8 +22661,12 @@
       <c r="BW259" s="11"/>
       <c r="BX259" s="11"/>
       <c r="BY259" s="11"/>
-    </row>
-    <row r="260" spans="3:77">
+      <c r="BZ259" s="11"/>
+      <c r="CA259" s="11"/>
+      <c r="CB259" s="11"/>
+      <c r="CC259" s="11"/>
+    </row>
+    <row r="260" spans="3:81">
       <c r="C260" s="11"/>
       <c r="D260" s="11"/>
       <c r="E260" s="11"/>
@@ -21679,8 +22742,12 @@
       <c r="BW260" s="11"/>
       <c r="BX260" s="11"/>
       <c r="BY260" s="11"/>
-    </row>
-    <row r="261" spans="3:77">
+      <c r="BZ260" s="11"/>
+      <c r="CA260" s="11"/>
+      <c r="CB260" s="11"/>
+      <c r="CC260" s="11"/>
+    </row>
+    <row r="261" spans="3:81">
       <c r="C261" s="11"/>
       <c r="D261" s="11"/>
       <c r="E261" s="11"/>
@@ -21756,8 +22823,12 @@
       <c r="BW261" s="11"/>
       <c r="BX261" s="11"/>
       <c r="BY261" s="11"/>
-    </row>
-    <row r="262" spans="3:77">
+      <c r="BZ261" s="11"/>
+      <c r="CA261" s="11"/>
+      <c r="CB261" s="11"/>
+      <c r="CC261" s="11"/>
+    </row>
+    <row r="262" spans="3:81">
       <c r="C262" s="11"/>
       <c r="D262" s="11"/>
       <c r="E262" s="11"/>
@@ -21833,8 +22904,12 @@
       <c r="BW262" s="11"/>
       <c r="BX262" s="11"/>
       <c r="BY262" s="11"/>
-    </row>
-    <row r="263" spans="3:77">
+      <c r="BZ262" s="11"/>
+      <c r="CA262" s="11"/>
+      <c r="CB262" s="11"/>
+      <c r="CC262" s="11"/>
+    </row>
+    <row r="263" spans="3:81">
       <c r="C263" s="11"/>
       <c r="D263" s="11"/>
       <c r="E263" s="11"/>
@@ -21910,8 +22985,12 @@
       <c r="BW263" s="11"/>
       <c r="BX263" s="11"/>
       <c r="BY263" s="11"/>
-    </row>
-    <row r="264" spans="3:77">
+      <c r="BZ263" s="11"/>
+      <c r="CA263" s="11"/>
+      <c r="CB263" s="11"/>
+      <c r="CC263" s="11"/>
+    </row>
+    <row r="264" spans="3:81">
       <c r="C264" s="11"/>
       <c r="D264" s="11"/>
       <c r="E264" s="11"/>
@@ -21987,8 +23066,12 @@
       <c r="BW264" s="11"/>
       <c r="BX264" s="11"/>
       <c r="BY264" s="11"/>
-    </row>
-    <row r="265" spans="3:77">
+      <c r="BZ264" s="11"/>
+      <c r="CA264" s="11"/>
+      <c r="CB264" s="11"/>
+      <c r="CC264" s="11"/>
+    </row>
+    <row r="265" spans="3:81">
       <c r="C265" s="11"/>
       <c r="D265" s="11"/>
       <c r="E265" s="11"/>
@@ -22064,8 +23147,12 @@
       <c r="BW265" s="11"/>
       <c r="BX265" s="11"/>
       <c r="BY265" s="11"/>
-    </row>
-    <row r="266" spans="3:77">
+      <c r="BZ265" s="11"/>
+      <c r="CA265" s="11"/>
+      <c r="CB265" s="11"/>
+      <c r="CC265" s="11"/>
+    </row>
+    <row r="266" spans="3:81">
       <c r="C266" s="11"/>
       <c r="D266" s="11"/>
       <c r="E266" s="11"/>
@@ -22141,8 +23228,12 @@
       <c r="BW266" s="11"/>
       <c r="BX266" s="11"/>
       <c r="BY266" s="11"/>
-    </row>
-    <row r="267" spans="3:77">
+      <c r="BZ266" s="11"/>
+      <c r="CA266" s="11"/>
+      <c r="CB266" s="11"/>
+      <c r="CC266" s="11"/>
+    </row>
+    <row r="267" spans="3:81">
       <c r="C267" s="11"/>
       <c r="D267" s="11"/>
       <c r="E267" s="11"/>
@@ -22218,8 +23309,12 @@
       <c r="BW267" s="11"/>
       <c r="BX267" s="11"/>
       <c r="BY267" s="11"/>
-    </row>
-    <row r="268" spans="3:77">
+      <c r="BZ267" s="11"/>
+      <c r="CA267" s="11"/>
+      <c r="CB267" s="11"/>
+      <c r="CC267" s="11"/>
+    </row>
+    <row r="268" spans="3:81">
       <c r="C268" s="11"/>
       <c r="D268" s="11"/>
       <c r="E268" s="11"/>
@@ -22295,8 +23390,12 @@
       <c r="BW268" s="11"/>
       <c r="BX268" s="11"/>
       <c r="BY268" s="11"/>
-    </row>
-    <row r="269" spans="3:77">
+      <c r="BZ268" s="11"/>
+      <c r="CA268" s="11"/>
+      <c r="CB268" s="11"/>
+      <c r="CC268" s="11"/>
+    </row>
+    <row r="269" spans="3:81">
       <c r="C269" s="11"/>
       <c r="D269" s="11"/>
       <c r="E269" s="11"/>
@@ -22372,8 +23471,12 @@
       <c r="BW269" s="11"/>
       <c r="BX269" s="11"/>
       <c r="BY269" s="11"/>
-    </row>
-    <row r="270" spans="3:77">
+      <c r="BZ269" s="11"/>
+      <c r="CA269" s="11"/>
+      <c r="CB269" s="11"/>
+      <c r="CC269" s="11"/>
+    </row>
+    <row r="270" spans="3:81">
       <c r="C270" s="11"/>
       <c r="D270" s="11"/>
       <c r="E270" s="11"/>
@@ -22449,8 +23552,12 @@
       <c r="BW270" s="11"/>
       <c r="BX270" s="11"/>
       <c r="BY270" s="11"/>
-    </row>
-    <row r="271" spans="3:77">
+      <c r="BZ270" s="11"/>
+      <c r="CA270" s="11"/>
+      <c r="CB270" s="11"/>
+      <c r="CC270" s="11"/>
+    </row>
+    <row r="271" spans="3:81">
       <c r="C271" s="11"/>
       <c r="D271" s="11"/>
       <c r="E271" s="11"/>
@@ -22526,8 +23633,12 @@
       <c r="BW271" s="11"/>
       <c r="BX271" s="11"/>
       <c r="BY271" s="11"/>
-    </row>
-    <row r="272" spans="3:77">
+      <c r="BZ271" s="11"/>
+      <c r="CA271" s="11"/>
+      <c r="CB271" s="11"/>
+      <c r="CC271" s="11"/>
+    </row>
+    <row r="272" spans="3:81">
       <c r="C272" s="11"/>
       <c r="D272" s="11"/>
       <c r="E272" s="11"/>
@@ -22603,8 +23714,12 @@
       <c r="BW272" s="11"/>
       <c r="BX272" s="11"/>
       <c r="BY272" s="11"/>
-    </row>
-    <row r="273" spans="3:77">
+      <c r="BZ272" s="11"/>
+      <c r="CA272" s="11"/>
+      <c r="CB272" s="11"/>
+      <c r="CC272" s="11"/>
+    </row>
+    <row r="273" spans="3:81">
       <c r="C273" s="11"/>
       <c r="D273" s="11"/>
       <c r="E273" s="11"/>
@@ -22680,8 +23795,12 @@
       <c r="BW273" s="11"/>
       <c r="BX273" s="11"/>
       <c r="BY273" s="11"/>
-    </row>
-    <row r="274" spans="3:77">
+      <c r="BZ273" s="11"/>
+      <c r="CA273" s="11"/>
+      <c r="CB273" s="11"/>
+      <c r="CC273" s="11"/>
+    </row>
+    <row r="274" spans="3:81">
       <c r="C274" s="11"/>
       <c r="D274" s="11"/>
       <c r="E274" s="11"/>
@@ -22757,8 +23876,12 @@
       <c r="BW274" s="11"/>
       <c r="BX274" s="11"/>
       <c r="BY274" s="11"/>
-    </row>
-    <row r="275" spans="3:77">
+      <c r="BZ274" s="11"/>
+      <c r="CA274" s="11"/>
+      <c r="CB274" s="11"/>
+      <c r="CC274" s="11"/>
+    </row>
+    <row r="275" spans="3:81">
       <c r="C275" s="11"/>
       <c r="D275" s="11"/>
       <c r="E275" s="11"/>
@@ -22834,8 +23957,12 @@
       <c r="BW275" s="11"/>
       <c r="BX275" s="11"/>
       <c r="BY275" s="11"/>
-    </row>
-    <row r="276" spans="3:77">
+      <c r="BZ275" s="11"/>
+      <c r="CA275" s="11"/>
+      <c r="CB275" s="11"/>
+      <c r="CC275" s="11"/>
+    </row>
+    <row r="276" spans="3:81">
       <c r="C276" s="11"/>
       <c r="D276" s="11"/>
       <c r="E276" s="11"/>
@@ -22911,8 +24038,12 @@
       <c r="BW276" s="11"/>
       <c r="BX276" s="11"/>
       <c r="BY276" s="11"/>
-    </row>
-    <row r="277" spans="3:77">
+      <c r="BZ276" s="11"/>
+      <c r="CA276" s="11"/>
+      <c r="CB276" s="11"/>
+      <c r="CC276" s="11"/>
+    </row>
+    <row r="277" spans="3:81">
       <c r="C277" s="11"/>
       <c r="D277" s="11"/>
       <c r="E277" s="11"/>
@@ -22988,8 +24119,12 @@
       <c r="BW277" s="11"/>
       <c r="BX277" s="11"/>
       <c r="BY277" s="11"/>
-    </row>
-    <row r="278" spans="3:77">
+      <c r="BZ277" s="11"/>
+      <c r="CA277" s="11"/>
+      <c r="CB277" s="11"/>
+      <c r="CC277" s="11"/>
+    </row>
+    <row r="278" spans="3:81">
       <c r="C278" s="11"/>
       <c r="D278" s="11"/>
       <c r="E278" s="11"/>
@@ -23065,8 +24200,12 @@
       <c r="BW278" s="11"/>
       <c r="BX278" s="11"/>
       <c r="BY278" s="11"/>
-    </row>
-    <row r="279" spans="3:77">
+      <c r="BZ278" s="11"/>
+      <c r="CA278" s="11"/>
+      <c r="CB278" s="11"/>
+      <c r="CC278" s="11"/>
+    </row>
+    <row r="279" spans="3:81">
       <c r="C279" s="11"/>
       <c r="D279" s="11"/>
       <c r="E279" s="11"/>
@@ -23142,8 +24281,12 @@
       <c r="BW279" s="11"/>
       <c r="BX279" s="11"/>
       <c r="BY279" s="11"/>
-    </row>
-    <row r="280" spans="3:77">
+      <c r="BZ279" s="11"/>
+      <c r="CA279" s="11"/>
+      <c r="CB279" s="11"/>
+      <c r="CC279" s="11"/>
+    </row>
+    <row r="280" spans="3:81">
       <c r="C280" s="11"/>
       <c r="D280" s="11"/>
       <c r="E280" s="11"/>
@@ -23219,8 +24362,12 @@
       <c r="BW280" s="11"/>
       <c r="BX280" s="11"/>
       <c r="BY280" s="11"/>
-    </row>
-    <row r="281" spans="3:77">
+      <c r="BZ280" s="11"/>
+      <c r="CA280" s="11"/>
+      <c r="CB280" s="11"/>
+      <c r="CC280" s="11"/>
+    </row>
+    <row r="281" spans="3:81">
       <c r="C281" s="11"/>
       <c r="D281" s="11"/>
       <c r="E281" s="11"/>
@@ -23296,8 +24443,12 @@
       <c r="BW281" s="11"/>
       <c r="BX281" s="11"/>
       <c r="BY281" s="11"/>
-    </row>
-    <row r="282" spans="3:77">
+      <c r="BZ281" s="11"/>
+      <c r="CA281" s="11"/>
+      <c r="CB281" s="11"/>
+      <c r="CC281" s="11"/>
+    </row>
+    <row r="282" spans="3:81">
       <c r="C282" s="11"/>
       <c r="D282" s="11"/>
       <c r="E282" s="11"/>
@@ -23373,8 +24524,12 @@
       <c r="BW282" s="11"/>
       <c r="BX282" s="11"/>
       <c r="BY282" s="11"/>
-    </row>
-    <row r="283" spans="3:77">
+      <c r="BZ282" s="11"/>
+      <c r="CA282" s="11"/>
+      <c r="CB282" s="11"/>
+      <c r="CC282" s="11"/>
+    </row>
+    <row r="283" spans="3:81">
       <c r="C283" s="11"/>
       <c r="D283" s="11"/>
       <c r="E283" s="11"/>
@@ -23450,8 +24605,12 @@
       <c r="BW283" s="11"/>
       <c r="BX283" s="11"/>
       <c r="BY283" s="11"/>
-    </row>
-    <row r="284" spans="3:77">
+      <c r="BZ283" s="11"/>
+      <c r="CA283" s="11"/>
+      <c r="CB283" s="11"/>
+      <c r="CC283" s="11"/>
+    </row>
+    <row r="284" spans="3:81">
       <c r="C284" s="11"/>
       <c r="D284" s="11"/>
       <c r="E284" s="11"/>
@@ -23527,8 +24686,12 @@
       <c r="BW284" s="11"/>
       <c r="BX284" s="11"/>
       <c r="BY284" s="11"/>
-    </row>
-    <row r="285" spans="3:77">
+      <c r="BZ284" s="11"/>
+      <c r="CA284" s="11"/>
+      <c r="CB284" s="11"/>
+      <c r="CC284" s="11"/>
+    </row>
+    <row r="285" spans="3:81">
       <c r="C285" s="11"/>
       <c r="D285" s="11"/>
       <c r="E285" s="11"/>
@@ -23604,8 +24767,12 @@
       <c r="BW285" s="11"/>
       <c r="BX285" s="11"/>
       <c r="BY285" s="11"/>
-    </row>
-    <row r="286" spans="3:77">
+      <c r="BZ285" s="11"/>
+      <c r="CA285" s="11"/>
+      <c r="CB285" s="11"/>
+      <c r="CC285" s="11"/>
+    </row>
+    <row r="286" spans="3:81">
       <c r="C286" s="11"/>
       <c r="D286" s="11"/>
       <c r="E286" s="11"/>
@@ -23681,8 +24848,12 @@
       <c r="BW286" s="11"/>
       <c r="BX286" s="11"/>
       <c r="BY286" s="11"/>
-    </row>
-    <row r="287" spans="3:77">
+      <c r="BZ286" s="11"/>
+      <c r="CA286" s="11"/>
+      <c r="CB286" s="11"/>
+      <c r="CC286" s="11"/>
+    </row>
+    <row r="287" spans="3:81">
       <c r="C287" s="11"/>
       <c r="D287" s="11"/>
       <c r="E287" s="11"/>
@@ -23758,8 +24929,12 @@
       <c r="BW287" s="11"/>
       <c r="BX287" s="11"/>
       <c r="BY287" s="11"/>
-    </row>
-    <row r="288" spans="3:77">
+      <c r="BZ287" s="11"/>
+      <c r="CA287" s="11"/>
+      <c r="CB287" s="11"/>
+      <c r="CC287" s="11"/>
+    </row>
+    <row r="288" spans="3:81">
       <c r="C288" s="11"/>
       <c r="D288" s="11"/>
       <c r="E288" s="11"/>
@@ -23835,8 +25010,12 @@
       <c r="BW288" s="11"/>
       <c r="BX288" s="11"/>
       <c r="BY288" s="11"/>
-    </row>
-    <row r="289" spans="3:77">
+      <c r="BZ288" s="11"/>
+      <c r="CA288" s="11"/>
+      <c r="CB288" s="11"/>
+      <c r="CC288" s="11"/>
+    </row>
+    <row r="289" spans="3:81">
       <c r="C289" s="11"/>
       <c r="D289" s="11"/>
       <c r="E289" s="11"/>
@@ -23912,8 +25091,12 @@
       <c r="BW289" s="11"/>
       <c r="BX289" s="11"/>
       <c r="BY289" s="11"/>
-    </row>
-    <row r="290" spans="3:77">
+      <c r="BZ289" s="11"/>
+      <c r="CA289" s="11"/>
+      <c r="CB289" s="11"/>
+      <c r="CC289" s="11"/>
+    </row>
+    <row r="290" spans="3:81">
       <c r="C290" s="11"/>
       <c r="D290" s="11"/>
       <c r="E290" s="11"/>
@@ -23989,8 +25172,12 @@
       <c r="BW290" s="11"/>
       <c r="BX290" s="11"/>
       <c r="BY290" s="11"/>
-    </row>
-    <row r="291" spans="3:77">
+      <c r="BZ290" s="11"/>
+      <c r="CA290" s="11"/>
+      <c r="CB290" s="11"/>
+      <c r="CC290" s="11"/>
+    </row>
+    <row r="291" spans="3:81">
       <c r="C291" s="11"/>
       <c r="D291" s="11"/>
       <c r="E291" s="11"/>
@@ -24066,8 +25253,12 @@
       <c r="BW291" s="11"/>
       <c r="BX291" s="11"/>
       <c r="BY291" s="11"/>
-    </row>
-    <row r="292" spans="3:77">
+      <c r="BZ291" s="11"/>
+      <c r="CA291" s="11"/>
+      <c r="CB291" s="11"/>
+      <c r="CC291" s="11"/>
+    </row>
+    <row r="292" spans="3:81">
       <c r="C292" s="11"/>
       <c r="D292" s="11"/>
       <c r="E292" s="11"/>
@@ -24143,8 +25334,12 @@
       <c r="BW292" s="11"/>
       <c r="BX292" s="11"/>
       <c r="BY292" s="11"/>
-    </row>
-    <row r="293" spans="3:77">
+      <c r="BZ292" s="11"/>
+      <c r="CA292" s="11"/>
+      <c r="CB292" s="11"/>
+      <c r="CC292" s="11"/>
+    </row>
+    <row r="293" spans="3:81">
       <c r="C293" s="11"/>
       <c r="D293" s="11"/>
       <c r="E293" s="11"/>
@@ -24220,8 +25415,12 @@
       <c r="BW293" s="11"/>
       <c r="BX293" s="11"/>
       <c r="BY293" s="11"/>
-    </row>
-    <row r="294" spans="3:77">
+      <c r="BZ293" s="11"/>
+      <c r="CA293" s="11"/>
+      <c r="CB293" s="11"/>
+      <c r="CC293" s="11"/>
+    </row>
+    <row r="294" spans="3:81">
       <c r="C294" s="11"/>
       <c r="D294" s="11"/>
       <c r="E294" s="11"/>
@@ -24297,8 +25496,12 @@
       <c r="BW294" s="11"/>
       <c r="BX294" s="11"/>
       <c r="BY294" s="11"/>
-    </row>
-    <row r="295" spans="3:77">
+      <c r="BZ294" s="11"/>
+      <c r="CA294" s="11"/>
+      <c r="CB294" s="11"/>
+      <c r="CC294" s="11"/>
+    </row>
+    <row r="295" spans="3:81">
       <c r="C295" s="11"/>
       <c r="D295" s="11"/>
       <c r="E295" s="11"/>
@@ -24374,8 +25577,12 @@
       <c r="BW295" s="11"/>
       <c r="BX295" s="11"/>
       <c r="BY295" s="11"/>
-    </row>
-    <row r="296" spans="3:77">
+      <c r="BZ295" s="11"/>
+      <c r="CA295" s="11"/>
+      <c r="CB295" s="11"/>
+      <c r="CC295" s="11"/>
+    </row>
+    <row r="296" spans="3:81">
       <c r="C296" s="11"/>
       <c r="D296" s="11"/>
       <c r="E296" s="11"/>
@@ -24451,8 +25658,12 @@
       <c r="BW296" s="11"/>
       <c r="BX296" s="11"/>
       <c r="BY296" s="11"/>
-    </row>
-    <row r="297" spans="3:77">
+      <c r="BZ296" s="11"/>
+      <c r="CA296" s="11"/>
+      <c r="CB296" s="11"/>
+      <c r="CC296" s="11"/>
+    </row>
+    <row r="297" spans="3:81">
       <c r="C297" s="11"/>
       <c r="D297" s="11"/>
       <c r="E297" s="11"/>
@@ -24528,8 +25739,12 @@
       <c r="BW297" s="11"/>
       <c r="BX297" s="11"/>
       <c r="BY297" s="11"/>
-    </row>
-    <row r="298" spans="3:77">
+      <c r="BZ297" s="11"/>
+      <c r="CA297" s="11"/>
+      <c r="CB297" s="11"/>
+      <c r="CC297" s="11"/>
+    </row>
+    <row r="298" spans="3:81">
       <c r="C298" s="11"/>
       <c r="D298" s="11"/>
       <c r="E298" s="11"/>
@@ -24605,8 +25820,12 @@
       <c r="BW298" s="11"/>
       <c r="BX298" s="11"/>
       <c r="BY298" s="11"/>
-    </row>
-    <row r="299" spans="3:77">
+      <c r="BZ298" s="11"/>
+      <c r="CA298" s="11"/>
+      <c r="CB298" s="11"/>
+      <c r="CC298" s="11"/>
+    </row>
+    <row r="299" spans="3:81">
       <c r="C299" s="11"/>
       <c r="D299" s="11"/>
       <c r="E299" s="11"/>
@@ -24682,8 +25901,12 @@
       <c r="BW299" s="11"/>
       <c r="BX299" s="11"/>
       <c r="BY299" s="11"/>
-    </row>
-    <row r="300" spans="3:77">
+      <c r="BZ299" s="11"/>
+      <c r="CA299" s="11"/>
+      <c r="CB299" s="11"/>
+      <c r="CC299" s="11"/>
+    </row>
+    <row r="300" spans="3:81">
       <c r="C300" s="11"/>
       <c r="D300" s="11"/>
       <c r="E300" s="11"/>
@@ -24759,8 +25982,12 @@
       <c r="BW300" s="11"/>
       <c r="BX300" s="11"/>
       <c r="BY300" s="11"/>
-    </row>
-    <row r="301" spans="3:77">
+      <c r="BZ300" s="11"/>
+      <c r="CA300" s="11"/>
+      <c r="CB300" s="11"/>
+      <c r="CC300" s="11"/>
+    </row>
+    <row r="301" spans="3:81">
       <c r="C301" s="11"/>
       <c r="D301" s="11"/>
       <c r="E301" s="11"/>
@@ -24836,8 +26063,12 @@
       <c r="BW301" s="11"/>
       <c r="BX301" s="11"/>
       <c r="BY301" s="11"/>
-    </row>
-    <row r="302" spans="3:77">
+      <c r="BZ301" s="11"/>
+      <c r="CA301" s="11"/>
+      <c r="CB301" s="11"/>
+      <c r="CC301" s="11"/>
+    </row>
+    <row r="302" spans="3:81">
       <c r="C302" s="11"/>
       <c r="D302" s="11"/>
       <c r="E302" s="11"/>
@@ -24913,8 +26144,12 @@
       <c r="BW302" s="11"/>
       <c r="BX302" s="11"/>
       <c r="BY302" s="11"/>
-    </row>
-    <row r="303" spans="3:77">
+      <c r="BZ302" s="11"/>
+      <c r="CA302" s="11"/>
+      <c r="CB302" s="11"/>
+      <c r="CC302" s="11"/>
+    </row>
+    <row r="303" spans="3:81">
       <c r="C303" s="11"/>
       <c r="D303" s="11"/>
       <c r="E303" s="11"/>
@@ -24990,8 +26225,12 @@
       <c r="BW303" s="11"/>
       <c r="BX303" s="11"/>
       <c r="BY303" s="11"/>
-    </row>
-    <row r="304" spans="3:77">
+      <c r="BZ303" s="11"/>
+      <c r="CA303" s="11"/>
+      <c r="CB303" s="11"/>
+      <c r="CC303" s="11"/>
+    </row>
+    <row r="304" spans="3:81">
       <c r="C304" s="11"/>
       <c r="D304" s="11"/>
       <c r="E304" s="11"/>
@@ -25067,8 +26306,12 @@
       <c r="BW304" s="11"/>
       <c r="BX304" s="11"/>
       <c r="BY304" s="11"/>
-    </row>
-    <row r="305" spans="3:77">
+      <c r="BZ304" s="11"/>
+      <c r="CA304" s="11"/>
+      <c r="CB304" s="11"/>
+      <c r="CC304" s="11"/>
+    </row>
+    <row r="305" spans="3:81">
       <c r="C305" s="11"/>
       <c r="D305" s="11"/>
       <c r="E305" s="11"/>
@@ -25144,8 +26387,12 @@
       <c r="BW305" s="11"/>
       <c r="BX305" s="11"/>
       <c r="BY305" s="11"/>
-    </row>
-    <row r="306" spans="3:77">
+      <c r="BZ305" s="11"/>
+      <c r="CA305" s="11"/>
+      <c r="CB305" s="11"/>
+      <c r="CC305" s="11"/>
+    </row>
+    <row r="306" spans="3:81">
       <c r="C306" s="11"/>
       <c r="D306" s="11"/>
       <c r="E306" s="11"/>
@@ -25221,8 +26468,12 @@
       <c r="BW306" s="11"/>
       <c r="BX306" s="11"/>
       <c r="BY306" s="11"/>
-    </row>
-    <row r="307" spans="3:77">
+      <c r="BZ306" s="11"/>
+      <c r="CA306" s="11"/>
+      <c r="CB306" s="11"/>
+      <c r="CC306" s="11"/>
+    </row>
+    <row r="307" spans="3:81">
       <c r="C307" s="11"/>
       <c r="D307" s="11"/>
       <c r="E307" s="11"/>
@@ -25298,8 +26549,12 @@
       <c r="BW307" s="11"/>
       <c r="BX307" s="11"/>
       <c r="BY307" s="11"/>
-    </row>
-    <row r="308" spans="3:77">
+      <c r="BZ307" s="11"/>
+      <c r="CA307" s="11"/>
+      <c r="CB307" s="11"/>
+      <c r="CC307" s="11"/>
+    </row>
+    <row r="308" spans="3:81">
       <c r="C308" s="11"/>
       <c r="D308" s="11"/>
       <c r="E308" s="11"/>
@@ -25375,8 +26630,12 @@
       <c r="BW308" s="11"/>
       <c r="BX308" s="11"/>
       <c r="BY308" s="11"/>
-    </row>
-    <row r="309" spans="3:77">
+      <c r="BZ308" s="11"/>
+      <c r="CA308" s="11"/>
+      <c r="CB308" s="11"/>
+      <c r="CC308" s="11"/>
+    </row>
+    <row r="309" spans="3:81">
       <c r="C309" s="11"/>
       <c r="D309" s="11"/>
       <c r="E309" s="11"/>
@@ -25452,8 +26711,12 @@
       <c r="BW309" s="11"/>
       <c r="BX309" s="11"/>
       <c r="BY309" s="11"/>
-    </row>
-    <row r="310" spans="3:77">
+      <c r="BZ309" s="11"/>
+      <c r="CA309" s="11"/>
+      <c r="CB309" s="11"/>
+      <c r="CC309" s="11"/>
+    </row>
+    <row r="310" spans="3:81">
       <c r="C310" s="11"/>
       <c r="D310" s="11"/>
       <c r="E310" s="11"/>
@@ -25529,8 +26792,12 @@
       <c r="BW310" s="11"/>
       <c r="BX310" s="11"/>
       <c r="BY310" s="11"/>
-    </row>
-    <row r="311" spans="3:77">
+      <c r="BZ310" s="11"/>
+      <c r="CA310" s="11"/>
+      <c r="CB310" s="11"/>
+      <c r="CC310" s="11"/>
+    </row>
+    <row r="311" spans="3:81">
       <c r="C311" s="11"/>
       <c r="D311" s="11"/>
       <c r="E311" s="11"/>
@@ -25606,8 +26873,12 @@
       <c r="BW311" s="11"/>
       <c r="BX311" s="11"/>
       <c r="BY311" s="11"/>
-    </row>
-    <row r="312" spans="3:77">
+      <c r="BZ311" s="11"/>
+      <c r="CA311" s="11"/>
+      <c r="CB311" s="11"/>
+      <c r="CC311" s="11"/>
+    </row>
+    <row r="312" spans="3:81">
       <c r="C312" s="11"/>
       <c r="D312" s="11"/>
       <c r="E312" s="11"/>
@@ -25683,8 +26954,12 @@
       <c r="BW312" s="11"/>
       <c r="BX312" s="11"/>
       <c r="BY312" s="11"/>
-    </row>
-    <row r="313" spans="3:77">
+      <c r="BZ312" s="11"/>
+      <c r="CA312" s="11"/>
+      <c r="CB312" s="11"/>
+      <c r="CC312" s="11"/>
+    </row>
+    <row r="313" spans="3:81">
       <c r="C313" s="11"/>
       <c r="D313" s="11"/>
       <c r="E313" s="11"/>
@@ -25760,8 +27035,12 @@
       <c r="BW313" s="11"/>
       <c r="BX313" s="11"/>
       <c r="BY313" s="11"/>
-    </row>
-    <row r="314" spans="3:77">
+      <c r="BZ313" s="11"/>
+      <c r="CA313" s="11"/>
+      <c r="CB313" s="11"/>
+      <c r="CC313" s="11"/>
+    </row>
+    <row r="314" spans="3:81">
       <c r="C314" s="11"/>
       <c r="D314" s="11"/>
       <c r="E314" s="11"/>
@@ -25837,8 +27116,12 @@
       <c r="BW314" s="11"/>
       <c r="BX314" s="11"/>
       <c r="BY314" s="11"/>
-    </row>
-    <row r="315" spans="3:77">
+      <c r="BZ314" s="11"/>
+      <c r="CA314" s="11"/>
+      <c r="CB314" s="11"/>
+      <c r="CC314" s="11"/>
+    </row>
+    <row r="315" spans="3:81">
       <c r="C315" s="11"/>
       <c r="D315" s="11"/>
       <c r="E315" s="11"/>
@@ -25914,8 +27197,12 @@
       <c r="BW315" s="11"/>
       <c r="BX315" s="11"/>
       <c r="BY315" s="11"/>
-    </row>
-    <row r="316" spans="3:77">
+      <c r="BZ315" s="11"/>
+      <c r="CA315" s="11"/>
+      <c r="CB315" s="11"/>
+      <c r="CC315" s="11"/>
+    </row>
+    <row r="316" spans="3:81">
       <c r="C316" s="11"/>
       <c r="D316" s="11"/>
       <c r="E316" s="11"/>
@@ -25991,8 +27278,12 @@
       <c r="BW316" s="11"/>
       <c r="BX316" s="11"/>
       <c r="BY316" s="11"/>
-    </row>
-    <row r="317" spans="3:77">
+      <c r="BZ316" s="11"/>
+      <c r="CA316" s="11"/>
+      <c r="CB316" s="11"/>
+      <c r="CC316" s="11"/>
+    </row>
+    <row r="317" spans="3:81">
       <c r="C317" s="11"/>
       <c r="D317" s="11"/>
       <c r="E317" s="11"/>
@@ -26068,8 +27359,12 @@
       <c r="BW317" s="11"/>
       <c r="BX317" s="11"/>
       <c r="BY317" s="11"/>
-    </row>
-    <row r="318" spans="3:77">
+      <c r="BZ317" s="11"/>
+      <c r="CA317" s="11"/>
+      <c r="CB317" s="11"/>
+      <c r="CC317" s="11"/>
+    </row>
+    <row r="318" spans="3:81">
       <c r="C318" s="11"/>
       <c r="D318" s="11"/>
       <c r="E318" s="11"/>
@@ -26145,8 +27440,12 @@
       <c r="BW318" s="11"/>
       <c r="BX318" s="11"/>
       <c r="BY318" s="11"/>
-    </row>
-    <row r="319" spans="3:77">
+      <c r="BZ318" s="11"/>
+      <c r="CA318" s="11"/>
+      <c r="CB318" s="11"/>
+      <c r="CC318" s="11"/>
+    </row>
+    <row r="319" spans="3:81">
       <c r="C319" s="11"/>
       <c r="D319" s="11"/>
       <c r="E319" s="11"/>
@@ -26222,8 +27521,12 @@
       <c r="BW319" s="11"/>
       <c r="BX319" s="11"/>
       <c r="BY319" s="11"/>
-    </row>
-    <row r="320" spans="3:77">
+      <c r="BZ319" s="11"/>
+      <c r="CA319" s="11"/>
+      <c r="CB319" s="11"/>
+      <c r="CC319" s="11"/>
+    </row>
+    <row r="320" spans="3:81">
       <c r="C320" s="11"/>
       <c r="D320" s="11"/>
       <c r="E320" s="11"/>
@@ -26299,8 +27602,12 @@
       <c r="BW320" s="11"/>
       <c r="BX320" s="11"/>
       <c r="BY320" s="11"/>
-    </row>
-    <row r="321" spans="3:77">
+      <c r="BZ320" s="11"/>
+      <c r="CA320" s="11"/>
+      <c r="CB320" s="11"/>
+      <c r="CC320" s="11"/>
+    </row>
+    <row r="321" spans="3:81">
       <c r="C321" s="11"/>
       <c r="D321" s="11"/>
       <c r="E321" s="11"/>
@@ -26376,8 +27683,12 @@
       <c r="BW321" s="11"/>
       <c r="BX321" s="11"/>
       <c r="BY321" s="11"/>
-    </row>
-    <row r="322" spans="3:77">
+      <c r="BZ321" s="11"/>
+      <c r="CA321" s="11"/>
+      <c r="CB321" s="11"/>
+      <c r="CC321" s="11"/>
+    </row>
+    <row r="322" spans="3:81">
       <c r="C322" s="11"/>
       <c r="D322" s="11"/>
       <c r="E322" s="11"/>
@@ -26453,8 +27764,12 @@
       <c r="BW322" s="11"/>
       <c r="BX322" s="11"/>
       <c r="BY322" s="11"/>
-    </row>
-    <row r="323" spans="3:77">
+      <c r="BZ322" s="11"/>
+      <c r="CA322" s="11"/>
+      <c r="CB322" s="11"/>
+      <c r="CC322" s="11"/>
+    </row>
+    <row r="323" spans="3:81">
       <c r="C323" s="11"/>
       <c r="D323" s="11"/>
       <c r="E323" s="11"/>
@@ -26530,8 +27845,12 @@
       <c r="BW323" s="11"/>
       <c r="BX323" s="11"/>
       <c r="BY323" s="11"/>
-    </row>
-    <row r="324" spans="3:77">
+      <c r="BZ323" s="11"/>
+      <c r="CA323" s="11"/>
+      <c r="CB323" s="11"/>
+      <c r="CC323" s="11"/>
+    </row>
+    <row r="324" spans="3:81">
       <c r="C324" s="11"/>
       <c r="D324" s="11"/>
       <c r="E324" s="11"/>
@@ -26607,8 +27926,12 @@
       <c r="BW324" s="11"/>
       <c r="BX324" s="11"/>
       <c r="BY324" s="11"/>
-    </row>
-    <row r="325" spans="3:77">
+      <c r="BZ324" s="11"/>
+      <c r="CA324" s="11"/>
+      <c r="CB324" s="11"/>
+      <c r="CC324" s="11"/>
+    </row>
+    <row r="325" spans="3:81">
       <c r="C325" s="11"/>
       <c r="D325" s="11"/>
       <c r="E325" s="11"/>
@@ -26684,8 +28007,12 @@
       <c r="BW325" s="11"/>
       <c r="BX325" s="11"/>
       <c r="BY325" s="11"/>
-    </row>
-    <row r="326" spans="3:77">
+      <c r="BZ325" s="11"/>
+      <c r="CA325" s="11"/>
+      <c r="CB325" s="11"/>
+      <c r="CC325" s="11"/>
+    </row>
+    <row r="326" spans="3:81">
       <c r="C326" s="11"/>
       <c r="D326" s="11"/>
       <c r="E326" s="11"/>
@@ -26761,8 +28088,12 @@
       <c r="BW326" s="11"/>
       <c r="BX326" s="11"/>
       <c r="BY326" s="11"/>
-    </row>
-    <row r="327" spans="3:77">
+      <c r="BZ326" s="11"/>
+      <c r="CA326" s="11"/>
+      <c r="CB326" s="11"/>
+      <c r="CC326" s="11"/>
+    </row>
+    <row r="327" spans="3:81">
       <c r="C327" s="11"/>
       <c r="D327" s="11"/>
       <c r="E327" s="11"/>
@@ -26838,8 +28169,12 @@
       <c r="BW327" s="11"/>
       <c r="BX327" s="11"/>
       <c r="BY327" s="11"/>
-    </row>
-    <row r="328" spans="3:77">
+      <c r="BZ327" s="11"/>
+      <c r="CA327" s="11"/>
+      <c r="CB327" s="11"/>
+      <c r="CC327" s="11"/>
+    </row>
+    <row r="328" spans="3:81">
       <c r="C328" s="11"/>
       <c r="D328" s="11"/>
       <c r="E328" s="11"/>
@@ -26915,8 +28250,12 @@
       <c r="BW328" s="11"/>
       <c r="BX328" s="11"/>
       <c r="BY328" s="11"/>
-    </row>
-    <row r="329" spans="3:77">
+      <c r="BZ328" s="11"/>
+      <c r="CA328" s="11"/>
+      <c r="CB328" s="11"/>
+      <c r="CC328" s="11"/>
+    </row>
+    <row r="329" spans="3:81">
       <c r="C329" s="11"/>
       <c r="D329" s="11"/>
       <c r="E329" s="11"/>
@@ -26992,8 +28331,12 @@
       <c r="BW329" s="11"/>
       <c r="BX329" s="11"/>
       <c r="BY329" s="11"/>
-    </row>
-    <row r="330" spans="3:77">
+      <c r="BZ329" s="11"/>
+      <c r="CA329" s="11"/>
+      <c r="CB329" s="11"/>
+      <c r="CC329" s="11"/>
+    </row>
+    <row r="330" spans="3:81">
       <c r="C330" s="11"/>
       <c r="D330" s="11"/>
       <c r="E330" s="11"/>
@@ -27069,8 +28412,12 @@
       <c r="BW330" s="11"/>
       <c r="BX330" s="11"/>
       <c r="BY330" s="11"/>
-    </row>
-    <row r="331" spans="3:77">
+      <c r="BZ330" s="11"/>
+      <c r="CA330" s="11"/>
+      <c r="CB330" s="11"/>
+      <c r="CC330" s="11"/>
+    </row>
+    <row r="331" spans="3:81">
       <c r="C331" s="11"/>
       <c r="D331" s="11"/>
       <c r="E331" s="11"/>
@@ -27146,8 +28493,12 @@
       <c r="BW331" s="11"/>
       <c r="BX331" s="11"/>
       <c r="BY331" s="11"/>
-    </row>
-    <row r="332" spans="3:77">
+      <c r="BZ331" s="11"/>
+      <c r="CA331" s="11"/>
+      <c r="CB331" s="11"/>
+      <c r="CC331" s="11"/>
+    </row>
+    <row r="332" spans="3:81">
       <c r="C332" s="11"/>
       <c r="D332" s="11"/>
       <c r="E332" s="11"/>
@@ -27223,8 +28574,12 @@
       <c r="BW332" s="11"/>
       <c r="BX332" s="11"/>
       <c r="BY332" s="11"/>
-    </row>
-    <row r="333" spans="3:77">
+      <c r="BZ332" s="11"/>
+      <c r="CA332" s="11"/>
+      <c r="CB332" s="11"/>
+      <c r="CC332" s="11"/>
+    </row>
+    <row r="333" spans="3:81">
       <c r="C333" s="11"/>
       <c r="D333" s="11"/>
       <c r="E333" s="11"/>
@@ -27300,8 +28655,12 @@
       <c r="BW333" s="11"/>
       <c r="BX333" s="11"/>
       <c r="BY333" s="11"/>
-    </row>
-    <row r="334" spans="3:77">
+      <c r="BZ333" s="11"/>
+      <c r="CA333" s="11"/>
+      <c r="CB333" s="11"/>
+      <c r="CC333" s="11"/>
+    </row>
+    <row r="334" spans="3:81">
       <c r="C334" s="11"/>
       <c r="D334" s="11"/>
       <c r="E334" s="11"/>
@@ -27377,8 +28736,12 @@
       <c r="BW334" s="11"/>
       <c r="BX334" s="11"/>
       <c r="BY334" s="11"/>
-    </row>
-    <row r="335" spans="3:77">
+      <c r="BZ334" s="11"/>
+      <c r="CA334" s="11"/>
+      <c r="CB334" s="11"/>
+      <c r="CC334" s="11"/>
+    </row>
+    <row r="335" spans="3:81">
       <c r="C335" s="11"/>
       <c r="D335" s="11"/>
       <c r="E335" s="11"/>
@@ -27454,8 +28817,12 @@
       <c r="BW335" s="11"/>
       <c r="BX335" s="11"/>
       <c r="BY335" s="11"/>
-    </row>
-    <row r="336" spans="3:77">
+      <c r="BZ335" s="11"/>
+      <c r="CA335" s="11"/>
+      <c r="CB335" s="11"/>
+      <c r="CC335" s="11"/>
+    </row>
+    <row r="336" spans="3:81">
       <c r="C336" s="11"/>
       <c r="D336" s="11"/>
       <c r="E336" s="11"/>
@@ -27531,8 +28898,12 @@
       <c r="BW336" s="11"/>
       <c r="BX336" s="11"/>
       <c r="BY336" s="11"/>
-    </row>
-    <row r="337" spans="3:77">
+      <c r="BZ336" s="11"/>
+      <c r="CA336" s="11"/>
+      <c r="CB336" s="11"/>
+      <c r="CC336" s="11"/>
+    </row>
+    <row r="337" spans="3:81">
       <c r="C337" s="11"/>
       <c r="D337" s="11"/>
       <c r="E337" s="11"/>
@@ -27608,8 +28979,12 @@
       <c r="BW337" s="11"/>
       <c r="BX337" s="11"/>
       <c r="BY337" s="11"/>
-    </row>
-    <row r="338" spans="3:77">
+      <c r="BZ337" s="11"/>
+      <c r="CA337" s="11"/>
+      <c r="CB337" s="11"/>
+      <c r="CC337" s="11"/>
+    </row>
+    <row r="338" spans="3:81">
       <c r="C338" s="11"/>
       <c r="D338" s="11"/>
       <c r="E338" s="11"/>
@@ -27685,8 +29060,12 @@
       <c r="BW338" s="11"/>
       <c r="BX338" s="11"/>
       <c r="BY338" s="11"/>
-    </row>
-    <row r="339" spans="3:77">
+      <c r="BZ338" s="11"/>
+      <c r="CA338" s="11"/>
+      <c r="CB338" s="11"/>
+      <c r="CC338" s="11"/>
+    </row>
+    <row r="339" spans="3:81">
       <c r="C339" s="11"/>
       <c r="D339" s="11"/>
       <c r="E339" s="11"/>
@@ -27762,8 +29141,12 @@
       <c r="BW339" s="11"/>
       <c r="BX339" s="11"/>
       <c r="BY339" s="11"/>
-    </row>
-    <row r="340" spans="3:77">
+      <c r="BZ339" s="11"/>
+      <c r="CA339" s="11"/>
+      <c r="CB339" s="11"/>
+      <c r="CC339" s="11"/>
+    </row>
+    <row r="340" spans="3:81">
       <c r="C340" s="11"/>
       <c r="D340" s="11"/>
       <c r="E340" s="11"/>
@@ -27839,8 +29222,12 @@
       <c r="BW340" s="11"/>
       <c r="BX340" s="11"/>
       <c r="BY340" s="11"/>
-    </row>
-    <row r="341" spans="3:77">
+      <c r="BZ340" s="11"/>
+      <c r="CA340" s="11"/>
+      <c r="CB340" s="11"/>
+      <c r="CC340" s="11"/>
+    </row>
+    <row r="341" spans="3:81">
       <c r="C341" s="11"/>
       <c r="D341" s="11"/>
       <c r="E341" s="11"/>
@@ -27916,8 +29303,12 @@
       <c r="BW341" s="11"/>
       <c r="BX341" s="11"/>
       <c r="BY341" s="11"/>
-    </row>
-    <row r="342" spans="3:77">
+      <c r="BZ341" s="11"/>
+      <c r="CA341" s="11"/>
+      <c r="CB341" s="11"/>
+      <c r="CC341" s="11"/>
+    </row>
+    <row r="342" spans="3:81">
       <c r="C342" s="11"/>
       <c r="D342" s="11"/>
       <c r="E342" s="11"/>
@@ -27993,8 +29384,12 @@
       <c r="BW342" s="11"/>
       <c r="BX342" s="11"/>
       <c r="BY342" s="11"/>
-    </row>
-    <row r="343" spans="3:77">
+      <c r="BZ342" s="11"/>
+      <c r="CA342" s="11"/>
+      <c r="CB342" s="11"/>
+      <c r="CC342" s="11"/>
+    </row>
+    <row r="343" spans="3:81">
       <c r="C343" s="11"/>
       <c r="D343" s="11"/>
       <c r="E343" s="11"/>
@@ -28070,8 +29465,12 @@
       <c r="BW343" s="11"/>
       <c r="BX343" s="11"/>
       <c r="BY343" s="11"/>
-    </row>
-    <row r="344" spans="3:77">
+      <c r="BZ343" s="11"/>
+      <c r="CA343" s="11"/>
+      <c r="CB343" s="11"/>
+      <c r="CC343" s="11"/>
+    </row>
+    <row r="344" spans="3:81">
       <c r="C344" s="11"/>
       <c r="D344" s="11"/>
       <c r="E344" s="11"/>
@@ -28147,8 +29546,12 @@
       <c r="BW344" s="11"/>
       <c r="BX344" s="11"/>
       <c r="BY344" s="11"/>
-    </row>
-    <row r="345" spans="3:77">
+      <c r="BZ344" s="11"/>
+      <c r="CA344" s="11"/>
+      <c r="CB344" s="11"/>
+      <c r="CC344" s="11"/>
+    </row>
+    <row r="345" spans="3:81">
       <c r="C345" s="11"/>
       <c r="D345" s="11"/>
       <c r="E345" s="11"/>
@@ -28224,8 +29627,12 @@
       <c r="BW345" s="11"/>
       <c r="BX345" s="11"/>
       <c r="BY345" s="11"/>
-    </row>
-    <row r="346" spans="3:77">
+      <c r="BZ345" s="11"/>
+      <c r="CA345" s="11"/>
+      <c r="CB345" s="11"/>
+      <c r="CC345" s="11"/>
+    </row>
+    <row r="346" spans="3:81">
       <c r="C346" s="11"/>
       <c r="D346" s="11"/>
       <c r="E346" s="11"/>
@@ -28301,8 +29708,12 @@
       <c r="BW346" s="11"/>
       <c r="BX346" s="11"/>
       <c r="BY346" s="11"/>
-    </row>
-    <row r="347" spans="3:77">
+      <c r="BZ346" s="11"/>
+      <c r="CA346" s="11"/>
+      <c r="CB346" s="11"/>
+      <c r="CC346" s="11"/>
+    </row>
+    <row r="347" spans="3:81">
       <c r="C347" s="11"/>
       <c r="D347" s="11"/>
       <c r="E347" s="11"/>
@@ -28378,8 +29789,12 @@
       <c r="BW347" s="11"/>
       <c r="BX347" s="11"/>
       <c r="BY347" s="11"/>
-    </row>
-    <row r="348" spans="3:77">
+      <c r="BZ347" s="11"/>
+      <c r="CA347" s="11"/>
+      <c r="CB347" s="11"/>
+      <c r="CC347" s="11"/>
+    </row>
+    <row r="348" spans="3:81">
       <c r="C348" s="11"/>
       <c r="D348" s="11"/>
       <c r="E348" s="11"/>
@@ -28455,8 +29870,12 @@
       <c r="BW348" s="11"/>
       <c r="BX348" s="11"/>
       <c r="BY348" s="11"/>
-    </row>
-    <row r="349" spans="3:77">
+      <c r="BZ348" s="11"/>
+      <c r="CA348" s="11"/>
+      <c r="CB348" s="11"/>
+      <c r="CC348" s="11"/>
+    </row>
+    <row r="349" spans="3:81">
       <c r="C349" s="11"/>
       <c r="D349" s="11"/>
       <c r="E349" s="11"/>
@@ -28532,8 +29951,12 @@
       <c r="BW349" s="11"/>
       <c r="BX349" s="11"/>
       <c r="BY349" s="11"/>
-    </row>
-    <row r="350" spans="3:77">
+      <c r="BZ349" s="11"/>
+      <c r="CA349" s="11"/>
+      <c r="CB349" s="11"/>
+      <c r="CC349" s="11"/>
+    </row>
+    <row r="350" spans="3:81">
       <c r="C350" s="11"/>
       <c r="D350" s="11"/>
       <c r="E350" s="11"/>
@@ -28609,8 +30032,12 @@
       <c r="BW350" s="11"/>
       <c r="BX350" s="11"/>
       <c r="BY350" s="11"/>
-    </row>
-    <row r="351" spans="3:77">
+      <c r="BZ350" s="11"/>
+      <c r="CA350" s="11"/>
+      <c r="CB350" s="11"/>
+      <c r="CC350" s="11"/>
+    </row>
+    <row r="351" spans="3:81">
       <c r="C351" s="11"/>
       <c r="D351" s="11"/>
       <c r="E351" s="11"/>
@@ -28686,8 +30113,12 @@
       <c r="BW351" s="11"/>
       <c r="BX351" s="11"/>
       <c r="BY351" s="11"/>
-    </row>
-    <row r="352" spans="3:77">
+      <c r="BZ351" s="11"/>
+      <c r="CA351" s="11"/>
+      <c r="CB351" s="11"/>
+      <c r="CC351" s="11"/>
+    </row>
+    <row r="352" spans="3:81">
       <c r="C352" s="11"/>
       <c r="D352" s="11"/>
       <c r="E352" s="11"/>
@@ -28763,8 +30194,12 @@
       <c r="BW352" s="11"/>
       <c r="BX352" s="11"/>
       <c r="BY352" s="11"/>
-    </row>
-    <row r="353" spans="3:77">
+      <c r="BZ352" s="11"/>
+      <c r="CA352" s="11"/>
+      <c r="CB352" s="11"/>
+      <c r="CC352" s="11"/>
+    </row>
+    <row r="353" spans="3:81">
       <c r="C353" s="11"/>
       <c r="D353" s="11"/>
       <c r="E353" s="11"/>
@@ -28840,8 +30275,12 @@
       <c r="BW353" s="11"/>
       <c r="BX353" s="11"/>
       <c r="BY353" s="11"/>
-    </row>
-    <row r="354" spans="3:77">
+      <c r="BZ353" s="11"/>
+      <c r="CA353" s="11"/>
+      <c r="CB353" s="11"/>
+      <c r="CC353" s="11"/>
+    </row>
+    <row r="354" spans="3:81">
       <c r="C354" s="11"/>
       <c r="D354" s="11"/>
       <c r="E354" s="11"/>
@@ -28917,8 +30356,12 @@
       <c r="BW354" s="11"/>
       <c r="BX354" s="11"/>
       <c r="BY354" s="11"/>
-    </row>
-    <row r="355" spans="3:77">
+      <c r="BZ354" s="11"/>
+      <c r="CA354" s="11"/>
+      <c r="CB354" s="11"/>
+      <c r="CC354" s="11"/>
+    </row>
+    <row r="355" spans="3:81">
       <c r="C355" s="11"/>
       <c r="D355" s="11"/>
       <c r="E355" s="11"/>
@@ -28994,8 +30437,12 @@
       <c r="BW355" s="11"/>
       <c r="BX355" s="11"/>
       <c r="BY355" s="11"/>
-    </row>
-    <row r="356" spans="3:77">
+      <c r="BZ355" s="11"/>
+      <c r="CA355" s="11"/>
+      <c r="CB355" s="11"/>
+      <c r="CC355" s="11"/>
+    </row>
+    <row r="356" spans="3:81">
       <c r="C356" s="11"/>
       <c r="D356" s="11"/>
       <c r="E356" s="11"/>
@@ -29071,8 +30518,12 @@
       <c r="BW356" s="11"/>
       <c r="BX356" s="11"/>
       <c r="BY356" s="11"/>
-    </row>
-    <row r="357" spans="3:77">
+      <c r="BZ356" s="11"/>
+      <c r="CA356" s="11"/>
+      <c r="CB356" s="11"/>
+      <c r="CC356" s="11"/>
+    </row>
+    <row r="357" spans="3:81">
       <c r="C357" s="11"/>
       <c r="D357" s="11"/>
       <c r="E357" s="11"/>
@@ -29148,8 +30599,12 @@
       <c r="BW357" s="11"/>
       <c r="BX357" s="11"/>
       <c r="BY357" s="11"/>
-    </row>
-    <row r="358" spans="3:77">
+      <c r="BZ357" s="11"/>
+      <c r="CA357" s="11"/>
+      <c r="CB357" s="11"/>
+      <c r="CC357" s="11"/>
+    </row>
+    <row r="358" spans="3:81">
       <c r="C358" s="11"/>
       <c r="D358" s="11"/>
       <c r="E358" s="11"/>
@@ -29225,8 +30680,12 @@
       <c r="BW358" s="11"/>
       <c r="BX358" s="11"/>
       <c r="BY358" s="11"/>
-    </row>
-    <row r="359" spans="3:77">
+      <c r="BZ358" s="11"/>
+      <c r="CA358" s="11"/>
+      <c r="CB358" s="11"/>
+      <c r="CC358" s="11"/>
+    </row>
+    <row r="359" spans="3:81">
       <c r="C359" s="11"/>
       <c r="D359" s="11"/>
       <c r="E359" s="11"/>
@@ -29302,8 +30761,12 @@
       <c r="BW359" s="11"/>
       <c r="BX359" s="11"/>
       <c r="BY359" s="11"/>
-    </row>
-    <row r="360" spans="3:77">
+      <c r="BZ359" s="11"/>
+      <c r="CA359" s="11"/>
+      <c r="CB359" s="11"/>
+      <c r="CC359" s="11"/>
+    </row>
+    <row r="360" spans="3:81">
       <c r="C360" s="11"/>
       <c r="D360" s="11"/>
       <c r="E360" s="11"/>
@@ -29379,8 +30842,12 @@
       <c r="BW360" s="11"/>
       <c r="BX360" s="11"/>
       <c r="BY360" s="11"/>
-    </row>
-    <row r="361" spans="3:77">
+      <c r="BZ360" s="11"/>
+      <c r="CA360" s="11"/>
+      <c r="CB360" s="11"/>
+      <c r="CC360" s="11"/>
+    </row>
+    <row r="361" spans="3:81">
       <c r="C361" s="11"/>
       <c r="D361" s="11"/>
       <c r="E361" s="11"/>
@@ -29456,8 +30923,12 @@
       <c r="BW361" s="11"/>
       <c r="BX361" s="11"/>
       <c r="BY361" s="11"/>
-    </row>
-    <row r="362" spans="3:77">
+      <c r="BZ361" s="11"/>
+      <c r="CA361" s="11"/>
+      <c r="CB361" s="11"/>
+      <c r="CC361" s="11"/>
+    </row>
+    <row r="362" spans="3:81">
       <c r="C362" s="11"/>
       <c r="D362" s="11"/>
       <c r="E362" s="11"/>
@@ -29533,8 +31004,12 @@
       <c r="BW362" s="11"/>
       <c r="BX362" s="11"/>
       <c r="BY362" s="11"/>
-    </row>
-    <row r="363" spans="3:77">
+      <c r="BZ362" s="11"/>
+      <c r="CA362" s="11"/>
+      <c r="CB362" s="11"/>
+      <c r="CC362" s="11"/>
+    </row>
+    <row r="363" spans="3:81">
       <c r="C363" s="11"/>
       <c r="D363" s="11"/>
       <c r="E363" s="11"/>
@@ -29610,8 +31085,12 @@
       <c r="BW363" s="11"/>
       <c r="BX363" s="11"/>
       <c r="BY363" s="11"/>
-    </row>
-    <row r="364" spans="3:77">
+      <c r="BZ363" s="11"/>
+      <c r="CA363" s="11"/>
+      <c r="CB363" s="11"/>
+      <c r="CC363" s="11"/>
+    </row>
+    <row r="364" spans="3:81">
       <c r="C364" s="11"/>
       <c r="D364" s="11"/>
       <c r="E364" s="11"/>
@@ -29687,8 +31166,12 @@
       <c r="BW364" s="11"/>
       <c r="BX364" s="11"/>
       <c r="BY364" s="11"/>
-    </row>
-    <row r="365" spans="3:77">
+      <c r="BZ364" s="11"/>
+      <c r="CA364" s="11"/>
+      <c r="CB364" s="11"/>
+      <c r="CC364" s="11"/>
+    </row>
+    <row r="365" spans="3:81">
       <c r="C365" s="11"/>
       <c r="D365" s="11"/>
       <c r="E365" s="11"/>
@@ -29764,8 +31247,12 @@
       <c r="BW365" s="11"/>
       <c r="BX365" s="11"/>
       <c r="BY365" s="11"/>
-    </row>
-    <row r="366" spans="3:77">
+      <c r="BZ365" s="11"/>
+      <c r="CA365" s="11"/>
+      <c r="CB365" s="11"/>
+      <c r="CC365" s="11"/>
+    </row>
+    <row r="366" spans="3:81">
       <c r="C366" s="11"/>
       <c r="D366" s="11"/>
       <c r="E366" s="11"/>
@@ -29841,8 +31328,12 @@
       <c r="BW366" s="11"/>
       <c r="BX366" s="11"/>
       <c r="BY366" s="11"/>
-    </row>
-    <row r="367" spans="3:77">
+      <c r="BZ366" s="11"/>
+      <c r="CA366" s="11"/>
+      <c r="CB366" s="11"/>
+      <c r="CC366" s="11"/>
+    </row>
+    <row r="367" spans="3:81">
       <c r="C367" s="11"/>
       <c r="D367" s="11"/>
       <c r="E367" s="11"/>
@@ -29918,8 +31409,12 @@
       <c r="BW367" s="11"/>
       <c r="BX367" s="11"/>
       <c r="BY367" s="11"/>
-    </row>
-    <row r="368" spans="3:77">
+      <c r="BZ367" s="11"/>
+      <c r="CA367" s="11"/>
+      <c r="CB367" s="11"/>
+      <c r="CC367" s="11"/>
+    </row>
+    <row r="368" spans="3:81">
       <c r="C368" s="11"/>
       <c r="D368" s="11"/>
       <c r="E368" s="11"/>
@@ -29995,8 +31490,12 @@
       <c r="BW368" s="11"/>
       <c r="BX368" s="11"/>
       <c r="BY368" s="11"/>
-    </row>
-    <row r="369" spans="3:77">
+      <c r="BZ368" s="11"/>
+      <c r="CA368" s="11"/>
+      <c r="CB368" s="11"/>
+      <c r="CC368" s="11"/>
+    </row>
+    <row r="369" spans="3:81">
       <c r="C369" s="11"/>
       <c r="D369" s="11"/>
       <c r="E369" s="11"/>
@@ -30072,8 +31571,12 @@
       <c r="BW369" s="11"/>
       <c r="BX369" s="11"/>
       <c r="BY369" s="11"/>
-    </row>
-    <row r="370" spans="3:77">
+      <c r="BZ369" s="11"/>
+      <c r="CA369" s="11"/>
+      <c r="CB369" s="11"/>
+      <c r="CC369" s="11"/>
+    </row>
+    <row r="370" spans="3:81">
       <c r="C370" s="11"/>
       <c r="D370" s="11"/>
       <c r="E370" s="11"/>
@@ -30149,8 +31652,12 @@
       <c r="BW370" s="11"/>
       <c r="BX370" s="11"/>
       <c r="BY370" s="11"/>
-    </row>
-    <row r="371" spans="3:77">
+      <c r="BZ370" s="11"/>
+      <c r="CA370" s="11"/>
+      <c r="CB370" s="11"/>
+      <c r="CC370" s="11"/>
+    </row>
+    <row r="371" spans="3:81">
       <c r="C371" s="11"/>
       <c r="D371" s="11"/>
       <c r="E371" s="11"/>
@@ -30226,8 +31733,12 @@
       <c r="BW371" s="11"/>
       <c r="BX371" s="11"/>
       <c r="BY371" s="11"/>
-    </row>
-    <row r="372" spans="3:77">
+      <c r="BZ371" s="11"/>
+      <c r="CA371" s="11"/>
+      <c r="CB371" s="11"/>
+      <c r="CC371" s="11"/>
+    </row>
+    <row r="372" spans="3:81">
       <c r="C372" s="11"/>
       <c r="D372" s="11"/>
       <c r="E372" s="11"/>
@@ -30303,8 +31814,12 @@
       <c r="BW372" s="11"/>
       <c r="BX372" s="11"/>
       <c r="BY372" s="11"/>
-    </row>
-    <row r="373" spans="3:77">
+      <c r="BZ372" s="11"/>
+      <c r="CA372" s="11"/>
+      <c r="CB372" s="11"/>
+      <c r="CC372" s="11"/>
+    </row>
+    <row r="373" spans="3:81">
       <c r="C373" s="11"/>
       <c r="D373" s="11"/>
       <c r="E373" s="11"/>
@@ -30380,8 +31895,12 @@
       <c r="BW373" s="11"/>
       <c r="BX373" s="11"/>
       <c r="BY373" s="11"/>
-    </row>
-    <row r="374" spans="3:77">
+      <c r="BZ373" s="11"/>
+      <c r="CA373" s="11"/>
+      <c r="CB373" s="11"/>
+      <c r="CC373" s="11"/>
+    </row>
+    <row r="374" spans="3:81">
       <c r="C374" s="11"/>
       <c r="D374" s="11"/>
       <c r="E374" s="11"/>
@@ -30457,8 +31976,12 @@
       <c r="BW374" s="11"/>
       <c r="BX374" s="11"/>
       <c r="BY374" s="11"/>
-    </row>
-    <row r="375" spans="3:77">
+      <c r="BZ374" s="11"/>
+      <c r="CA374" s="11"/>
+      <c r="CB374" s="11"/>
+      <c r="CC374" s="11"/>
+    </row>
+    <row r="375" spans="3:81">
       <c r="C375" s="11"/>
       <c r="D375" s="11"/>
       <c r="E375" s="11"/>
@@ -30534,8 +32057,12 @@
       <c r="BW375" s="11"/>
       <c r="BX375" s="11"/>
       <c r="BY375" s="11"/>
-    </row>
-    <row r="376" spans="3:77">
+      <c r="BZ375" s="11"/>
+      <c r="CA375" s="11"/>
+      <c r="CB375" s="11"/>
+      <c r="CC375" s="11"/>
+    </row>
+    <row r="376" spans="3:81">
       <c r="C376" s="11"/>
       <c r="D376" s="11"/>
       <c r="E376" s="11"/>
@@ -30611,8 +32138,12 @@
       <c r="BW376" s="11"/>
       <c r="BX376" s="11"/>
       <c r="BY376" s="11"/>
-    </row>
-    <row r="377" spans="3:77">
+      <c r="BZ376" s="11"/>
+      <c r="CA376" s="11"/>
+      <c r="CB376" s="11"/>
+      <c r="CC376" s="11"/>
+    </row>
+    <row r="377" spans="3:81">
       <c r="C377" s="11"/>
       <c r="D377" s="11"/>
       <c r="E377" s="11"/>
@@ -30688,8 +32219,12 @@
       <c r="BW377" s="11"/>
       <c r="BX377" s="11"/>
       <c r="BY377" s="11"/>
-    </row>
-    <row r="378" spans="3:77">
+      <c r="BZ377" s="11"/>
+      <c r="CA377" s="11"/>
+      <c r="CB377" s="11"/>
+      <c r="CC377" s="11"/>
+    </row>
+    <row r="378" spans="3:81">
       <c r="C378" s="11"/>
       <c r="D378" s="11"/>
       <c r="E378" s="11"/>
@@ -30765,8 +32300,12 @@
       <c r="BW378" s="11"/>
       <c r="BX378" s="11"/>
       <c r="BY378" s="11"/>
-    </row>
-    <row r="379" spans="3:77">
+      <c r="BZ378" s="11"/>
+      <c r="CA378" s="11"/>
+      <c r="CB378" s="11"/>
+      <c r="CC378" s="11"/>
+    </row>
+    <row r="379" spans="3:81">
       <c r="C379" s="11"/>
       <c r="D379" s="11"/>
       <c r="E379" s="11"/>
@@ -30842,8 +32381,12 @@
       <c r="BW379" s="11"/>
       <c r="BX379" s="11"/>
       <c r="BY379" s="11"/>
-    </row>
-    <row r="380" spans="3:77">
+      <c r="BZ379" s="11"/>
+      <c r="CA379" s="11"/>
+      <c r="CB379" s="11"/>
+      <c r="CC379" s="11"/>
+    </row>
+    <row r="380" spans="3:81">
       <c r="C380" s="11"/>
       <c r="D380" s="11"/>
       <c r="E380" s="11"/>
@@ -30919,8 +32462,12 @@
       <c r="BW380" s="11"/>
       <c r="BX380" s="11"/>
       <c r="BY380" s="11"/>
-    </row>
-    <row r="381" spans="3:77">
+      <c r="BZ380" s="11"/>
+      <c r="CA380" s="11"/>
+      <c r="CB380" s="11"/>
+      <c r="CC380" s="11"/>
+    </row>
+    <row r="381" spans="3:81">
       <c r="C381" s="11"/>
       <c r="D381" s="11"/>
       <c r="E381" s="11"/>
@@ -30996,8 +32543,12 @@
       <c r="BW381" s="11"/>
       <c r="BX381" s="11"/>
       <c r="BY381" s="11"/>
-    </row>
-    <row r="382" spans="3:77">
+      <c r="BZ381" s="11"/>
+      <c r="CA381" s="11"/>
+      <c r="CB381" s="11"/>
+      <c r="CC381" s="11"/>
+    </row>
+    <row r="382" spans="3:81">
       <c r="C382" s="11"/>
       <c r="D382" s="11"/>
       <c r="E382" s="11"/>
@@ -31073,8 +32624,12 @@
       <c r="BW382" s="11"/>
       <c r="BX382" s="11"/>
       <c r="BY382" s="11"/>
-    </row>
-    <row r="383" spans="3:77">
+      <c r="BZ382" s="11"/>
+      <c r="CA382" s="11"/>
+      <c r="CB382" s="11"/>
+      <c r="CC382" s="11"/>
+    </row>
+    <row r="383" spans="3:81">
       <c r="C383" s="11"/>
       <c r="D383" s="11"/>
       <c r="E383" s="11"/>
@@ -31150,8 +32705,12 @@
       <c r="BW383" s="11"/>
       <c r="BX383" s="11"/>
       <c r="BY383" s="11"/>
-    </row>
-    <row r="384" spans="3:77">
+      <c r="BZ383" s="11"/>
+      <c r="CA383" s="11"/>
+      <c r="CB383" s="11"/>
+      <c r="CC383" s="11"/>
+    </row>
+    <row r="384" spans="3:81">
       <c r="C384" s="11"/>
       <c r="D384" s="11"/>
       <c r="E384" s="11"/>
@@ -31227,8 +32786,12 @@
       <c r="BW384" s="11"/>
       <c r="BX384" s="11"/>
       <c r="BY384" s="11"/>
-    </row>
-    <row r="385" spans="3:77">
+      <c r="BZ384" s="11"/>
+      <c r="CA384" s="11"/>
+      <c r="CB384" s="11"/>
+      <c r="CC384" s="11"/>
+    </row>
+    <row r="385" spans="3:81">
       <c r="C385" s="11"/>
       <c r="D385" s="11"/>
       <c r="E385" s="11"/>
@@ -31304,8 +32867,12 @@
       <c r="BW385" s="11"/>
       <c r="BX385" s="11"/>
       <c r="BY385" s="11"/>
-    </row>
-    <row r="386" spans="3:77">
+      <c r="BZ385" s="11"/>
+      <c r="CA385" s="11"/>
+      <c r="CB385" s="11"/>
+      <c r="CC385" s="11"/>
+    </row>
+    <row r="386" spans="3:81">
       <c r="C386" s="11"/>
       <c r="D386" s="11"/>
       <c r="E386" s="11"/>
@@ -31381,8 +32948,12 @@
       <c r="BW386" s="11"/>
       <c r="BX386" s="11"/>
       <c r="BY386" s="11"/>
-    </row>
-    <row r="387" spans="3:77">
+      <c r="BZ386" s="11"/>
+      <c r="CA386" s="11"/>
+      <c r="CB386" s="11"/>
+      <c r="CC386" s="11"/>
+    </row>
+    <row r="387" spans="3:81">
       <c r="C387" s="11"/>
       <c r="D387" s="11"/>
       <c r="E387" s="11"/>
@@ -31458,8 +33029,12 @@
       <c r="BW387" s="11"/>
       <c r="BX387" s="11"/>
       <c r="BY387" s="11"/>
-    </row>
-    <row r="388" spans="3:77">
+      <c r="BZ387" s="11"/>
+      <c r="CA387" s="11"/>
+      <c r="CB387" s="11"/>
+      <c r="CC387" s="11"/>
+    </row>
+    <row r="388" spans="3:81">
       <c r="C388" s="11"/>
       <c r="D388" s="11"/>
       <c r="E388" s="11"/>
@@ -31535,8 +33110,12 @@
       <c r="BW388" s="11"/>
       <c r="BX388" s="11"/>
       <c r="BY388" s="11"/>
-    </row>
-    <row r="389" spans="3:77">
+      <c r="BZ388" s="11"/>
+      <c r="CA388" s="11"/>
+      <c r="CB388" s="11"/>
+      <c r="CC388" s="11"/>
+    </row>
+    <row r="389" spans="3:81">
       <c r="C389" s="11"/>
       <c r="D389" s="11"/>
       <c r="E389" s="11"/>
@@ -31612,8 +33191,12 @@
       <c r="BW389" s="11"/>
       <c r="BX389" s="11"/>
       <c r="BY389" s="11"/>
-    </row>
-    <row r="390" spans="3:77">
+      <c r="BZ389" s="11"/>
+      <c r="CA389" s="11"/>
+      <c r="CB389" s="11"/>
+      <c r="CC389" s="11"/>
+    </row>
+    <row r="390" spans="3:81">
       <c r="C390" s="11"/>
       <c r="D390" s="11"/>
       <c r="E390" s="11"/>
@@ -31689,8 +33272,12 @@
       <c r="BW390" s="11"/>
       <c r="BX390" s="11"/>
       <c r="BY390" s="11"/>
-    </row>
-    <row r="391" spans="3:77">
+      <c r="BZ390" s="11"/>
+      <c r="CA390" s="11"/>
+      <c r="CB390" s="11"/>
+      <c r="CC390" s="11"/>
+    </row>
+    <row r="391" spans="3:81">
       <c r="C391" s="11"/>
       <c r="D391" s="11"/>
       <c r="E391" s="11"/>
@@ -31766,8 +33353,12 @@
       <c r="BW391" s="11"/>
       <c r="BX391" s="11"/>
       <c r="BY391" s="11"/>
-    </row>
-    <row r="392" spans="3:77">
+      <c r="BZ391" s="11"/>
+      <c r="CA391" s="11"/>
+      <c r="CB391" s="11"/>
+      <c r="CC391" s="11"/>
+    </row>
+    <row r="392" spans="3:81">
       <c r="C392" s="11"/>
       <c r="D392" s="11"/>
       <c r="E392" s="11"/>
@@ -31843,8 +33434,12 @@
       <c r="BW392" s="11"/>
       <c r="BX392" s="11"/>
       <c r="BY392" s="11"/>
-    </row>
-    <row r="393" spans="3:77">
+      <c r="BZ392" s="11"/>
+      <c r="CA392" s="11"/>
+      <c r="CB392" s="11"/>
+      <c r="CC392" s="11"/>
+    </row>
+    <row r="393" spans="3:81">
       <c r="C393" s="11"/>
       <c r="D393" s="11"/>
       <c r="E393" s="11"/>
@@ -31920,8 +33515,12 @@
       <c r="BW393" s="11"/>
       <c r="BX393" s="11"/>
       <c r="BY393" s="11"/>
-    </row>
-    <row r="394" spans="3:77">
+      <c r="BZ393" s="11"/>
+      <c r="CA393" s="11"/>
+      <c r="CB393" s="11"/>
+      <c r="CC393" s="11"/>
+    </row>
+    <row r="394" spans="3:81">
       <c r="C394" s="11"/>
       <c r="D394" s="11"/>
       <c r="E394" s="11"/>
@@ -31997,8 +33596,12 @@
       <c r="BW394" s="11"/>
       <c r="BX394" s="11"/>
       <c r="BY394" s="11"/>
-    </row>
-    <row r="395" spans="3:77">
+      <c r="BZ394" s="11"/>
+      <c r="CA394" s="11"/>
+      <c r="CB394" s="11"/>
+      <c r="CC394" s="11"/>
+    </row>
+    <row r="395" spans="3:81">
       <c r="C395" s="11"/>
       <c r="D395" s="11"/>
       <c r="E395" s="11"/>
@@ -32074,8 +33677,12 @@
       <c r="BW395" s="11"/>
       <c r="BX395" s="11"/>
       <c r="BY395" s="11"/>
-    </row>
-    <row r="396" spans="3:77">
+      <c r="BZ395" s="11"/>
+      <c r="CA395" s="11"/>
+      <c r="CB395" s="11"/>
+      <c r="CC395" s="11"/>
+    </row>
+    <row r="396" spans="3:81">
       <c r="C396" s="11"/>
       <c r="D396" s="11"/>
       <c r="E396" s="11"/>
@@ -32151,8 +33758,12 @@
       <c r="BW396" s="11"/>
       <c r="BX396" s="11"/>
       <c r="BY396" s="11"/>
-    </row>
-    <row r="397" spans="3:77">
+      <c r="BZ396" s="11"/>
+      <c r="CA396" s="11"/>
+      <c r="CB396" s="11"/>
+      <c r="CC396" s="11"/>
+    </row>
+    <row r="397" spans="3:81">
       <c r="C397" s="11"/>
       <c r="D397" s="11"/>
       <c r="E397" s="11"/>
@@ -32228,8 +33839,12 @@
       <c r="BW397" s="11"/>
       <c r="BX397" s="11"/>
       <c r="BY397" s="11"/>
-    </row>
-    <row r="398" spans="3:77">
+      <c r="BZ397" s="11"/>
+      <c r="CA397" s="11"/>
+      <c r="CB397" s="11"/>
+      <c r="CC397" s="11"/>
+    </row>
+    <row r="398" spans="3:81">
       <c r="C398" s="11"/>
       <c r="D398" s="11"/>
       <c r="E398" s="11"/>
@@ -32305,8 +33920,12 @@
       <c r="BW398" s="11"/>
       <c r="BX398" s="11"/>
       <c r="BY398" s="11"/>
-    </row>
-    <row r="399" spans="3:77">
+      <c r="BZ398" s="11"/>
+      <c r="CA398" s="11"/>
+      <c r="CB398" s="11"/>
+      <c r="CC398" s="11"/>
+    </row>
+    <row r="399" spans="3:81">
       <c r="C399" s="11"/>
       <c r="D399" s="11"/>
       <c r="E399" s="11"/>
@@ -32382,8 +34001,12 @@
       <c r="BW399" s="11"/>
       <c r="BX399" s="11"/>
       <c r="BY399" s="11"/>
-    </row>
-    <row r="400" spans="3:77">
+      <c r="BZ399" s="11"/>
+      <c r="CA399" s="11"/>
+      <c r="CB399" s="11"/>
+      <c r="CC399" s="11"/>
+    </row>
+    <row r="400" spans="3:81">
       <c r="C400" s="11"/>
       <c r="D400" s="11"/>
       <c r="E400" s="11"/>
@@ -32459,8 +34082,12 @@
       <c r="BW400" s="11"/>
       <c r="BX400" s="11"/>
       <c r="BY400" s="11"/>
-    </row>
-    <row r="401" spans="3:77">
+      <c r="BZ400" s="11"/>
+      <c r="CA400" s="11"/>
+      <c r="CB400" s="11"/>
+      <c r="CC400" s="11"/>
+    </row>
+    <row r="401" spans="3:81">
       <c r="C401" s="11"/>
       <c r="D401" s="11"/>
       <c r="E401" s="11"/>
@@ -32536,8 +34163,12 @@
       <c r="BW401" s="11"/>
       <c r="BX401" s="11"/>
       <c r="BY401" s="11"/>
-    </row>
-    <row r="402" spans="3:77">
+      <c r="BZ401" s="11"/>
+      <c r="CA401" s="11"/>
+      <c r="CB401" s="11"/>
+      <c r="CC401" s="11"/>
+    </row>
+    <row r="402" spans="3:81">
       <c r="C402" s="11"/>
       <c r="D402" s="11"/>
       <c r="E402" s="11"/>
@@ -32613,8 +34244,12 @@
       <c r="BW402" s="11"/>
       <c r="BX402" s="11"/>
       <c r="BY402" s="11"/>
-    </row>
-    <row r="403" spans="3:77">
+      <c r="BZ402" s="11"/>
+      <c r="CA402" s="11"/>
+      <c r="CB402" s="11"/>
+      <c r="CC402" s="11"/>
+    </row>
+    <row r="403" spans="3:81">
       <c r="C403" s="11"/>
       <c r="D403" s="11"/>
       <c r="E403" s="11"/>
@@ -32690,8 +34325,12 @@
       <c r="BW403" s="11"/>
       <c r="BX403" s="11"/>
       <c r="BY403" s="11"/>
-    </row>
-    <row r="404" spans="3:77">
+      <c r="BZ403" s="11"/>
+      <c r="CA403" s="11"/>
+      <c r="CB403" s="11"/>
+      <c r="CC403" s="11"/>
+    </row>
+    <row r="404" spans="3:81">
       <c r="C404" s="11"/>
       <c r="D404" s="11"/>
       <c r="E404" s="11"/>
@@ -32767,8 +34406,12 @@
       <c r="BW404" s="11"/>
       <c r="BX404" s="11"/>
       <c r="BY404" s="11"/>
-    </row>
-    <row r="405" spans="3:77">
+      <c r="BZ404" s="11"/>
+      <c r="CA404" s="11"/>
+      <c r="CB404" s="11"/>
+      <c r="CC404" s="11"/>
+    </row>
+    <row r="405" spans="3:81">
       <c r="C405" s="11"/>
       <c r="D405" s="11"/>
       <c r="E405" s="11"/>
@@ -32844,8 +34487,12 @@
       <c r="BW405" s="11"/>
       <c r="BX405" s="11"/>
       <c r="BY405" s="11"/>
-    </row>
-    <row r="406" spans="3:77">
+      <c r="BZ405" s="11"/>
+      <c r="CA405" s="11"/>
+      <c r="CB405" s="11"/>
+      <c r="CC405" s="11"/>
+    </row>
+    <row r="406" spans="3:81">
       <c r="C406" s="11"/>
       <c r="D406" s="11"/>
       <c r="E406" s="11"/>
@@ -32921,8 +34568,12 @@
       <c r="BW406" s="11"/>
       <c r="BX406" s="11"/>
       <c r="BY406" s="11"/>
-    </row>
-    <row r="407" spans="3:77">
+      <c r="BZ406" s="11"/>
+      <c r="CA406" s="11"/>
+      <c r="CB406" s="11"/>
+      <c r="CC406" s="11"/>
+    </row>
+    <row r="407" spans="3:81">
       <c r="C407" s="11"/>
       <c r="D407" s="11"/>
       <c r="E407" s="11"/>
@@ -32998,8 +34649,12 @@
       <c r="BW407" s="11"/>
       <c r="BX407" s="11"/>
       <c r="BY407" s="11"/>
-    </row>
-    <row r="408" spans="3:77">
+      <c r="BZ407" s="11"/>
+      <c r="CA407" s="11"/>
+      <c r="CB407" s="11"/>
+      <c r="CC407" s="11"/>
+    </row>
+    <row r="408" spans="3:81">
       <c r="C408" s="11"/>
       <c r="D408" s="11"/>
       <c r="E408" s="11"/>
@@ -33075,8 +34730,12 @@
       <c r="BW408" s="11"/>
       <c r="BX408" s="11"/>
       <c r="BY408" s="11"/>
-    </row>
-    <row r="409" spans="3:77">
+      <c r="BZ408" s="11"/>
+      <c r="CA408" s="11"/>
+      <c r="CB408" s="11"/>
+      <c r="CC408" s="11"/>
+    </row>
+    <row r="409" spans="3:81">
       <c r="C409" s="11"/>
       <c r="D409" s="11"/>
       <c r="E409" s="11"/>
@@ -33152,8 +34811,12 @@
       <c r="BW409" s="11"/>
       <c r="BX409" s="11"/>
       <c r="BY409" s="11"/>
-    </row>
-    <row r="410" spans="3:77">
+      <c r="BZ409" s="11"/>
+      <c r="CA409" s="11"/>
+      <c r="CB409" s="11"/>
+      <c r="CC409" s="11"/>
+    </row>
+    <row r="410" spans="3:81">
       <c r="C410" s="11"/>
       <c r="D410" s="11"/>
       <c r="E410" s="11"/>
@@ -33229,8 +34892,12 @@
       <c r="BW410" s="11"/>
       <c r="BX410" s="11"/>
       <c r="BY410" s="11"/>
-    </row>
-    <row r="411" spans="3:77">
+      <c r="BZ410" s="11"/>
+      <c r="CA410" s="11"/>
+      <c r="CB410" s="11"/>
+      <c r="CC410" s="11"/>
+    </row>
+    <row r="411" spans="3:81">
       <c r="C411" s="11"/>
       <c r="D411" s="11"/>
       <c r="E411" s="11"/>
@@ -33306,8 +34973,12 @@
       <c r="BW411" s="11"/>
       <c r="BX411" s="11"/>
       <c r="BY411" s="11"/>
-    </row>
-    <row r="412" spans="3:77">
+      <c r="BZ411" s="11"/>
+      <c r="CA411" s="11"/>
+      <c r="CB411" s="11"/>
+      <c r="CC411" s="11"/>
+    </row>
+    <row r="412" spans="3:81">
       <c r="C412" s="11"/>
       <c r="D412" s="11"/>
       <c r="E412" s="11"/>
@@ -33383,8 +35054,12 @@
       <c r="BW412" s="11"/>
       <c r="BX412" s="11"/>
       <c r="BY412" s="11"/>
-    </row>
-    <row r="413" spans="3:77">
+      <c r="BZ412" s="11"/>
+      <c r="CA412" s="11"/>
+      <c r="CB412" s="11"/>
+      <c r="CC412" s="11"/>
+    </row>
+    <row r="413" spans="3:81">
       <c r="C413" s="11"/>
       <c r="D413" s="11"/>
       <c r="E413" s="11"/>
@@ -33460,8 +35135,12 @@
       <c r="BW413" s="11"/>
       <c r="BX413" s="11"/>
       <c r="BY413" s="11"/>
-    </row>
-    <row r="414" spans="3:77">
+      <c r="BZ413" s="11"/>
+      <c r="CA413" s="11"/>
+      <c r="CB413" s="11"/>
+      <c r="CC413" s="11"/>
+    </row>
+    <row r="414" spans="3:81">
       <c r="C414" s="11"/>
       <c r="D414" s="11"/>
       <c r="E414" s="11"/>
@@ -33537,8 +35216,12 @@
       <c r="BW414" s="11"/>
       <c r="BX414" s="11"/>
       <c r="BY414" s="11"/>
-    </row>
-    <row r="415" spans="3:77">
+      <c r="BZ414" s="11"/>
+      <c r="CA414" s="11"/>
+      <c r="CB414" s="11"/>
+      <c r="CC414" s="11"/>
+    </row>
+    <row r="415" spans="3:81">
       <c r="C415" s="11"/>
       <c r="D415" s="11"/>
       <c r="E415" s="11"/>
@@ -33614,8 +35297,12 @@
       <c r="BW415" s="11"/>
       <c r="BX415" s="11"/>
       <c r="BY415" s="11"/>
-    </row>
-    <row r="416" spans="3:77">
+      <c r="BZ415" s="11"/>
+      <c r="CA415" s="11"/>
+      <c r="CB415" s="11"/>
+      <c r="CC415" s="11"/>
+    </row>
+    <row r="416" spans="3:81">
       <c r="C416" s="11"/>
       <c r="D416" s="11"/>
       <c r="E416" s="11"/>
@@ -33691,8 +35378,12 @@
       <c r="BW416" s="11"/>
       <c r="BX416" s="11"/>
       <c r="BY416" s="11"/>
-    </row>
-    <row r="417" spans="3:77">
+      <c r="BZ416" s="11"/>
+      <c r="CA416" s="11"/>
+      <c r="CB416" s="11"/>
+      <c r="CC416" s="11"/>
+    </row>
+    <row r="417" spans="3:81">
       <c r="C417" s="11"/>
       <c r="D417" s="11"/>
       <c r="E417" s="11"/>
@@ -33768,8 +35459,12 @@
       <c r="BW417" s="11"/>
       <c r="BX417" s="11"/>
       <c r="BY417" s="11"/>
-    </row>
-    <row r="418" spans="3:77">
+      <c r="BZ417" s="11"/>
+      <c r="CA417" s="11"/>
+      <c r="CB417" s="11"/>
+      <c r="CC417" s="11"/>
+    </row>
+    <row r="418" spans="3:81">
       <c r="C418" s="11"/>
       <c r="D418" s="11"/>
       <c r="E418" s="11"/>
@@ -33845,8 +35540,12 @@
       <c r="BW418" s="11"/>
       <c r="BX418" s="11"/>
       <c r="BY418" s="11"/>
-    </row>
-    <row r="419" spans="3:77">
+      <c r="BZ418" s="11"/>
+      <c r="CA418" s="11"/>
+      <c r="CB418" s="11"/>
+      <c r="CC418" s="11"/>
+    </row>
+    <row r="419" spans="3:81">
       <c r="C419" s="11"/>
       <c r="D419" s="11"/>
       <c r="E419" s="11"/>
@@ -33922,8 +35621,12 @@
       <c r="BW419" s="11"/>
       <c r="BX419" s="11"/>
       <c r="BY419" s="11"/>
-    </row>
-    <row r="420" spans="3:77">
+      <c r="BZ419" s="11"/>
+      <c r="CA419" s="11"/>
+      <c r="CB419" s="11"/>
+      <c r="CC419" s="11"/>
+    </row>
+    <row r="420" spans="3:81">
       <c r="C420" s="11"/>
       <c r="D420" s="11"/>
       <c r="E420" s="11"/>
@@ -33999,8 +35702,12 @@
       <c r="BW420" s="11"/>
       <c r="BX420" s="11"/>
       <c r="BY420" s="11"/>
-    </row>
-    <row r="421" spans="3:77">
+      <c r="BZ420" s="11"/>
+      <c r="CA420" s="11"/>
+      <c r="CB420" s="11"/>
+      <c r="CC420" s="11"/>
+    </row>
+    <row r="421" spans="3:81">
       <c r="C421" s="11"/>
       <c r="D421" s="11"/>
       <c r="E421" s="11"/>
@@ -34076,8 +35783,12 @@
       <c r="BW421" s="11"/>
       <c r="BX421" s="11"/>
       <c r="BY421" s="11"/>
-    </row>
-    <row r="422" spans="3:77">
+      <c r="BZ421" s="11"/>
+      <c r="CA421" s="11"/>
+      <c r="CB421" s="11"/>
+      <c r="CC421" s="11"/>
+    </row>
+    <row r="422" spans="3:81">
       <c r="C422" s="11"/>
       <c r="D422" s="11"/>
       <c r="E422" s="11"/>
@@ -34153,8 +35864,12 @@
       <c r="BW422" s="11"/>
       <c r="BX422" s="11"/>
       <c r="BY422" s="11"/>
-    </row>
-    <row r="423" spans="3:77">
+      <c r="BZ422" s="11"/>
+      <c r="CA422" s="11"/>
+      <c r="CB422" s="11"/>
+      <c r="CC422" s="11"/>
+    </row>
+    <row r="423" spans="3:81">
       <c r="C423" s="11"/>
       <c r="D423" s="11"/>
       <c r="E423" s="11"/>
@@ -34230,8 +35945,12 @@
       <c r="BW423" s="11"/>
       <c r="BX423" s="11"/>
       <c r="BY423" s="11"/>
-    </row>
-    <row r="424" spans="3:77">
+      <c r="BZ423" s="11"/>
+      <c r="CA423" s="11"/>
+      <c r="CB423" s="11"/>
+      <c r="CC423" s="11"/>
+    </row>
+    <row r="424" spans="3:81">
       <c r="C424" s="11"/>
       <c r="D424" s="11"/>
       <c r="E424" s="11"/>
@@ -34307,8 +36026,12 @@
       <c r="BW424" s="11"/>
       <c r="BX424" s="11"/>
       <c r="BY424" s="11"/>
-    </row>
-    <row r="425" spans="3:77">
+      <c r="BZ424" s="11"/>
+      <c r="CA424" s="11"/>
+      <c r="CB424" s="11"/>
+      <c r="CC424" s="11"/>
+    </row>
+    <row r="425" spans="3:81">
       <c r="C425" s="11"/>
       <c r="D425" s="11"/>
       <c r="E425" s="11"/>
@@ -34384,8 +36107,12 @@
       <c r="BW425" s="11"/>
       <c r="BX425" s="11"/>
       <c r="BY425" s="11"/>
-    </row>
-    <row r="426" spans="3:77">
+      <c r="BZ425" s="11"/>
+      <c r="CA425" s="11"/>
+      <c r="CB425" s="11"/>
+      <c r="CC425" s="11"/>
+    </row>
+    <row r="426" spans="3:81">
       <c r="C426" s="11"/>
       <c r="D426" s="11"/>
       <c r="E426" s="11"/>
@@ -34461,8 +36188,12 @@
       <c r="BW426" s="11"/>
       <c r="BX426" s="11"/>
       <c r="BY426" s="11"/>
-    </row>
-    <row r="427" spans="3:77">
+      <c r="BZ426" s="11"/>
+      <c r="CA426" s="11"/>
+      <c r="CB426" s="11"/>
+      <c r="CC426" s="11"/>
+    </row>
+    <row r="427" spans="3:81">
       <c r="C427" s="11"/>
       <c r="D427" s="11"/>
       <c r="E427" s="11"/>
@@ -34538,8 +36269,12 @@
       <c r="BW427" s="11"/>
       <c r="BX427" s="11"/>
       <c r="BY427" s="11"/>
-    </row>
-    <row r="428" spans="3:77">
+      <c r="BZ427" s="11"/>
+      <c r="CA427" s="11"/>
+      <c r="CB427" s="11"/>
+      <c r="CC427" s="11"/>
+    </row>
+    <row r="428" spans="3:81">
       <c r="C428" s="11"/>
       <c r="D428" s="11"/>
       <c r="E428" s="11"/>
@@ -34615,8 +36350,12 @@
       <c r="BW428" s="11"/>
       <c r="BX428" s="11"/>
       <c r="BY428" s="11"/>
-    </row>
-    <row r="429" spans="3:77">
+      <c r="BZ428" s="11"/>
+      <c r="CA428" s="11"/>
+      <c r="CB428" s="11"/>
+      <c r="CC428" s="11"/>
+    </row>
+    <row r="429" spans="3:81">
       <c r="C429" s="11"/>
       <c r="D429" s="11"/>
       <c r="E429" s="11"/>
@@ -34692,8 +36431,12 @@
       <c r="BW429" s="11"/>
       <c r="BX429" s="11"/>
       <c r="BY429" s="11"/>
-    </row>
-    <row r="430" spans="3:77">
+      <c r="BZ429" s="11"/>
+      <c r="CA429" s="11"/>
+      <c r="CB429" s="11"/>
+      <c r="CC429" s="11"/>
+    </row>
+    <row r="430" spans="3:81">
       <c r="C430" s="11"/>
       <c r="D430" s="11"/>
       <c r="E430" s="11"/>
@@ -34769,8 +36512,12 @@
       <c r="BW430" s="11"/>
       <c r="BX430" s="11"/>
       <c r="BY430" s="11"/>
-    </row>
-    <row r="431" spans="3:77">
+      <c r="BZ430" s="11"/>
+      <c r="CA430" s="11"/>
+      <c r="CB430" s="11"/>
+      <c r="CC430" s="11"/>
+    </row>
+    <row r="431" spans="3:81">
       <c r="C431" s="11"/>
       <c r="D431" s="11"/>
       <c r="E431" s="11"/>
@@ -34846,8 +36593,12 @@
       <c r="BW431" s="11"/>
       <c r="BX431" s="11"/>
       <c r="BY431" s="11"/>
-    </row>
-    <row r="432" spans="3:77">
+      <c r="BZ431" s="11"/>
+      <c r="CA431" s="11"/>
+      <c r="CB431" s="11"/>
+      <c r="CC431" s="11"/>
+    </row>
+    <row r="432" spans="3:81">
       <c r="C432" s="11"/>
       <c r="D432" s="11"/>
       <c r="E432" s="11"/>
@@ -34923,8 +36674,12 @@
       <c r="BW432" s="11"/>
       <c r="BX432" s="11"/>
       <c r="BY432" s="11"/>
-    </row>
-    <row r="433" spans="3:77">
+      <c r="BZ432" s="11"/>
+      <c r="CA432" s="11"/>
+      <c r="CB432" s="11"/>
+      <c r="CC432" s="11"/>
+    </row>
+    <row r="433" spans="3:81">
       <c r="C433" s="11"/>
       <c r="D433" s="11"/>
       <c r="E433" s="11"/>
@@ -35000,8 +36755,12 @@
       <c r="BW433" s="11"/>
       <c r="BX433" s="11"/>
       <c r="BY433" s="11"/>
-    </row>
-    <row r="434" spans="3:77">
+      <c r="BZ433" s="11"/>
+      <c r="CA433" s="11"/>
+      <c r="CB433" s="11"/>
+      <c r="CC433" s="11"/>
+    </row>
+    <row r="434" spans="3:81">
       <c r="C434" s="11"/>
       <c r="D434" s="11"/>
       <c r="E434" s="11"/>
@@ -35077,8 +36836,12 @@
       <c r="BW434" s="11"/>
       <c r="BX434" s="11"/>
       <c r="BY434" s="11"/>
-    </row>
-    <row r="435" spans="3:77">
+      <c r="BZ434" s="11"/>
+      <c r="CA434" s="11"/>
+      <c r="CB434" s="11"/>
+      <c r="CC434" s="11"/>
+    </row>
+    <row r="435" spans="3:81">
       <c r="C435" s="11"/>
       <c r="D435" s="11"/>
       <c r="E435" s="11"/>
@@ -35154,8 +36917,12 @@
       <c r="BW435" s="11"/>
       <c r="BX435" s="11"/>
       <c r="BY435" s="11"/>
-    </row>
-    <row r="436" spans="3:77">
+      <c r="BZ435" s="11"/>
+      <c r="CA435" s="11"/>
+      <c r="CB435" s="11"/>
+      <c r="CC435" s="11"/>
+    </row>
+    <row r="436" spans="3:81">
       <c r="C436" s="11"/>
       <c r="D436" s="11"/>
       <c r="E436" s="11"/>
@@ -35231,8 +36998,12 @@
       <c r="BW436" s="11"/>
       <c r="BX436" s="11"/>
       <c r="BY436" s="11"/>
-    </row>
-    <row r="437" spans="3:77">
+      <c r="BZ436" s="11"/>
+      <c r="CA436" s="11"/>
+      <c r="CB436" s="11"/>
+      <c r="CC436" s="11"/>
+    </row>
+    <row r="437" spans="3:81">
       <c r="C437" s="11"/>
       <c r="D437" s="11"/>
       <c r="E437" s="11"/>
@@ -35308,8 +37079,12 @@
       <c r="BW437" s="11"/>
       <c r="BX437" s="11"/>
       <c r="BY437" s="11"/>
-    </row>
-    <row r="438" spans="3:77">
+      <c r="BZ437" s="11"/>
+      <c r="CA437" s="11"/>
+      <c r="CB437" s="11"/>
+      <c r="CC437" s="11"/>
+    </row>
+    <row r="438" spans="3:81">
       <c r="C438" s="11"/>
       <c r="D438" s="11"/>
       <c r="E438" s="11"/>
@@ -35385,8 +37160,12 @@
       <c r="BW438" s="11"/>
       <c r="BX438" s="11"/>
       <c r="BY438" s="11"/>
-    </row>
-    <row r="439" spans="3:77">
+      <c r="BZ438" s="11"/>
+      <c r="CA438" s="11"/>
+      <c r="CB438" s="11"/>
+      <c r="CC438" s="11"/>
+    </row>
+    <row r="439" spans="3:81">
       <c r="C439" s="11"/>
       <c r="D439" s="11"/>
       <c r="E439" s="11"/>
@@ -35462,8 +37241,12 @@
       <c r="BW439" s="11"/>
       <c r="BX439" s="11"/>
       <c r="BY439" s="11"/>
-    </row>
-    <row r="440" spans="3:77">
+      <c r="BZ439" s="11"/>
+      <c r="CA439" s="11"/>
+      <c r="CB439" s="11"/>
+      <c r="CC439" s="11"/>
+    </row>
+    <row r="440" spans="3:81">
       <c r="C440" s="11"/>
       <c r="D440" s="11"/>
       <c r="E440" s="11"/>
@@ -35539,8 +37322,12 @@
       <c r="BW440" s="11"/>
       <c r="BX440" s="11"/>
       <c r="BY440" s="11"/>
-    </row>
-    <row r="441" spans="3:77">
+      <c r="BZ440" s="11"/>
+      <c r="CA440" s="11"/>
+      <c r="CB440" s="11"/>
+      <c r="CC440" s="11"/>
+    </row>
+    <row r="441" spans="3:81">
       <c r="C441" s="11"/>
       <c r="D441" s="11"/>
       <c r="E441" s="11"/>
@@ -35616,8 +37403,12 @@
       <c r="BW441" s="11"/>
       <c r="BX441" s="11"/>
       <c r="BY441" s="11"/>
-    </row>
-    <row r="442" spans="3:77">
+      <c r="BZ441" s="11"/>
+      <c r="CA441" s="11"/>
+      <c r="CB441" s="11"/>
+      <c r="CC441" s="11"/>
+    </row>
+    <row r="442" spans="3:81">
       <c r="C442" s="11"/>
       <c r="D442" s="11"/>
       <c r="E442" s="11"/>
@@ -35693,8 +37484,12 @@
       <c r="BW442" s="11"/>
       <c r="BX442" s="11"/>
       <c r="BY442" s="11"/>
-    </row>
-    <row r="443" spans="3:77">
+      <c r="BZ442" s="11"/>
+      <c r="CA442" s="11"/>
+      <c r="CB442" s="11"/>
+      <c r="CC442" s="11"/>
+    </row>
+    <row r="443" spans="3:81">
       <c r="C443" s="11"/>
       <c r="D443" s="11"/>
       <c r="E443" s="11"/>
@@ -35770,6 +37565,10 @@
       <c r="BW443" s="11"/>
       <c r="BX443" s="11"/>
       <c r="BY443" s="11"/>
+      <c r="BZ443" s="11"/>
+      <c r="CA443" s="11"/>
+      <c r="CB443" s="11"/>
+      <c r="CC443" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E101D433-A70B-445A-A23F-311F00B78FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CBE449-53E7-4968-B083-1AFEA8E2B263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
   </bookViews>
@@ -710,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>330.87</v>
+        <v>323.43</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -721,10 +721,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="4">
-        <v>4741.2737989999996</v>
+        <v>4734.6681840000001</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="4">
         <f>G3*G4</f>
-        <v>1568745.26187513</v>
+        <v>1531333.73075112</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -744,10 +744,10 @@
         <v>7</v>
       </c>
       <c r="G6" s="4">
-        <v>16178</v>
+        <v>14174</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -758,11 +758,11 @@
         <v>8</v>
       </c>
       <c r="G7" s="4">
-        <f>3152+61984</f>
-        <v>65136</v>
+        <f>2252+63805</f>
+        <v>66057</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -771,7 +771,7 @@
       </c>
       <c r="G8" s="4">
         <f>G5-G6+G7</f>
-        <v>1617703.26187513</v>
+        <v>1583216.73075112</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +895,9 @@
         <f>+W3-SUM(G3:I3)</f>
         <v>18913</v>
       </c>
-      <c r="K3" s="11"/>
+      <c r="K3" s="11">
+        <v>14130</v>
+      </c>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
@@ -1002,7 +1004,9 @@
         <f>+W4-SUM(G4:I4)</f>
         <v>-898</v>
       </c>
-      <c r="K4" s="11"/>
+      <c r="K4" s="11">
+        <v>4181</v>
+      </c>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
@@ -1231,7 +1235,9 @@
         <f>+W6-SUM(G6:I6)</f>
         <v>3606</v>
       </c>
-      <c r="K6" s="11"/>
+      <c r="K6" s="11">
+        <v>4041</v>
+      </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -1338,7 +1344,9 @@
         <f>+W7-SUM(G7:I7)</f>
         <v>607</v>
       </c>
-      <c r="K7" s="11"/>
+      <c r="K7" s="11">
+        <v>638</v>
+      </c>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -1451,7 +1459,10 @@
         <f>+W8-SUM(G8:I8)</f>
         <v>1553</v>
       </c>
-      <c r="K8" s="11"/>
+      <c r="K8" s="11">
+        <f>1462+13</f>
+        <v>1475</v>
+      </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -1540,7 +1551,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="11">
-        <f t="shared" ref="C9:J9" si="2">+C5-SUM(C6:C8)</f>
+        <f t="shared" ref="C9:K9" si="2">+C5-SUM(C6:C8)</f>
         <v>7375</v>
       </c>
       <c r="D9" s="11">
@@ -1571,7 +1582,10 @@
         <f t="shared" si="2"/>
         <v>12249</v>
       </c>
-      <c r="K9" s="11"/>
+      <c r="K9" s="11">
+        <f t="shared" si="2"/>
+        <v>13157</v>
+      </c>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
@@ -1694,7 +1708,9 @@
         <f>+W10-SUM(G10:I10)</f>
         <v>2981</v>
       </c>
-      <c r="K10" s="11"/>
+      <c r="K10" s="11">
+        <v>2965</v>
+      </c>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
@@ -1801,7 +1817,9 @@
         <f>+W11-SUM(G11:I11)</f>
         <v>1107</v>
       </c>
-      <c r="K11" s="11"/>
+      <c r="K11" s="11">
+        <v>1019</v>
+      </c>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
@@ -1908,7 +1926,9 @@
         <f>+W12-SUM(G12:I12)</f>
         <v>507</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="11">
+        <v>507</v>
+      </c>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
@@ -2015,7 +2035,9 @@
         <f>+W13-SUM(G13:I13)</f>
         <v>146</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="11">
+        <v>103</v>
+      </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
@@ -2100,7 +2122,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="11">
-        <f t="shared" ref="C14:J14" si="4">+C9-SUM(C10:C13)</f>
+        <f t="shared" ref="C14:K14" si="4">+C9-SUM(C10:C13)</f>
         <v>2083</v>
       </c>
       <c r="D14" s="11">
@@ -2131,7 +2153,10 @@
         <f t="shared" si="4"/>
         <v>7508</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="11">
+        <f t="shared" si="4"/>
+        <v>8563</v>
+      </c>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
@@ -2256,7 +2281,9 @@
         <f>+W15-SUM(G15:I15)</f>
         <v>-864</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="11">
+        <v>-801</v>
+      </c>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
@@ -2363,7 +2390,9 @@
         <f>+W16-SUM(G16:I16)</f>
         <v>225</v>
       </c>
-      <c r="K16" s="11"/>
+      <c r="K16" s="11">
+        <v>433</v>
+      </c>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
@@ -2448,7 +2477,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="11">
-        <f t="shared" ref="C17:J17" si="7">+C14+SUM(C15:C16)</f>
+        <f t="shared" ref="C17:K17" si="7">+C14+SUM(C15:C16)</f>
         <v>1393</v>
       </c>
       <c r="D17" s="11">
@@ -2479,7 +2508,10 @@
         <f t="shared" si="7"/>
         <v>6869</v>
       </c>
-      <c r="K17" s="11"/>
+      <c r="K17" s="11">
+        <f t="shared" si="7"/>
+        <v>8195</v>
+      </c>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
@@ -2602,7 +2634,9 @@
         <f>+W18-SUM(G18:I18)</f>
         <v>-1649</v>
       </c>
-      <c r="K18" s="11"/>
+      <c r="K18" s="11">
+        <v>846</v>
+      </c>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
@@ -2687,7 +2721,7 @@
         <v>43</v>
       </c>
       <c r="C19" s="11">
-        <f t="shared" ref="C19:J19" si="10">+C17-C18</f>
+        <f t="shared" ref="C19:K19" si="10">+C17-C18</f>
         <v>1325</v>
       </c>
       <c r="D19" s="11">
@@ -2718,7 +2752,10 @@
         <f t="shared" si="10"/>
         <v>8518</v>
       </c>
-      <c r="K19" s="11"/>
+      <c r="K19" s="11">
+        <f t="shared" si="10"/>
+        <v>7349</v>
+      </c>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
@@ -2841,7 +2878,9 @@
         <f>+W20-SUM(G20:I20)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="11"/>
+      <c r="K20" s="11">
+        <v>0</v>
+      </c>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
@@ -2946,7 +2985,7 @@
         <v>5503</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" ref="H21:J21" si="14">+H19-H20</f>
+        <f t="shared" ref="H21:K21" si="14">+H19-H20</f>
         <v>4965</v>
       </c>
       <c r="I21" s="11">
@@ -2957,7 +2996,10 @@
         <f t="shared" si="14"/>
         <v>8518</v>
       </c>
-      <c r="K21" s="11"/>
+      <c r="K21" s="11">
+        <f t="shared" si="14"/>
+        <v>7349</v>
+      </c>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
@@ -3159,7 +3201,7 @@
         <v>1.1720979765708199</v>
       </c>
       <c r="H23" s="14">
-        <f t="shared" ref="H23:J23" si="18">+H21/H24</f>
+        <f t="shared" ref="H23:K23" si="18">+H21/H24</f>
         <v>1.0548119821542383</v>
       </c>
       <c r="I23" s="14">
@@ -3170,7 +3212,10 @@
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="14"/>
+      <c r="K23" s="14">
+        <f t="shared" si="18"/>
+        <v>1.5500949166842439</v>
+      </c>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
@@ -3290,7 +3335,9 @@
         <v>4714</v>
       </c>
       <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
+      <c r="K24" s="11">
+        <v>4741</v>
+      </c>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
@@ -3472,33 +3519,36 @@
         <v>0.24438768651700493</v>
       </c>
       <c r="J26" s="15" t="e">
-        <f t="shared" ref="J26:J28" si="23">+J3/F3-1</f>
+        <f>+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="15"/>
+      <c r="K26" s="15">
+        <f>+K3/G3-1</f>
+        <v>0.72928650104026427</v>
+      </c>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="15" t="e">
-        <f t="shared" ref="Q26:U28" si="24">+Q3/P3-1</f>
+        <f t="shared" ref="Q26:U28" si="23">+Q3/P3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R26" s="15" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S26" s="15" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T26" s="15" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U26" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>6.1422536819271567E-2</v>
       </c>
       <c r="V26" s="15">
@@ -3589,41 +3639,44 @@
         <v>0.18853186579087522</v>
       </c>
       <c r="J27" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f>+J4/F4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="15"/>
+      <c r="K27" s="15">
+        <f>+K4/G4-1</f>
+        <v>-0.38013343217197926</v>
+      </c>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="15" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" s="15" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" s="15" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" s="15" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="15">
+        <f t="shared" si="23"/>
+        <v>0.14467224949465773</v>
+      </c>
+      <c r="V27" s="15">
+        <f t="shared" ref="V27:W28" si="24">+V4/U4-1</f>
+        <v>1.6759586276488396</v>
+      </c>
+      <c r="W27" s="15">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" s="15">
-        <f t="shared" si="24"/>
-        <v>0.14467224949465773</v>
-      </c>
-      <c r="V27" s="15">
-        <f t="shared" ref="V27:W28" si="25">+V4/U4-1</f>
-        <v>1.6759586276488396</v>
-      </c>
-      <c r="W27" s="15">
-        <f t="shared" si="25"/>
         <v>-0.10252180061277394</v>
       </c>
       <c r="X27" s="11"/>
@@ -3706,41 +3759,44 @@
         <v>0.2203182374541004</v>
       </c>
       <c r="J28" s="16">
-        <f t="shared" si="23"/>
+        <f>+J5/F5-1</f>
         <v>0.2818414686210331</v>
       </c>
-      <c r="K28" s="16"/>
+      <c r="K28" s="16">
+        <f>+K5/G5-1</f>
+        <v>0.29465004022526142</v>
+      </c>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="16" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" s="16" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S28" s="16" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28" s="16" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="16">
+        <f t="shared" si="23"/>
+        <v>7.8788061319760239E-2</v>
+      </c>
+      <c r="V28" s="16">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R28" s="16" t="e">
+        <v>0.43985035874815037</v>
+      </c>
+      <c r="W28" s="16">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S28" s="16" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28" s="16" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" s="16">
-        <f t="shared" si="24"/>
-        <v>7.8788061319760239E-2</v>
-      </c>
-      <c r="V28" s="16">
-        <f t="shared" si="25"/>
-        <v>0.43985035874815037</v>
-      </c>
-      <c r="W28" s="16">
-        <f t="shared" si="25"/>
         <v>0.23874432853763516</v>
       </c>
       <c r="X28" s="13"/>
@@ -3807,64 +3863,67 @@
         <v>47</v>
       </c>
       <c r="C29" s="15">
-        <f t="shared" ref="C29:G29" si="26">+C9/C5</f>
+        <f t="shared" ref="C29:G29" si="25">+C9/C5</f>
         <v>0.61658724186940894</v>
       </c>
       <c r="D29" s="15">
+        <f t="shared" si="25"/>
+        <v>0.62272763674221188</v>
+      </c>
+      <c r="E29" s="15">
+        <f t="shared" si="25"/>
+        <v>0.6392288861689106</v>
+      </c>
+      <c r="F29" s="15">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="25"/>
+        <v>0.68014212925717354</v>
+      </c>
+      <c r="H29" s="15">
+        <f t="shared" ref="H29:J29" si="26">+H9/H5</f>
+        <v>0.6796187683284457</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="26"/>
-        <v>0.62272763674221188</v>
-      </c>
-      <c r="E29" s="15">
-        <f t="shared" si="26"/>
-        <v>0.6392288861689106</v>
-      </c>
-      <c r="F29" s="15">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="G29" s="15">
-        <f t="shared" si="26"/>
-        <v>0.68014212925717354</v>
-      </c>
-      <c r="H29" s="15">
-        <f t="shared" ref="H29:J29" si="27">+H9/H5</f>
-        <v>0.6796187683284457</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="27"/>
         <v>0.67095035105315948</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="27"/>
+        <f>+J9/J5</f>
         <v>0.6799333888426311</v>
       </c>
-      <c r="K29" s="15"/>
+      <c r="K29" s="15">
+        <f>+K9/K5</f>
+        <v>0.68132152659106204</v>
+      </c>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="11"/>
       <c r="P29" s="15" t="e">
-        <f t="shared" ref="P29:U29" si="28">+P9/P5</f>
+        <f t="shared" ref="P29:U29" si="27">+P9/P5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="15" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="15" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S29" s="15" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.66545191699545225</v>
       </c>
       <c r="U29" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.68929897540411511</v>
       </c>
       <c r="V29" s="15">
@@ -3939,64 +3998,67 @@
         <v>48</v>
       </c>
       <c r="C30" s="15">
-        <f t="shared" ref="C30:G30" si="29">+C14/C5</f>
+        <f t="shared" ref="C30:G30" si="28">+C14/C5</f>
         <v>0.17414931861884458</v>
       </c>
       <c r="D30" s="15">
+        <f t="shared" si="28"/>
+        <v>0.23744694482261552</v>
+      </c>
+      <c r="E30" s="15">
+        <f t="shared" si="28"/>
+        <v>0.28977968176254593</v>
+      </c>
+      <c r="F30" s="15">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="28"/>
+        <v>0.41968356127648165</v>
+      </c>
+      <c r="H30" s="15">
+        <f t="shared" ref="H30:J30" si="29">+H14/H5</f>
+        <v>0.38849640095974408</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="29"/>
-        <v>0.23744694482261552</v>
-      </c>
-      <c r="E30" s="15">
-        <f t="shared" si="29"/>
-        <v>0.28977968176254593</v>
-      </c>
-      <c r="F30" s="15">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="G30" s="15">
-        <f t="shared" si="29"/>
-        <v>0.41968356127648165</v>
-      </c>
-      <c r="H30" s="15">
-        <f t="shared" ref="H30:J30" si="30">+H14/H5</f>
-        <v>0.38849640095974408</v>
-      </c>
-      <c r="I30" s="15">
-        <f t="shared" si="30"/>
         <v>0.36904463390170511</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="30"/>
+        <f>+J14/J5</f>
         <v>0.41676380793782958</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="15">
+        <f>+K14/K5</f>
+        <v>0.44342602661695407</v>
+      </c>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="11"/>
       <c r="P30" s="15" t="e">
-        <f t="shared" ref="P30:U30" si="31">+P14/P5</f>
+        <f t="shared" ref="P30:U30" si="30">+P14/P5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q30" s="15" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R30" s="15" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S30" s="15" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0.42842514230641809</v>
       </c>
       <c r="U30" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0.45246935983695802</v>
       </c>
       <c r="V30" s="15">
@@ -4071,64 +4133,67 @@
         <v>49</v>
       </c>
       <c r="C31" s="15">
-        <f t="shared" ref="C31:G31" si="32">+C18/C17</f>
+        <f t="shared" ref="C31:G31" si="31">+C18/C17</f>
         <v>4.8815506101938265E-2</v>
       </c>
       <c r="D31" s="15">
+        <f t="shared" si="31"/>
+        <v>-5.7855361596009978E-2</v>
+      </c>
+      <c r="E31" s="15">
+        <f t="shared" si="31"/>
+        <v>1.5103349964362081</v>
+      </c>
+      <c r="F31" s="15">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="15">
+        <f t="shared" si="31"/>
+        <v>-2.3679417122040073E-3</v>
+      </c>
+      <c r="H31" s="15">
+        <f t="shared" ref="H31:J31" si="32">+H18/H17</f>
+        <v>2.359882005899705E-2</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="32"/>
-        <v>-5.7855361596009978E-2</v>
-      </c>
-      <c r="E31" s="15">
-        <f t="shared" si="32"/>
-        <v>1.5103349964362081</v>
-      </c>
-      <c r="F31" s="15">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="15">
-        <f t="shared" si="32"/>
-        <v>-2.3679417122040073E-3</v>
-      </c>
-      <c r="H31" s="15">
-        <f t="shared" ref="H31:J31" si="33">+H18/H17</f>
-        <v>2.359882005899705E-2</v>
-      </c>
-      <c r="I31" s="15">
-        <f t="shared" si="33"/>
         <v>0.21665089877010407</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="33"/>
+        <f>+J18/J17</f>
         <v>-0.24006405590333382</v>
       </c>
-      <c r="K31" s="15"/>
+      <c r="K31" s="15">
+        <f>+K18/K17</f>
+        <v>0.10323367907260525</v>
+      </c>
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="11"/>
       <c r="P31" s="15" t="e">
-        <f t="shared" ref="P31:U31" si="34">+P18/P17</f>
+        <f t="shared" ref="P31:U31" si="33">+P18/P17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>7.5518738941611707E-2</v>
       </c>
       <c r="U31" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>6.7231900377558454E-2</v>
       </c>
       <c r="V31" s="15">

--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CBE449-53E7-4968-B083-1AFEA8E2B263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16135A6D-A9A4-489E-BF27-72356FC94E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
   </bookViews>
@@ -710,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>323.43</v>
+        <v>385.02</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="4">
         <f>G3*G4</f>
-        <v>1531333.73075112</v>
+        <v>1822941.9442036799</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -771,7 +771,7 @@
       </c>
       <c r="G8" s="4">
         <f>G5-G6+G7</f>
-        <v>1583216.73075112</v>
+        <v>1874824.9442036799</v>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +1119,9 @@
       <c r="K5" s="13">
         <v>19311</v>
       </c>
-      <c r="L5" s="13"/>
+      <c r="L5" s="13">
+        <v>22187</v>
+      </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="11"/>
@@ -3519,11 +3521,11 @@
         <v>0.24438768651700493</v>
       </c>
       <c r="J26" s="15" t="e">
-        <f>+J3/F3-1</f>
+        <f t="shared" ref="J26:K28" si="23">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="15">
-        <f>+K3/G3-1</f>
+        <f t="shared" si="23"/>
         <v>0.72928650104026427</v>
       </c>
       <c r="L26" s="15"/>
@@ -3532,23 +3534,23 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="15" t="e">
-        <f t="shared" ref="Q26:U28" si="23">+Q3/P3-1</f>
+        <f t="shared" ref="Q26:U28" si="24">+Q3/P3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R26" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S26" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T26" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U26" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.1422536819271567E-2</v>
       </c>
       <c r="V26" s="15">
@@ -3639,11 +3641,11 @@
         <v>0.18853186579087522</v>
       </c>
       <c r="J27" s="15" t="e">
-        <f>+J4/F4-1</f>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="15">
-        <f>+K4/G4-1</f>
+        <f t="shared" si="23"/>
         <v>-0.38013343217197926</v>
       </c>
       <c r="L27" s="15"/>
@@ -3652,31 +3654,31 @@
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R27" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S27" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T27" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U27" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.14467224949465773</v>
       </c>
       <c r="V27" s="15">
-        <f t="shared" ref="V27:W28" si="24">+V4/U4-1</f>
+        <f t="shared" ref="V27:W28" si="25">+V4/U4-1</f>
         <v>1.6759586276488396</v>
       </c>
       <c r="W27" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.10252180061277394</v>
       </c>
       <c r="X27" s="11"/>
@@ -3759,11 +3761,11 @@
         <v>0.2203182374541004</v>
       </c>
       <c r="J28" s="16">
-        <f>+J5/F5-1</f>
+        <f t="shared" si="23"/>
         <v>0.2818414686210331</v>
       </c>
       <c r="K28" s="16">
-        <f>+K5/G5-1</f>
+        <f t="shared" si="23"/>
         <v>0.29465004022526142</v>
       </c>
       <c r="L28" s="16"/>
@@ -3772,31 +3774,31 @@
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="16" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R28" s="16" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S28" s="16" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T28" s="16" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.8788061319760239E-2</v>
       </c>
       <c r="V28" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.43985035874815037</v>
       </c>
       <c r="W28" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.23874432853763516</v>
       </c>
       <c r="X28" s="13"/>
@@ -3863,31 +3865,31 @@
         <v>47</v>
       </c>
       <c r="C29" s="15">
-        <f t="shared" ref="C29:G29" si="25">+C9/C5</f>
+        <f t="shared" ref="C29:G29" si="26">+C9/C5</f>
         <v>0.61658724186940894</v>
       </c>
       <c r="D29" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.62272763674221188</v>
       </c>
       <c r="E29" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.6392288861689106</v>
       </c>
       <c r="F29" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="G29" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.68014212925717354</v>
       </c>
       <c r="H29" s="15">
-        <f t="shared" ref="H29:J29" si="26">+H9/H5</f>
+        <f t="shared" ref="H29:I29" si="27">+H9/H5</f>
         <v>0.6796187683284457</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.67095035105315948</v>
       </c>
       <c r="J29" s="15">
@@ -3903,27 +3905,27 @@
       <c r="N29" s="15"/>
       <c r="O29" s="11"/>
       <c r="P29" s="15" t="e">
-        <f t="shared" ref="P29:U29" si="27">+P9/P5</f>
+        <f t="shared" ref="P29:U29" si="28">+P9/P5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="15" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="15" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S29" s="15" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.66545191699545225</v>
       </c>
       <c r="U29" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.68929897540411511</v>
       </c>
       <c r="V29" s="15">
@@ -3998,31 +4000,31 @@
         <v>48</v>
       </c>
       <c r="C30" s="15">
-        <f t="shared" ref="C30:G30" si="28">+C14/C5</f>
+        <f t="shared" ref="C30:G30" si="29">+C14/C5</f>
         <v>0.17414931861884458</v>
       </c>
       <c r="D30" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.23744694482261552</v>
       </c>
       <c r="E30" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.28977968176254593</v>
       </c>
       <c r="F30" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G30" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.41968356127648165</v>
       </c>
       <c r="H30" s="15">
-        <f t="shared" ref="H30:J30" si="29">+H14/H5</f>
+        <f t="shared" ref="H30:I30" si="30">+H14/H5</f>
         <v>0.38849640095974408</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.36904463390170511</v>
       </c>
       <c r="J30" s="15">
@@ -4038,27 +4040,27 @@
       <c r="N30" s="15"/>
       <c r="O30" s="11"/>
       <c r="P30" s="15" t="e">
-        <f t="shared" ref="P30:U30" si="30">+P14/P5</f>
+        <f t="shared" ref="P30:U30" si="31">+P14/P5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q30" s="15" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R30" s="15" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S30" s="15" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.42842514230641809</v>
       </c>
       <c r="U30" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.45246935983695802</v>
       </c>
       <c r="V30" s="15">
@@ -4133,31 +4135,31 @@
         <v>49</v>
       </c>
       <c r="C31" s="15">
-        <f t="shared" ref="C31:G31" si="31">+C18/C17</f>
+        <f t="shared" ref="C31:G31" si="32">+C18/C17</f>
         <v>4.8815506101938265E-2</v>
       </c>
       <c r="D31" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-5.7855361596009978E-2</v>
       </c>
       <c r="E31" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.5103349964362081</v>
       </c>
       <c r="F31" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="G31" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.3679417122040073E-3</v>
       </c>
       <c r="H31" s="15">
-        <f t="shared" ref="H31:J31" si="32">+H18/H17</f>
+        <f t="shared" ref="H31:I31" si="33">+H18/H17</f>
         <v>2.359882005899705E-2</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.21665089877010407</v>
       </c>
       <c r="J31" s="15">
@@ -4173,27 +4175,27 @@
       <c r="N31" s="15"/>
       <c r="O31" s="11"/>
       <c r="P31" s="15" t="e">
-        <f t="shared" ref="P31:U31" si="33">+P18/P17</f>
+        <f t="shared" ref="P31:U31" si="34">+P18/P17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="15" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="15" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="15" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7.5518738941611707E-2</v>
       </c>
       <c r="U31" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.7231900377558454E-2</v>
       </c>
       <c r="V31" s="15">

--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16135A6D-A9A4-489E-BF27-72356FC94E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC517A7-4365-43F2-9ED5-146F7B37754D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
   </bookViews>
@@ -721,10 +721,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="4">
-        <v>4734.6681840000001</v>
+        <v>4757.5801979999997</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="4">
         <f>G3*G4</f>
-        <v>1822941.9442036799</v>
+        <v>1831763.5278339598</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -744,10 +744,10 @@
         <v>7</v>
       </c>
       <c r="G6" s="4">
-        <v>14174</v>
+        <v>19628</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -758,11 +758,11 @@
         <v>8</v>
       </c>
       <c r="G7" s="4">
-        <f>2252+63805</f>
-        <v>66057</v>
+        <f>2252+62655</f>
+        <v>64907</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -771,7 +771,7 @@
       </c>
       <c r="G8" s="4">
         <f>G5-G6+G7</f>
-        <v>1874824.9442036799</v>
+        <v>1877042.5278339598</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,9 @@
       <c r="K3" s="11">
         <v>14130</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="11">
+        <v>16892</v>
+      </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
@@ -1007,7 +1009,9 @@
       <c r="K4" s="11">
         <v>4181</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="11">
+        <v>5295</v>
+      </c>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
@@ -1240,7 +1244,9 @@
       <c r="K6" s="11">
         <v>4041</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="11">
+        <v>4665</v>
+      </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
@@ -1349,7 +1355,9 @@
       <c r="K7" s="11">
         <v>638</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="11">
+        <v>636</v>
+      </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
@@ -1465,7 +1473,10 @@
         <f>1462+13</f>
         <v>1475</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="11">
+        <f>1461+10</f>
+        <v>1471</v>
+      </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
@@ -1553,7 +1564,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="11">
-        <f t="shared" ref="C9:K9" si="2">+C5-SUM(C6:C8)</f>
+        <f t="shared" ref="C9:L9" si="2">+C5-SUM(C6:C8)</f>
         <v>7375</v>
       </c>
       <c r="D9" s="11">
@@ -1588,7 +1599,10 @@
         <f t="shared" si="2"/>
         <v>13157</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="11">
+        <f t="shared" si="2"/>
+        <v>15415</v>
+      </c>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
@@ -1713,7 +1727,9 @@
       <c r="K10" s="11">
         <v>2965</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="11">
+        <v>2995</v>
+      </c>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
@@ -1822,7 +1838,9 @@
       <c r="K11" s="11">
         <v>1019</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="11">
+        <v>1055</v>
+      </c>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
@@ -1931,7 +1949,9 @@
       <c r="K12" s="11">
         <v>507</v>
       </c>
-      <c r="L12" s="11"/>
+      <c r="L12" s="11">
+        <v>506</v>
+      </c>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
@@ -2040,7 +2060,9 @@
       <c r="K13" s="11">
         <v>103</v>
       </c>
-      <c r="L13" s="11"/>
+      <c r="L13" s="11">
+        <v>71</v>
+      </c>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
@@ -2124,7 +2146,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="11">
-        <f t="shared" ref="C14:K14" si="4">+C9-SUM(C10:C13)</f>
+        <f t="shared" ref="C14:L14" si="4">+C9-SUM(C10:C13)</f>
         <v>2083</v>
       </c>
       <c r="D14" s="11">
@@ -2159,7 +2181,10 @@
         <f t="shared" si="4"/>
         <v>8563</v>
       </c>
-      <c r="L14" s="11"/>
+      <c r="L14" s="11">
+        <f t="shared" si="4"/>
+        <v>10788</v>
+      </c>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
@@ -2286,7 +2311,9 @@
       <c r="K15" s="11">
         <v>-801</v>
       </c>
-      <c r="L15" s="11"/>
+      <c r="L15" s="11">
+        <v>-776</v>
+      </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
@@ -2395,7 +2422,9 @@
       <c r="K16" s="11">
         <v>433</v>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="11">
+        <v>118</v>
+      </c>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
@@ -2479,7 +2508,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="11">
-        <f t="shared" ref="C17:K17" si="7">+C14+SUM(C15:C16)</f>
+        <f t="shared" ref="C17:L17" si="7">+C14+SUM(C15:C16)</f>
         <v>1393</v>
       </c>
       <c r="D17" s="11">
@@ -2514,7 +2543,10 @@
         <f t="shared" si="7"/>
         <v>8195</v>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="11">
+        <f t="shared" si="7"/>
+        <v>10130</v>
+      </c>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
@@ -2639,7 +2671,9 @@
       <c r="K18" s="11">
         <v>846</v>
       </c>
-      <c r="L18" s="11"/>
+      <c r="L18" s="11">
+        <v>820</v>
+      </c>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
@@ -2723,7 +2757,7 @@
         <v>43</v>
       </c>
       <c r="C19" s="11">
-        <f t="shared" ref="C19:K19" si="10">+C17-C18</f>
+        <f t="shared" ref="C19:L19" si="10">+C17-C18</f>
         <v>1325</v>
       </c>
       <c r="D19" s="11">
@@ -2758,7 +2792,10 @@
         <f t="shared" si="10"/>
         <v>7349</v>
       </c>
-      <c r="L19" s="11"/>
+      <c r="L19" s="11">
+        <f t="shared" si="10"/>
+        <v>9310</v>
+      </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
@@ -2883,7 +2920,9 @@
       <c r="K20" s="11">
         <v>0</v>
       </c>
-      <c r="L20" s="11"/>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
@@ -2987,7 +3026,7 @@
         <v>5503</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" ref="H21:K21" si="14">+H19-H20</f>
+        <f t="shared" ref="H21:L21" si="14">+H19-H20</f>
         <v>4965</v>
       </c>
       <c r="I21" s="11">
@@ -3002,7 +3041,10 @@
         <f t="shared" si="14"/>
         <v>7349</v>
       </c>
-      <c r="L21" s="11"/>
+      <c r="L21" s="11">
+        <f t="shared" si="14"/>
+        <v>9310</v>
+      </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
@@ -3203,7 +3245,7 @@
         <v>1.1720979765708199</v>
       </c>
       <c r="H23" s="14">
-        <f t="shared" ref="H23:K23" si="18">+H21/H24</f>
+        <f t="shared" ref="H23:L23" si="18">+H21/H24</f>
         <v>1.0548119821542383</v>
       </c>
       <c r="I23" s="14">
@@ -3218,7 +3260,10 @@
         <f t="shared" si="18"/>
         <v>1.5500949166842439</v>
       </c>
-      <c r="L23" s="14"/>
+      <c r="L23" s="14">
+        <f t="shared" si="18"/>
+        <v>1.9779052475037178</v>
+      </c>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="11"/>
@@ -3340,7 +3385,9 @@
       <c r="K24" s="11">
         <v>4741</v>
       </c>
-      <c r="L24" s="11"/>
+      <c r="L24" s="11">
+        <v>4707</v>
+      </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
@@ -3521,14 +3568,17 @@
         <v>0.24438768651700493</v>
       </c>
       <c r="J26" s="15" t="e">
-        <f t="shared" ref="J26:K28" si="23">+J3/F3-1</f>
+        <f t="shared" ref="J26:L28" si="23">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="15">
         <f t="shared" si="23"/>
         <v>0.72928650104026427</v>
       </c>
-      <c r="L26" s="15"/>
+      <c r="L26" s="15">
+        <f t="shared" si="23"/>
+        <v>0.98589231130966382</v>
+      </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="11"/>
@@ -3648,7 +3698,10 @@
         <f t="shared" si="23"/>
         <v>-0.38013343217197926</v>
       </c>
-      <c r="L27" s="15"/>
+      <c r="L27" s="15">
+        <f t="shared" si="23"/>
+        <v>-0.18513388734995384</v>
+      </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="11"/>
@@ -3768,7 +3821,10 @@
         <f t="shared" si="23"/>
         <v>0.29465004022526142</v>
       </c>
-      <c r="L28" s="16"/>
+      <c r="L28" s="16">
+        <f t="shared" si="23"/>
+        <v>0.47873900293255134</v>
+      </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
       <c r="O28" s="13"/>
@@ -3900,7 +3956,10 @@
         <f>+K9/K5</f>
         <v>0.68132152659106204</v>
       </c>
-      <c r="L29" s="15"/>
+      <c r="L29" s="15">
+        <f>+L9/L5</f>
+        <v>0.69477622030919006</v>
+      </c>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="11"/>
@@ -4035,7 +4094,10 @@
         <f>+K14/K5</f>
         <v>0.44342602661695407</v>
       </c>
-      <c r="L30" s="15"/>
+      <c r="L30" s="15">
+        <f>+L14/L5</f>
+        <v>0.48623067562085909</v>
+      </c>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="11"/>
@@ -4170,7 +4232,10 @@
         <f>+K18/K17</f>
         <v>0.10323367907260525</v>
       </c>
-      <c r="L31" s="15"/>
+      <c r="L31" s="15">
+        <f>+L18/L17</f>
+        <v>8.0947680157946691E-2</v>
+      </c>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="11"/>
